--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,6 +1734,315 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129476557</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80184</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>493793</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6834958</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129456266</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>493797</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6834958</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129456325</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98710</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Korplammsmyran, Korplammsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>493795</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6834954</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1739,7 +1739,7 @@
         <v>129476557</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,6 +2042,2431 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129512476</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>494654</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6833987</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129512298</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>494611</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6834107</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129513963</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Korplamm, Korplamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>494311</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6834701</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129513412</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>494427</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6834434</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129512195</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>494612</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6834233</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129512125</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>494678</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6834243</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129513122</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>494490</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6834127</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129511985</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>494672</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6834352</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129511911</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>494614</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6834378</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129511957</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>494635</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6834347</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129512105</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>494664</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6834295</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129512361</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>494634</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6834067</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129512918</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>494417</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6833948</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129511943</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78802</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>494635</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6834347</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129514113</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98716</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Korplamm, Korplamm, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>494256</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6834732</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129512658</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>494506</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6834042</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129513370</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>494369</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6834380</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129512549</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>494625</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6834032</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129512676</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>494500</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6834016</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129513741</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>494548</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6834603</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129512470</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>494652</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6833984</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129512771</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>494466</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6833989</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129513342</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>494384</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6834354</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129512788</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>494465</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6833963</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129512556</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80185</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>494625</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6834033</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129512298</v>
+        <v>129513963</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2173,14 +2173,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494611</v>
+        <v>494311</v>
       </c>
       <c r="R15" t="n">
-        <v>6834107</v>
+        <v>6834701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513963</v>
+        <v>129513412</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494311</v>
+        <v>494427</v>
       </c>
       <c r="R16" t="n">
-        <v>6834701</v>
+        <v>6834434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129513412</v>
+        <v>129512298</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494427</v>
+        <v>494611</v>
       </c>
       <c r="R17" t="n">
-        <v>6834434</v>
+        <v>6834107</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129511957</v>
+        <v>129512105</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494635</v>
+        <v>494664</v>
       </c>
       <c r="R23" t="n">
-        <v>6834347</v>
+        <v>6834295</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129512105</v>
+        <v>129511957</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494664</v>
+        <v>494635</v>
       </c>
       <c r="R24" t="n">
-        <v>6834295</v>
+        <v>6834347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3403,45 +3403,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129512658</v>
+        <v>129514113</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494506</v>
+        <v>494256</v>
       </c>
       <c r="R28" t="n">
-        <v>6834042</v>
+        <v>6834732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,45 +3500,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129514113</v>
+        <v>129512658</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494256</v>
+        <v>494506</v>
       </c>
       <c r="R29" t="n">
-        <v>6834732</v>
+        <v>6834042</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129513342</v>
+        <v>129512470</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494384</v>
+        <v>494652</v>
       </c>
       <c r="R34" t="n">
-        <v>6834354</v>
+        <v>6833984</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129512470</v>
+        <v>129513342</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494652</v>
+        <v>494384</v>
       </c>
       <c r="R35" t="n">
-        <v>6833984</v>
+        <v>6834354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R40" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522417</v>
+        <v>129522021</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494442</v>
+        <v>494337</v>
       </c>
       <c r="R41" t="n">
-        <v>6834141</v>
+        <v>6834149</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129522256</v>
+        <v>129524595</v>
       </c>
       <c r="B47" t="n">
-        <v>78802</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494384</v>
+        <v>494349</v>
       </c>
       <c r="R47" t="n">
-        <v>6834211</v>
+        <v>6834611</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129521425</v>
+        <v>129524385</v>
       </c>
       <c r="B48" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494187</v>
+        <v>494528</v>
       </c>
       <c r="R48" t="n">
-        <v>6834373</v>
+        <v>6834660</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129524595</v>
+        <v>129522256</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>78802</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494349</v>
+        <v>494384</v>
       </c>
       <c r="R49" t="n">
-        <v>6834611</v>
+        <v>6834211</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129524385</v>
+        <v>129521425</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494528</v>
+        <v>494187</v>
       </c>
       <c r="R50" t="n">
-        <v>6834660</v>
+        <v>6834373</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5731,32 +5731,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521887</v>
+        <v>129520992</v>
       </c>
       <c r="B52" t="n">
-        <v>80178</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494350</v>
+        <v>494221</v>
       </c>
       <c r="R52" t="n">
-        <v>6834298</v>
+        <v>6834431</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129522129</v>
+        <v>129521655</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5839,37 +5839,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494397</v>
+        <v>494247</v>
       </c>
       <c r="R53" t="n">
-        <v>6834116</v>
+        <v>6834296</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5913,22 +5913,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521655</v>
+        <v>129522129</v>
       </c>
       <c r="B54" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,37 +5936,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494247</v>
+        <v>494397</v>
       </c>
       <c r="R54" t="n">
-        <v>6834296</v>
+        <v>6834116</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,12 +6010,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129520992</v>
+        <v>129521887</v>
       </c>
       <c r="B56" t="n">
-        <v>78710</v>
+        <v>80178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494221</v>
+        <v>494350</v>
       </c>
       <c r="R56" t="n">
-        <v>6834431</v>
+        <v>6834298</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6313,57 +6313,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129524059</v>
+        <v>129522432</v>
       </c>
       <c r="B58" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494582</v>
+        <v>494325</v>
       </c>
       <c r="R58" t="n">
-        <v>6834361</v>
+        <v>6834177</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6419,10 +6410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129524189</v>
+        <v>129522151</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6430,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6454,13 +6445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494606</v>
+        <v>494385</v>
       </c>
       <c r="R59" t="n">
-        <v>6834497</v>
+        <v>6834229</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6516,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524775</v>
+        <v>129522138</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6527,21 +6518,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6551,13 +6542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494416</v>
+        <v>494375</v>
       </c>
       <c r="R60" t="n">
-        <v>6834464</v>
+        <v>6834215</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6710,10 +6701,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129522857</v>
+        <v>129521358</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6712,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6736,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494475</v>
+        <v>494221</v>
       </c>
       <c r="R62" t="n">
-        <v>6834232</v>
+        <v>6834353</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,10 +6798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129521358</v>
+        <v>129521656</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>80150</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6818,37 +6809,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494221</v>
+        <v>494219</v>
       </c>
       <c r="R63" t="n">
-        <v>6834353</v>
+        <v>6834291</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6892,22 +6883,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129522151</v>
+        <v>129524189</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6915,21 +6906,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,13 +6930,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494385</v>
+        <v>494606</v>
       </c>
       <c r="R64" t="n">
-        <v>6834229</v>
+        <v>6834497</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7001,10 +6992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129521656</v>
+        <v>129522857</v>
       </c>
       <c r="B65" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7012,37 +7003,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494219</v>
+        <v>494475</v>
       </c>
       <c r="R65" t="n">
-        <v>6834291</v>
+        <v>6834232</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7086,22 +7077,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129522138</v>
+        <v>129524775</v>
       </c>
       <c r="B66" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7100,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,13 +7124,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494375</v>
+        <v>494416</v>
       </c>
       <c r="R66" t="n">
-        <v>6834215</v>
+        <v>6834464</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7195,48 +7186,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129522432</v>
+        <v>129524059</v>
       </c>
       <c r="B67" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494325</v>
+        <v>494582</v>
       </c>
       <c r="R67" t="n">
-        <v>6834177</v>
+        <v>6834361</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129520975</v>
+        <v>129521986</v>
       </c>
       <c r="B68" t="n">
-        <v>78801</v>
+        <v>80150</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494243</v>
+        <v>494336</v>
       </c>
       <c r="R68" t="n">
-        <v>6834445</v>
+        <v>6834146</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,12 +7377,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129521986</v>
+        <v>129520975</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>78801</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,37 +7497,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494336</v>
+        <v>494243</v>
       </c>
       <c r="R70" t="n">
-        <v>6834146</v>
+        <v>6834445</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,12 +7571,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129523011</v>
+        <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494480</v>
+        <v>494385</v>
       </c>
       <c r="R73" t="n">
-        <v>6834232</v>
+        <v>6834293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,19 +7862,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129522011</v>
+        <v>129521838</v>
       </c>
       <c r="B74" t="n">
         <v>79076</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494385</v>
+        <v>494355</v>
       </c>
       <c r="R74" t="n">
-        <v>6834293</v>
+        <v>6834299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129521838</v>
+        <v>129523011</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,37 +7982,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494355</v>
+        <v>494480</v>
       </c>
       <c r="R75" t="n">
-        <v>6834299</v>
+        <v>6834232</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8056,12 +8056,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8165,10 +8165,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524246</v>
+        <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,21 +8176,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8200,13 +8200,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494560</v>
+        <v>494596</v>
       </c>
       <c r="R77" t="n">
-        <v>6834565</v>
+        <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129524147</v>
+        <v>129521271</v>
       </c>
       <c r="B78" t="n">
         <v>79076</v>
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494596</v>
+        <v>494237</v>
       </c>
       <c r="R78" t="n">
-        <v>6834467</v>
+        <v>6834397</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524119</v>
+        <v>129524246</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,34 +8370,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494556</v>
+        <v>494560</v>
       </c>
       <c r="R79" t="n">
-        <v>6834468</v>
+        <v>6834565</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8444,69 +8444,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129520989</v>
+        <v>129522450</v>
       </c>
       <c r="B80" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494262</v>
+        <v>494325</v>
       </c>
       <c r="R80" t="n">
-        <v>6834427</v>
+        <v>6834177</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8550,66 +8541,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522644</v>
+        <v>129522454</v>
       </c>
       <c r="B81" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494450</v>
+        <v>494456</v>
       </c>
       <c r="R81" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8668,10 +8650,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129521271</v>
+        <v>129524119</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8679,37 +8661,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494237</v>
+        <v>494556</v>
       </c>
       <c r="R82" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8753,57 +8735,66 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522454</v>
+        <v>129522644</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494456</v>
+        <v>494450</v>
       </c>
       <c r="R83" t="n">
-        <v>6834177</v>
+        <v>6834178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8862,48 +8853,57 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522450</v>
+        <v>129520989</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494325</v>
+        <v>494262</v>
       </c>
       <c r="R84" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8947,12 +8947,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129521041</v>
+        <v>129521936</v>
       </c>
       <c r="B88" t="n">
         <v>79076</v>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494251</v>
+        <v>494342</v>
       </c>
       <c r="R88" t="n">
-        <v>6834413</v>
+        <v>6834284</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521936</v>
+        <v>129521041</v>
       </c>
       <c r="B89" t="n">
         <v>79076</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494342</v>
+        <v>494251</v>
       </c>
       <c r="R89" t="n">
-        <v>6834284</v>
+        <v>6834413</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9541,10 +9541,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129524791</v>
+        <v>129522027</v>
       </c>
       <c r="B91" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9552,34 +9552,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494381</v>
+        <v>494337</v>
       </c>
       <c r="R91" t="n">
-        <v>6834429</v>
+        <v>6834149</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,71 +9626,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524797</v>
+        <v>129524791</v>
       </c>
       <c r="B92" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494387</v>
+        <v>494381</v>
       </c>
       <c r="R92" t="n">
-        <v>6834437</v>
+        <v>6834429</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9749,10 +9735,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129522027</v>
+        <v>129521475</v>
       </c>
       <c r="B93" t="n">
-        <v>80150</v>
+        <v>78802</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9760,21 +9746,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9784,10 +9770,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494337</v>
+        <v>494181</v>
       </c>
       <c r="R93" t="n">
-        <v>6834149</v>
+        <v>6834367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9943,45 +9929,59 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129522173</v>
+        <v>129524797</v>
       </c>
       <c r="B95" t="n">
-        <v>80149</v>
+        <v>92832</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494418</v>
+        <v>494387</v>
       </c>
       <c r="R95" t="n">
-        <v>6834113</v>
+        <v>6834437</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,22 +10028,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521475</v>
+        <v>129522173</v>
       </c>
       <c r="B96" t="n">
-        <v>78802</v>
+        <v>80149</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494181</v>
+        <v>494418</v>
       </c>
       <c r="R96" t="n">
-        <v>6834367</v>
+        <v>6834113</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10137,10 +10137,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129523005</v>
+        <v>129524273</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10148,21 +10148,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10172,13 +10172,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494491</v>
+        <v>494549</v>
       </c>
       <c r="R97" t="n">
-        <v>6834229</v>
+        <v>6834588</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10437,10 +10437,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129524273</v>
+        <v>129523005</v>
       </c>
       <c r="B100" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10448,21 +10448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10472,13 +10472,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494549</v>
+        <v>494491</v>
       </c>
       <c r="R100" t="n">
-        <v>6834588</v>
+        <v>6834229</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129521144</v>
+        <v>129522517</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494222</v>
+        <v>494455</v>
       </c>
       <c r="R102" t="n">
-        <v>6834390</v>
+        <v>6834176</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,22 +10716,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129524122</v>
+        <v>129521977</v>
       </c>
       <c r="B103" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,21 +10739,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494556</v>
+        <v>494334</v>
       </c>
       <c r="R103" t="n">
-        <v>6834468</v>
+        <v>6834144</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521977</v>
+        <v>129522341</v>
       </c>
       <c r="B104" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,34 +10836,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494334</v>
+        <v>494345</v>
       </c>
       <c r="R104" t="n">
-        <v>6834144</v>
+        <v>6834202</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129522517</v>
+        <v>129521144</v>
       </c>
       <c r="B105" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494455</v>
+        <v>494222</v>
       </c>
       <c r="R105" t="n">
-        <v>6834176</v>
+        <v>6834390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,44 +11007,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129522100</v>
+        <v>129521418</v>
       </c>
       <c r="B106" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11054,13 +11054,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494368</v>
+        <v>494176</v>
       </c>
       <c r="R106" t="n">
-        <v>6834126</v>
+        <v>6834368</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11213,32 +11213,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521418</v>
+        <v>129522100</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494176</v>
+        <v>494368</v>
       </c>
       <c r="R108" t="n">
-        <v>6834368</v>
+        <v>6834126</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11310,10 +11310,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522341</v>
+        <v>129524122</v>
       </c>
       <c r="B109" t="n">
-        <v>78801</v>
+        <v>80150</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11321,34 +11321,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494345</v>
+        <v>494556</v>
       </c>
       <c r="R109" t="n">
-        <v>6834202</v>
+        <v>6834467</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11395,12 +11395,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11504,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129522819</v>
+        <v>129521874</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494470</v>
+        <v>494355</v>
       </c>
       <c r="R111" t="n">
-        <v>6834231</v>
+        <v>6834295</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129521874</v>
+        <v>129522819</v>
       </c>
       <c r="B112" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494355</v>
+        <v>494470</v>
       </c>
       <c r="R112" t="n">
-        <v>6834295</v>
+        <v>6834231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129521147</v>
+        <v>129524240</v>
       </c>
       <c r="B114" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,37 +11815,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494225</v>
+        <v>494559</v>
       </c>
       <c r="R114" t="n">
-        <v>6834382</v>
+        <v>6834519</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11889,19 +11889,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521072</v>
+        <v>129521147</v>
       </c>
       <c r="B115" t="n">
         <v>79044</v>
@@ -11932,14 +11932,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494234</v>
+        <v>494225</v>
       </c>
       <c r="R115" t="n">
-        <v>6834416</v>
+        <v>6834382</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11986,19 +11986,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129524762</v>
+        <v>129521072</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12033,10 +12033,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494406</v>
+        <v>494234</v>
       </c>
       <c r="R116" t="n">
-        <v>6834477</v>
+        <v>6834416</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129524240</v>
+        <v>129524762</v>
       </c>
       <c r="B117" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12130,13 +12130,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494559</v>
+        <v>494406</v>
       </c>
       <c r="R117" t="n">
-        <v>6834519</v>
+        <v>6834477</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129524747</v>
+        <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494401</v>
+        <v>494255</v>
       </c>
       <c r="R118" t="n">
-        <v>6834640</v>
+        <v>6834250</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12289,7 +12289,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524381</v>
+        <v>129524747</v>
       </c>
       <c r="B119" t="n">
         <v>79044</v>
@@ -12320,14 +12320,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494485</v>
+        <v>494401</v>
       </c>
       <c r="R119" t="n">
-        <v>6834612</v>
+        <v>6834640</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12386,10 +12386,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129523234</v>
+        <v>129524381</v>
       </c>
       <c r="B120" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,34 +12397,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494472</v>
+        <v>494485</v>
       </c>
       <c r="R120" t="n">
-        <v>6834268</v>
+        <v>6834612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12471,12 +12471,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -12580,10 +12580,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129521664</v>
+        <v>129523234</v>
       </c>
       <c r="B122" t="n">
-        <v>91571</v>
+        <v>78802</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494255</v>
+        <v>494472</v>
       </c>
       <c r="R122" t="n">
-        <v>6834250</v>
+        <v>6834268</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,22 +12665,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522783</v>
+        <v>129522736</v>
       </c>
       <c r="B123" t="n">
-        <v>79076</v>
+        <v>91571</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494456</v>
+        <v>494443</v>
       </c>
       <c r="R123" t="n">
-        <v>6834228</v>
+        <v>6834230</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522903</v>
+        <v>129521635</v>
       </c>
       <c r="B124" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494466</v>
+        <v>494214</v>
       </c>
       <c r="R124" t="n">
-        <v>6834211</v>
+        <v>6834306</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129522736</v>
+        <v>129524581</v>
       </c>
       <c r="B125" t="n">
-        <v>91571</v>
+        <v>80149</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494443</v>
+        <v>494323</v>
       </c>
       <c r="R125" t="n">
-        <v>6834230</v>
+        <v>6834627</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129523308</v>
+        <v>129521002</v>
       </c>
       <c r="B126" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494520</v>
+        <v>494241</v>
       </c>
       <c r="R126" t="n">
-        <v>6834279</v>
+        <v>6834425</v>
       </c>
       <c r="S126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129521002</v>
+        <v>129522903</v>
       </c>
       <c r="B127" t="n">
         <v>79044</v>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494241</v>
+        <v>494466</v>
       </c>
       <c r="R127" t="n">
-        <v>6834425</v>
+        <v>6834211</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129522012</v>
+        <v>129521823</v>
       </c>
       <c r="B128" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,13 +13197,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494337</v>
+        <v>494360</v>
       </c>
       <c r="R128" t="n">
-        <v>6834146</v>
+        <v>6834206</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129521823</v>
+        <v>129522783</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,37 +13270,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494360</v>
+        <v>494456</v>
       </c>
       <c r="R129" t="n">
-        <v>6834206</v>
+        <v>6834228</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13344,19 +13344,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129521635</v>
+        <v>129523308</v>
       </c>
       <c r="B130" t="n">
         <v>78710</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494214</v>
+        <v>494520</v>
       </c>
       <c r="R130" t="n">
-        <v>6834306</v>
+        <v>6834279</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129524581</v>
+        <v>129522012</v>
       </c>
       <c r="B131" t="n">
         <v>80149</v>
@@ -13484,14 +13484,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494323</v>
+        <v>494337</v>
       </c>
       <c r="R131" t="n">
-        <v>6834627</v>
+        <v>6834146</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13538,22 +13538,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521302</v>
+        <v>129521752</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494215</v>
+        <v>494258</v>
       </c>
       <c r="R132" t="n">
-        <v>6834362</v>
+        <v>6834310</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B133" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13658,21 +13658,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13682,13 +13682,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R133" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13841,45 +13841,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521085</v>
+        <v>129521403</v>
       </c>
       <c r="B135" t="n">
-        <v>98724</v>
+        <v>90582</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494228</v>
+        <v>494199</v>
       </c>
       <c r="R135" t="n">
-        <v>6834405</v>
+        <v>6834366</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13926,22 +13926,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129521403</v>
+        <v>129524667</v>
       </c>
       <c r="B136" t="n">
-        <v>90582</v>
+        <v>80150</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13949,34 +13949,43 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494199</v>
+        <v>494352</v>
       </c>
       <c r="R136" t="n">
-        <v>6834366</v>
+        <v>6834596</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14132,54 +14141,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129524667</v>
+        <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>80150</v>
+        <v>98724</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494352</v>
+        <v>494228</v>
       </c>
       <c r="R138" t="n">
-        <v>6834596</v>
+        <v>6834405</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14226,12 +14226,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R39" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522021</v>
+        <v>129520952</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,21 +4675,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494337</v>
+        <v>494291</v>
       </c>
       <c r="R41" t="n">
-        <v>6834149</v>
+        <v>6834454</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5634,32 +5634,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129521826</v>
+        <v>129521887</v>
       </c>
       <c r="B51" t="n">
-        <v>80150</v>
+        <v>80178</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494361</v>
+        <v>494350</v>
       </c>
       <c r="R51" t="n">
-        <v>6834336</v>
+        <v>6834298</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129520992</v>
+        <v>129521826</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>80150</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494221</v>
+        <v>494361</v>
       </c>
       <c r="R52" t="n">
-        <v>6834431</v>
+        <v>6834336</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521655</v>
+        <v>129520992</v>
       </c>
       <c r="B53" t="n">
         <v>78710</v>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494247</v>
+        <v>494221</v>
       </c>
       <c r="R53" t="n">
-        <v>6834296</v>
+        <v>6834431</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522129</v>
+        <v>129521655</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,37 +5936,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494397</v>
+        <v>494247</v>
       </c>
       <c r="R54" t="n">
-        <v>6834116</v>
+        <v>6834296</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,19 +6010,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522706</v>
+        <v>129522129</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6053,17 +6053,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494454</v>
+        <v>494397</v>
       </c>
       <c r="R55" t="n">
-        <v>6834225</v>
+        <v>6834116</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6107,44 +6107,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521887</v>
+        <v>129522706</v>
       </c>
       <c r="B56" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494350</v>
+        <v>494454</v>
       </c>
       <c r="R56" t="n">
-        <v>6834298</v>
+        <v>6834225</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6216,32 +6216,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129524392</v>
+        <v>129521656</v>
       </c>
       <c r="B57" t="n">
-        <v>92832</v>
+        <v>80150</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6251,13 +6251,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494486</v>
+        <v>494219</v>
       </c>
       <c r="R57" t="n">
-        <v>6834613</v>
+        <v>6834291</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129522432</v>
+        <v>129524189</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,21 +6324,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6348,10 +6348,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494325</v>
+        <v>494606</v>
       </c>
       <c r="R58" t="n">
-        <v>6834177</v>
+        <v>6834497</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6410,10 +6410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522151</v>
+        <v>129522857</v>
       </c>
       <c r="B59" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6421,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494385</v>
+        <v>494475</v>
       </c>
       <c r="R59" t="n">
-        <v>6834229</v>
+        <v>6834232</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129522138</v>
+        <v>129524775</v>
       </c>
       <c r="B60" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6518,21 +6518,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6542,13 +6542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494375</v>
+        <v>494416</v>
       </c>
       <c r="R60" t="n">
-        <v>6834215</v>
+        <v>6834464</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6604,48 +6604,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521131</v>
+        <v>129524059</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494230</v>
+        <v>494582</v>
       </c>
       <c r="R61" t="n">
-        <v>6834385</v>
+        <v>6834361</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6701,45 +6710,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129521358</v>
+        <v>129524392</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>92832</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494221</v>
+        <v>494486</v>
       </c>
       <c r="R62" t="n">
-        <v>6834353</v>
+        <v>6834613</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6786,22 +6795,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129521656</v>
+        <v>129522432</v>
       </c>
       <c r="B63" t="n">
-        <v>80150</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,37 +6818,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494219</v>
+        <v>494325</v>
       </c>
       <c r="R63" t="n">
-        <v>6834291</v>
+        <v>6834177</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6883,22 +6892,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524189</v>
+        <v>129522151</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6906,21 +6915,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6930,13 +6939,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494606</v>
+        <v>494385</v>
       </c>
       <c r="R64" t="n">
-        <v>6834497</v>
+        <v>6834229</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6992,10 +7001,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129522857</v>
+        <v>129522138</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,21 +7012,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7027,13 +7036,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494475</v>
+        <v>494375</v>
       </c>
       <c r="R65" t="n">
-        <v>6834232</v>
+        <v>6834215</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7089,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129524775</v>
+        <v>129521131</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,13 +7133,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494416</v>
+        <v>494230</v>
       </c>
       <c r="R66" t="n">
-        <v>6834464</v>
+        <v>6834385</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7186,54 +7195,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524059</v>
+        <v>129521358</v>
       </c>
       <c r="B67" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494582</v>
+        <v>494221</v>
       </c>
       <c r="R67" t="n">
-        <v>6834361</v>
+        <v>6834353</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129522011</v>
+        <v>129523011</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494385</v>
+        <v>494480</v>
       </c>
       <c r="R73" t="n">
-        <v>6834293</v>
+        <v>6834232</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,19 +7862,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129521838</v>
+        <v>129522011</v>
       </c>
       <c r="B74" t="n">
         <v>79076</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494355</v>
+        <v>494385</v>
       </c>
       <c r="R74" t="n">
-        <v>6834299</v>
+        <v>6834293</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129523011</v>
+        <v>129521838</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,37 +7982,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494480</v>
+        <v>494355</v>
       </c>
       <c r="R75" t="n">
-        <v>6834232</v>
+        <v>6834299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8056,12 +8056,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8165,10 +8165,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524147</v>
+        <v>129524119</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,37 +8176,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494596</v>
+        <v>494556</v>
       </c>
       <c r="R77" t="n">
         <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,19 +8250,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129521271</v>
+        <v>129524147</v>
       </c>
       <c r="B78" t="n">
         <v>79076</v>
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494237</v>
+        <v>494596</v>
       </c>
       <c r="R78" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524246</v>
+        <v>129521271</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,21 +8370,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494560</v>
+        <v>494237</v>
       </c>
       <c r="R79" t="n">
-        <v>6834565</v>
+        <v>6834397</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522450</v>
+        <v>129524246</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -8491,13 +8491,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494325</v>
+        <v>494560</v>
       </c>
       <c r="R80" t="n">
-        <v>6834177</v>
+        <v>6834565</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -8584,17 +8584,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R81" t="n">
         <v>6834177</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8638,22 +8638,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129524119</v>
+        <v>129522454</v>
       </c>
       <c r="B82" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8661,21 +8661,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8685,10 +8685,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494556</v>
+        <v>494456</v>
       </c>
       <c r="R82" t="n">
-        <v>6834467</v>
+        <v>6834177</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9541,10 +9541,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522027</v>
+        <v>129521475</v>
       </c>
       <c r="B91" t="n">
-        <v>80150</v>
+        <v>78802</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9552,21 +9552,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494337</v>
+        <v>494181</v>
       </c>
       <c r="R91" t="n">
-        <v>6834149</v>
+        <v>6834367</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9638,45 +9638,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524791</v>
+        <v>129521897</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494381</v>
+        <v>494323</v>
       </c>
       <c r="R92" t="n">
-        <v>6834429</v>
+        <v>6834131</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,57 +9723,71 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129521475</v>
+        <v>129524797</v>
       </c>
       <c r="B93" t="n">
-        <v>78802</v>
+        <v>92832</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494181</v>
+        <v>494387</v>
       </c>
       <c r="R93" t="n">
-        <v>6834367</v>
+        <v>6834437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9820,44 +9834,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129521897</v>
+        <v>129522027</v>
       </c>
       <c r="B94" t="n">
-        <v>98724</v>
+        <v>80150</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9867,10 +9881,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494323</v>
+        <v>494337</v>
       </c>
       <c r="R94" t="n">
-        <v>6834131</v>
+        <v>6834149</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9929,59 +9943,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129524797</v>
+        <v>129524791</v>
       </c>
       <c r="B95" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494387</v>
+        <v>494381</v>
       </c>
       <c r="R95" t="n">
-        <v>6834437</v>
+        <v>6834429</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10137,48 +10137,57 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129524273</v>
+        <v>129522632</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494549</v>
+        <v>494455</v>
       </c>
       <c r="R97" t="n">
-        <v>6834588</v>
+        <v>6834185</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10222,69 +10231,60 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129522632</v>
+        <v>129524273</v>
       </c>
       <c r="B98" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494455</v>
+        <v>494549</v>
       </c>
       <c r="R98" t="n">
-        <v>6834185</v>
+        <v>6834588</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10328,12 +10328,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129522517</v>
+        <v>129521977</v>
       </c>
       <c r="B102" t="n">
-        <v>78802</v>
+        <v>80149</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,21 +10642,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494455</v>
+        <v>494334</v>
       </c>
       <c r="R102" t="n">
-        <v>6834176</v>
+        <v>6834144</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521977</v>
+        <v>129522341</v>
       </c>
       <c r="B103" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,34 +10739,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494334</v>
+        <v>494345</v>
       </c>
       <c r="R103" t="n">
-        <v>6834144</v>
+        <v>6834202</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,60 +10813,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129522341</v>
+        <v>129522100</v>
       </c>
       <c r="B104" t="n">
-        <v>78801</v>
+        <v>58097</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494345</v>
+        <v>494368</v>
       </c>
       <c r="R104" t="n">
-        <v>6834202</v>
+        <v>6834126</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521144</v>
+        <v>129524122</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494222</v>
+        <v>494556</v>
       </c>
       <c r="R105" t="n">
-        <v>6834390</v>
+        <v>6834467</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,19 +11007,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521418</v>
+        <v>129521144</v>
       </c>
       <c r="B106" t="n">
         <v>79044</v>
@@ -11050,14 +11050,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494176</v>
+        <v>494222</v>
       </c>
       <c r="R106" t="n">
-        <v>6834368</v>
+        <v>6834390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,19 +11104,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521967</v>
+        <v>129521418</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -11147,14 +11147,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494346</v>
+        <v>494176</v>
       </c>
       <c r="R107" t="n">
-        <v>6834277</v>
+        <v>6834368</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,60 +11201,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522100</v>
+        <v>129521967</v>
       </c>
       <c r="B108" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494368</v>
+        <v>494346</v>
       </c>
       <c r="R108" t="n">
-        <v>6834126</v>
+        <v>6834277</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11298,22 +11298,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129524122</v>
+        <v>129522517</v>
       </c>
       <c r="B109" t="n">
-        <v>80150</v>
+        <v>78802</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11321,21 +11321,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494556</v>
+        <v>494455</v>
       </c>
       <c r="R109" t="n">
-        <v>6834467</v>
+        <v>6834176</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521147</v>
+        <v>129521072</v>
       </c>
       <c r="B115" t="n">
         <v>79044</v>
@@ -11932,14 +11932,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494225</v>
+        <v>494234</v>
       </c>
       <c r="R115" t="n">
-        <v>6834382</v>
+        <v>6834416</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11986,19 +11986,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521072</v>
+        <v>129524762</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12033,10 +12033,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494234</v>
+        <v>494406</v>
       </c>
       <c r="R116" t="n">
-        <v>6834416</v>
+        <v>6834477</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12095,7 +12095,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129524762</v>
+        <v>129521147</v>
       </c>
       <c r="B117" t="n">
         <v>79044</v>
@@ -12126,14 +12126,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494406</v>
+        <v>494225</v>
       </c>
       <c r="R117" t="n">
-        <v>6834477</v>
+        <v>6834382</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12180,12 +12180,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B132" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R132" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521302</v>
+        <v>129520912</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -13678,17 +13678,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494215</v>
+        <v>494290</v>
       </c>
       <c r="R133" t="n">
-        <v>6834362</v>
+        <v>6834454</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13732,22 +13732,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129520912</v>
+        <v>129521752</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,34 +13755,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494290</v>
+        <v>494258</v>
       </c>
       <c r="R134" t="n">
-        <v>6834454</v>
+        <v>6834310</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13829,12 +13829,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129513963</v>
+        <v>129512298</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2173,14 +2173,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494311</v>
+        <v>494611</v>
       </c>
       <c r="R15" t="n">
-        <v>6834701</v>
+        <v>6834107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513412</v>
+        <v>129513963</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494427</v>
+        <v>494311</v>
       </c>
       <c r="R16" t="n">
-        <v>6834434</v>
+        <v>6834701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129512298</v>
+        <v>129513412</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494611</v>
+        <v>494427</v>
       </c>
       <c r="R17" t="n">
-        <v>6834107</v>
+        <v>6834434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129512105</v>
+        <v>129511957</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494664</v>
+        <v>494635</v>
       </c>
       <c r="R23" t="n">
-        <v>6834295</v>
+        <v>6834347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129511957</v>
+        <v>129512105</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494635</v>
+        <v>494664</v>
       </c>
       <c r="R24" t="n">
-        <v>6834347</v>
+        <v>6834295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129512918</v>
+        <v>129511943</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494417</v>
+        <v>494635</v>
       </c>
       <c r="R26" t="n">
-        <v>6833948</v>
+        <v>6834347</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129511943</v>
+        <v>129512918</v>
       </c>
       <c r="B27" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,21 +3317,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494635</v>
+        <v>494417</v>
       </c>
       <c r="R27" t="n">
-        <v>6834347</v>
+        <v>6833948</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3403,45 +3403,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129514113</v>
+        <v>129512658</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494256</v>
+        <v>494506</v>
       </c>
       <c r="R28" t="n">
-        <v>6834732</v>
+        <v>6834042</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,45 +3500,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129512658</v>
+        <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494506</v>
+        <v>494256</v>
       </c>
       <c r="R29" t="n">
-        <v>6834042</v>
+        <v>6834732</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R31" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R32" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129522021</v>
+        <v>129520952</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494337</v>
+        <v>494291</v>
       </c>
       <c r="R39" t="n">
-        <v>6834149</v>
+        <v>6834454</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>129522417</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,21 +4675,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R41" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129524342</v>
+        <v>129521092</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494544</v>
+        <v>494222</v>
       </c>
       <c r="R42" t="n">
-        <v>6834616</v>
+        <v>6834398</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4846,22 +4846,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129521092</v>
+        <v>129524342</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494222</v>
+        <v>494544</v>
       </c>
       <c r="R43" t="n">
-        <v>6834398</v>
+        <v>6834616</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5634,32 +5634,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129521887</v>
+        <v>129520992</v>
       </c>
       <c r="B51" t="n">
-        <v>80178</v>
+        <v>78710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494350</v>
+        <v>494221</v>
       </c>
       <c r="R51" t="n">
-        <v>6834298</v>
+        <v>6834431</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521826</v>
+        <v>129521655</v>
       </c>
       <c r="B52" t="n">
-        <v>80150</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494361</v>
+        <v>494247</v>
       </c>
       <c r="R52" t="n">
-        <v>6834336</v>
+        <v>6834296</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129520992</v>
+        <v>129521887</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>80178</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494221</v>
+        <v>494350</v>
       </c>
       <c r="R53" t="n">
-        <v>6834431</v>
+        <v>6834298</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521655</v>
+        <v>129521826</v>
       </c>
       <c r="B54" t="n">
-        <v>78710</v>
+        <v>80150</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,13 +5960,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494247</v>
+        <v>494361</v>
       </c>
       <c r="R54" t="n">
-        <v>6834296</v>
+        <v>6834336</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522129</v>
+        <v>129522706</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6053,17 +6053,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494397</v>
+        <v>494454</v>
       </c>
       <c r="R55" t="n">
-        <v>6834116</v>
+        <v>6834225</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6107,19 +6107,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129522706</v>
+        <v>129522129</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6150,17 +6150,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494454</v>
+        <v>494397</v>
       </c>
       <c r="R56" t="n">
-        <v>6834225</v>
+        <v>6834116</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6204,22 +6204,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521656</v>
+        <v>129522138</v>
       </c>
       <c r="B57" t="n">
-        <v>80150</v>
+        <v>79634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,37 +6227,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494219</v>
+        <v>494375</v>
       </c>
       <c r="R57" t="n">
-        <v>6834291</v>
+        <v>6834215</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6301,60 +6301,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129524189</v>
+        <v>129524059</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494606</v>
+        <v>494582</v>
       </c>
       <c r="R58" t="n">
-        <v>6834497</v>
+        <v>6834361</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6410,10 +6419,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522857</v>
+        <v>129522151</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6421,21 +6430,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6445,10 +6454,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494475</v>
+        <v>494385</v>
       </c>
       <c r="R59" t="n">
-        <v>6834232</v>
+        <v>6834229</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,7 +6516,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524775</v>
+        <v>129524189</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6542,13 +6551,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494416</v>
+        <v>494606</v>
       </c>
       <c r="R60" t="n">
-        <v>6834464</v>
+        <v>6834497</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6604,54 +6613,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129524059</v>
+        <v>129522857</v>
       </c>
       <c r="B61" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494582</v>
+        <v>494475</v>
       </c>
       <c r="R61" t="n">
-        <v>6834361</v>
+        <v>6834232</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,45 +6710,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524392</v>
+        <v>129524775</v>
       </c>
       <c r="B62" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494486</v>
+        <v>494416</v>
       </c>
       <c r="R62" t="n">
-        <v>6834613</v>
+        <v>6834464</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6795,19 +6795,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129522432</v>
+        <v>129521358</v>
       </c>
       <c r="B63" t="n">
         <v>79076</v>
@@ -6842,13 +6842,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494325</v>
+        <v>494221</v>
       </c>
       <c r="R63" t="n">
-        <v>6834177</v>
+        <v>6834353</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6904,10 +6904,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129522151</v>
+        <v>129521131</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6915,21 +6915,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494385</v>
+        <v>494230</v>
       </c>
       <c r="R64" t="n">
-        <v>6834229</v>
+        <v>6834385</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7001,10 +7001,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129522138</v>
+        <v>129522432</v>
       </c>
       <c r="B65" t="n">
-        <v>79634</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7012,21 +7012,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494375</v>
+        <v>494325</v>
       </c>
       <c r="R65" t="n">
-        <v>6834215</v>
+        <v>6834177</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7098,48 +7098,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129521131</v>
+        <v>129524392</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>92835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494230</v>
+        <v>494486</v>
       </c>
       <c r="R66" t="n">
-        <v>6834385</v>
+        <v>6834613</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7183,22 +7183,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129521358</v>
+        <v>129521656</v>
       </c>
       <c r="B67" t="n">
-        <v>79076</v>
+        <v>80150</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,37 +7206,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494221</v>
+        <v>494219</v>
       </c>
       <c r="R67" t="n">
-        <v>6834353</v>
+        <v>6834291</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7280,22 +7280,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B68" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R68" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B69" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R69" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129520975</v>
+        <v>129521986</v>
       </c>
       <c r="B70" t="n">
-        <v>78801</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,37 +7497,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494243</v>
+        <v>494336</v>
       </c>
       <c r="R70" t="n">
-        <v>6834445</v>
+        <v>6834146</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,12 +7571,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7586,7 +7586,7 @@
         <v>129522294</v>
       </c>
       <c r="B71" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129521804</v>
+        <v>129524680</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7691,21 +7691,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494297</v>
+        <v>494357</v>
       </c>
       <c r="R72" t="n">
-        <v>6834314</v>
+        <v>6834592</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129523011</v>
+        <v>129524606</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494480</v>
+        <v>494333</v>
       </c>
       <c r="R73" t="n">
-        <v>6834232</v>
+        <v>6834609</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,22 +7862,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129522011</v>
+        <v>129523011</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,34 +7885,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494385</v>
+        <v>494480</v>
       </c>
       <c r="R74" t="n">
-        <v>6834293</v>
+        <v>6834232</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7959,19 +7959,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129521838</v>
+        <v>129522011</v>
       </c>
       <c r="B75" t="n">
         <v>79076</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494355</v>
+        <v>494385</v>
       </c>
       <c r="R75" t="n">
-        <v>6834299</v>
+        <v>6834293</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129524606</v>
+        <v>129521838</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,21 +8079,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8103,13 +8103,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494333</v>
+        <v>494355</v>
       </c>
       <c r="R76" t="n">
-        <v>6834609</v>
+        <v>6834299</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8165,10 +8165,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524119</v>
+        <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,37 +8176,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494556</v>
+        <v>494596</v>
       </c>
       <c r="R77" t="n">
         <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,19 +8250,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129524147</v>
+        <v>129521271</v>
       </c>
       <c r="B78" t="n">
         <v>79076</v>
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494596</v>
+        <v>494237</v>
       </c>
       <c r="R78" t="n">
-        <v>6834467</v>
+        <v>6834397</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129521271</v>
+        <v>129524119</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,37 +8370,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494237</v>
+        <v>494556</v>
       </c>
       <c r="R79" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8444,12 +8444,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8553,7 +8553,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522450</v>
+        <v>129522454</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -8584,17 +8584,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494325</v>
+        <v>494456</v>
       </c>
       <c r="R81" t="n">
         <v>6834177</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8638,19 +8638,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -8681,17 +8681,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R82" t="n">
         <v>6834177</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8735,12 +8735,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8750,7 +8750,7 @@
         <v>129522644</v>
       </c>
       <c r="B83" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>129520989</v>
       </c>
       <c r="B84" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129520902</v>
+        <v>129523899</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8970,37 +8970,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494278</v>
+        <v>494543</v>
       </c>
       <c r="R85" t="n">
-        <v>6834456</v>
+        <v>6834251</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9044,19 +9044,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129524525</v>
+        <v>129520902</v>
       </c>
       <c r="B86" t="n">
         <v>79044</v>
@@ -9087,14 +9087,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494354</v>
+        <v>494278</v>
       </c>
       <c r="R86" t="n">
-        <v>6834662</v>
+        <v>6834456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9141,22 +9141,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129523899</v>
+        <v>129524525</v>
       </c>
       <c r="B87" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9164,37 +9164,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494543</v>
+        <v>494354</v>
       </c>
       <c r="R87" t="n">
-        <v>6834251</v>
+        <v>6834662</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129521936</v>
+        <v>129522147</v>
       </c>
       <c r="B88" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494342</v>
+        <v>494385</v>
       </c>
       <c r="R88" t="n">
-        <v>6834284</v>
+        <v>6834229</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521041</v>
+        <v>129521936</v>
       </c>
       <c r="B89" t="n">
         <v>79076</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494251</v>
+        <v>494342</v>
       </c>
       <c r="R89" t="n">
-        <v>6834413</v>
+        <v>6834284</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129522147</v>
+        <v>129521041</v>
       </c>
       <c r="B90" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,21 +9455,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494385</v>
+        <v>494251</v>
       </c>
       <c r="R90" t="n">
-        <v>6834229</v>
+        <v>6834413</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9541,45 +9541,59 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129521475</v>
+        <v>129524797</v>
       </c>
       <c r="B91" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494181</v>
+        <v>494387</v>
       </c>
       <c r="R91" t="n">
-        <v>6834367</v>
+        <v>6834437</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,44 +9640,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129521897</v>
+        <v>129522173</v>
       </c>
       <c r="B92" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9673,10 +9687,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494323</v>
+        <v>494418</v>
       </c>
       <c r="R92" t="n">
-        <v>6834131</v>
+        <v>6834113</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9735,59 +9749,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524797</v>
+        <v>129524791</v>
       </c>
       <c r="B93" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494387</v>
+        <v>494381</v>
       </c>
       <c r="R93" t="n">
-        <v>6834437</v>
+        <v>6834429</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9943,45 +9943,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129524791</v>
+        <v>129521897</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494381</v>
+        <v>494323</v>
       </c>
       <c r="R95" t="n">
-        <v>6834429</v>
+        <v>6834131</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,22 +10028,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129522173</v>
+        <v>129521475</v>
       </c>
       <c r="B96" t="n">
-        <v>80149</v>
+        <v>78802</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494418</v>
+        <v>494181</v>
       </c>
       <c r="R96" t="n">
-        <v>6834113</v>
+        <v>6834367</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10137,54 +10137,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129522632</v>
+        <v>129524530</v>
       </c>
       <c r="B97" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494455</v>
+        <v>494349</v>
       </c>
       <c r="R97" t="n">
-        <v>6834185</v>
+        <v>6834653</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10231,12 +10222,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10534,45 +10525,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129524530</v>
+        <v>129522632</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494349</v>
+        <v>494455</v>
       </c>
       <c r="R101" t="n">
-        <v>6834653</v>
+        <v>6834185</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10619,22 +10619,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129521977</v>
+        <v>129521967</v>
       </c>
       <c r="B102" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494334</v>
+        <v>494346</v>
       </c>
       <c r="R102" t="n">
-        <v>6834144</v>
+        <v>6834277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,22 +10716,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129522341</v>
+        <v>129521418</v>
       </c>
       <c r="B103" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,34 +10739,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494345</v>
+        <v>494176</v>
       </c>
       <c r="R103" t="n">
-        <v>6834202</v>
+        <v>6834368</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,60 +10813,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129522100</v>
+        <v>129521144</v>
       </c>
       <c r="B104" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494368</v>
+        <v>494222</v>
       </c>
       <c r="R104" t="n">
-        <v>6834126</v>
+        <v>6834390</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129524122</v>
+        <v>129522341</v>
       </c>
       <c r="B105" t="n">
-        <v>80150</v>
+        <v>78801</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494556</v>
+        <v>494345</v>
       </c>
       <c r="R105" t="n">
-        <v>6834467</v>
+        <v>6834202</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521144</v>
+        <v>129524122</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494222</v>
+        <v>494556</v>
       </c>
       <c r="R106" t="n">
-        <v>6834390</v>
+        <v>6834467</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,44 +11104,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521418</v>
+        <v>129522100</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,13 +11151,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494176</v>
+        <v>494368</v>
       </c>
       <c r="R107" t="n">
-        <v>6834368</v>
+        <v>6834126</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521967</v>
+        <v>129521977</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,34 +11224,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494346</v>
+        <v>494334</v>
       </c>
       <c r="R108" t="n">
-        <v>6834277</v>
+        <v>6834144</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11298,12 +11298,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11601,45 +11601,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129522819</v>
+        <v>129524619</v>
       </c>
       <c r="B112" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494470</v>
+        <v>494338</v>
       </c>
       <c r="R112" t="n">
-        <v>6834231</v>
+        <v>6834601</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11698,54 +11707,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B113" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R113" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521072</v>
+        <v>129524762</v>
       </c>
       <c r="B115" t="n">
         <v>79044</v>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494234</v>
+        <v>494406</v>
       </c>
       <c r="R115" t="n">
-        <v>6834416</v>
+        <v>6834477</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11998,7 +11998,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129524762</v>
+        <v>129521147</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12029,14 +12029,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494406</v>
+        <v>494225</v>
       </c>
       <c r="R116" t="n">
-        <v>6834477</v>
+        <v>6834382</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12083,19 +12083,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129521147</v>
+        <v>129521072</v>
       </c>
       <c r="B117" t="n">
         <v>79044</v>
@@ -12126,14 +12126,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494225</v>
+        <v>494234</v>
       </c>
       <c r="R117" t="n">
-        <v>6834382</v>
+        <v>6834416</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12180,12 +12180,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12195,7 +12195,7 @@
         <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>129522736</v>
       </c>
       <c r="B123" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129521635</v>
+        <v>129521002</v>
       </c>
       <c r="B124" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494214</v>
+        <v>494241</v>
       </c>
       <c r="R124" t="n">
-        <v>6834306</v>
+        <v>6834425</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129524581</v>
+        <v>129522903</v>
       </c>
       <c r="B125" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494323</v>
+        <v>494466</v>
       </c>
       <c r="R125" t="n">
-        <v>6834627</v>
+        <v>6834211</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12968,7 +12968,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521002</v>
+        <v>129521823</v>
       </c>
       <c r="B126" t="n">
         <v>79044</v>
@@ -12999,17 +12999,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494241</v>
+        <v>494360</v>
       </c>
       <c r="R126" t="n">
-        <v>6834425</v>
+        <v>6834206</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13053,22 +13053,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522903</v>
+        <v>129522783</v>
       </c>
       <c r="B127" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494466</v>
+        <v>494456</v>
       </c>
       <c r="R127" t="n">
-        <v>6834211</v>
+        <v>6834228</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129521823</v>
+        <v>129523308</v>
       </c>
       <c r="B128" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,37 +13173,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494360</v>
+        <v>494520</v>
       </c>
       <c r="R128" t="n">
-        <v>6834206</v>
+        <v>6834279</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13247,22 +13247,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129522783</v>
+        <v>129521635</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>78710</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13294,13 +13294,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494456</v>
+        <v>494214</v>
       </c>
       <c r="R129" t="n">
-        <v>6834228</v>
+        <v>6834306</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13356,10 +13356,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129523308</v>
+        <v>129522012</v>
       </c>
       <c r="B130" t="n">
-        <v>78710</v>
+        <v>80149</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,37 +13367,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494520</v>
+        <v>494337</v>
       </c>
       <c r="R130" t="n">
-        <v>6834279</v>
+        <v>6834146</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13441,19 +13441,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522012</v>
+        <v>129524581</v>
       </c>
       <c r="B131" t="n">
         <v>80149</v>
@@ -13484,14 +13484,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494337</v>
+        <v>494323</v>
       </c>
       <c r="R131" t="n">
-        <v>6834146</v>
+        <v>6834627</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13538,22 +13538,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521302</v>
+        <v>129521752</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494215</v>
+        <v>494258</v>
       </c>
       <c r="R132" t="n">
-        <v>6834362</v>
+        <v>6834310</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129520912</v>
+        <v>129521302</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -13678,17 +13678,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494290</v>
+        <v>494215</v>
       </c>
       <c r="R133" t="n">
-        <v>6834454</v>
+        <v>6834362</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13732,22 +13732,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521752</v>
+        <v>129520912</v>
       </c>
       <c r="B134" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,34 +13755,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494258</v>
+        <v>494290</v>
       </c>
       <c r="R134" t="n">
-        <v>6834310</v>
+        <v>6834454</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13829,12 +13829,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -13844,7 +13844,7 @@
         <v>129521403</v>
       </c>
       <c r="B135" t="n">
-        <v>90582</v>
+        <v>90585</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129512298</v>
+        <v>129513412</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494611</v>
+        <v>494427</v>
       </c>
       <c r="R15" t="n">
-        <v>6834107</v>
+        <v>6834434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513963</v>
+        <v>129512298</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494311</v>
+        <v>494611</v>
       </c>
       <c r="R16" t="n">
-        <v>6834701</v>
+        <v>6834107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129513412</v>
+        <v>129513963</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2367,14 +2367,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494427</v>
+        <v>494311</v>
       </c>
       <c r="R17" t="n">
-        <v>6834434</v>
+        <v>6834701</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129511943</v>
+        <v>129512918</v>
       </c>
       <c r="B26" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494635</v>
+        <v>494417</v>
       </c>
       <c r="R26" t="n">
-        <v>6834347</v>
+        <v>6833948</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129512918</v>
+        <v>129511943</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,21 +3317,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494417</v>
+        <v>494635</v>
       </c>
       <c r="R27" t="n">
-        <v>6833948</v>
+        <v>6834347</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3403,45 +3403,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129512658</v>
+        <v>129514113</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494506</v>
+        <v>494256</v>
       </c>
       <c r="R28" t="n">
-        <v>6834042</v>
+        <v>6834732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,45 +3500,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129514113</v>
+        <v>129512658</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494256</v>
+        <v>494506</v>
       </c>
       <c r="R29" t="n">
-        <v>6834732</v>
+        <v>6834042</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R31" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R32" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129512470</v>
+        <v>129513342</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494652</v>
+        <v>494384</v>
       </c>
       <c r="R34" t="n">
-        <v>6833984</v>
+        <v>6834354</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129513342</v>
+        <v>129512470</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494384</v>
+        <v>494652</v>
       </c>
       <c r="R35" t="n">
-        <v>6834354</v>
+        <v>6833984</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522417</v>
+        <v>129522021</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494442</v>
+        <v>494337</v>
       </c>
       <c r="R40" t="n">
-        <v>6834141</v>
+        <v>6834149</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R41" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129520992</v>
+        <v>129521826</v>
       </c>
       <c r="B51" t="n">
-        <v>78710</v>
+        <v>80150</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494221</v>
+        <v>494361</v>
       </c>
       <c r="R51" t="n">
-        <v>6834431</v>
+        <v>6834336</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521655</v>
+        <v>129520992</v>
       </c>
       <c r="B52" t="n">
         <v>78710</v>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494247</v>
+        <v>494221</v>
       </c>
       <c r="R52" t="n">
-        <v>6834296</v>
+        <v>6834431</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521887</v>
+        <v>129521655</v>
       </c>
       <c r="B53" t="n">
-        <v>80178</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494350</v>
+        <v>494247</v>
       </c>
       <c r="R53" t="n">
-        <v>6834298</v>
+        <v>6834296</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,32 +5925,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521826</v>
+        <v>129521887</v>
       </c>
       <c r="B54" t="n">
-        <v>80150</v>
+        <v>80178</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494361</v>
+        <v>494350</v>
       </c>
       <c r="R54" t="n">
-        <v>6834336</v>
+        <v>6834298</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6313,54 +6313,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129524059</v>
+        <v>129521358</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494582</v>
+        <v>494221</v>
       </c>
       <c r="R58" t="n">
-        <v>6834361</v>
+        <v>6834353</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6419,10 +6410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522151</v>
+        <v>129521131</v>
       </c>
       <c r="B59" t="n">
-        <v>78801</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6430,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6454,13 +6445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494385</v>
+        <v>494230</v>
       </c>
       <c r="R59" t="n">
-        <v>6834229</v>
+        <v>6834385</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6516,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524189</v>
+        <v>129522432</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6527,21 +6518,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6551,10 +6542,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494606</v>
+        <v>494325</v>
       </c>
       <c r="R60" t="n">
-        <v>6834497</v>
+        <v>6834177</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6613,10 +6604,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129522857</v>
+        <v>129522151</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,21 +6615,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6648,10 +6639,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494475</v>
+        <v>494385</v>
       </c>
       <c r="R61" t="n">
-        <v>6834232</v>
+        <v>6834229</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,7 +6701,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524775</v>
+        <v>129524189</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -6745,13 +6736,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494416</v>
+        <v>494606</v>
       </c>
       <c r="R62" t="n">
-        <v>6834464</v>
+        <v>6834497</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6807,10 +6798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129521358</v>
+        <v>129522857</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6818,21 +6809,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6842,10 +6833,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494221</v>
+        <v>494475</v>
       </c>
       <c r="R63" t="n">
-        <v>6834353</v>
+        <v>6834232</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,10 +6895,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129521131</v>
+        <v>129524775</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6915,21 +6906,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6939,13 +6930,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494230</v>
+        <v>494416</v>
       </c>
       <c r="R64" t="n">
-        <v>6834385</v>
+        <v>6834464</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7001,48 +6992,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129522432</v>
+        <v>129524392</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>92835</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494325</v>
+        <v>494486</v>
       </c>
       <c r="R65" t="n">
-        <v>6834177</v>
+        <v>6834613</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7086,44 +7077,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129524392</v>
+        <v>129521656</v>
       </c>
       <c r="B66" t="n">
-        <v>92835</v>
+        <v>80150</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,13 +7124,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494486</v>
+        <v>494219</v>
       </c>
       <c r="R66" t="n">
-        <v>6834613</v>
+        <v>6834291</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7195,48 +7186,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129521656</v>
+        <v>129524059</v>
       </c>
       <c r="B67" t="n">
-        <v>80150</v>
+        <v>98727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494219</v>
+        <v>494582</v>
       </c>
       <c r="R67" t="n">
-        <v>6834291</v>
+        <v>6834361</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7280,22 +7280,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521804</v>
+        <v>129521986</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494297</v>
+        <v>494336</v>
       </c>
       <c r="R68" t="n">
-        <v>6834314</v>
+        <v>6834146</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129520975</v>
+        <v>129524680</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>80149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494243</v>
+        <v>494357</v>
       </c>
       <c r="R69" t="n">
-        <v>6834445</v>
+        <v>6834592</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,37 +7497,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R70" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,60 +7571,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129522294</v>
+        <v>129520975</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494419</v>
+        <v>494243</v>
       </c>
       <c r="R71" t="n">
-        <v>6834113</v>
+        <v>6834445</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7668,57 +7668,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129524680</v>
+        <v>129522294</v>
       </c>
       <c r="B72" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494357</v>
+        <v>494419</v>
       </c>
       <c r="R72" t="n">
-        <v>6834592</v>
+        <v>6834113</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7765,22 +7765,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129524606</v>
+        <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,21 +7788,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494333</v>
+        <v>494385</v>
       </c>
       <c r="R73" t="n">
-        <v>6834609</v>
+        <v>6834293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129523011</v>
+        <v>129521838</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,37 +7885,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494480</v>
+        <v>494355</v>
       </c>
       <c r="R74" t="n">
-        <v>6834232</v>
+        <v>6834299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7959,22 +7959,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129522011</v>
+        <v>129523011</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,34 +7982,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494385</v>
+        <v>494480</v>
       </c>
       <c r="R75" t="n">
-        <v>6834293</v>
+        <v>6834232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8056,22 +8056,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129521838</v>
+        <v>129524606</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,21 +8079,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8103,13 +8103,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494355</v>
+        <v>494333</v>
       </c>
       <c r="R76" t="n">
-        <v>6834299</v>
+        <v>6834609</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8165,10 +8165,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524147</v>
+        <v>129524119</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,37 +8176,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494596</v>
+        <v>494556</v>
       </c>
       <c r="R77" t="n">
         <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,60 +8250,69 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129521271</v>
+        <v>129520989</v>
       </c>
       <c r="B78" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494237</v>
+        <v>494262</v>
       </c>
       <c r="R78" t="n">
-        <v>6834397</v>
+        <v>6834427</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8347,57 +8356,66 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524119</v>
+        <v>129522644</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494556</v>
+        <v>494450</v>
       </c>
       <c r="R79" t="n">
-        <v>6834467</v>
+        <v>6834178</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8456,10 +8474,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129524246</v>
+        <v>129524147</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8467,21 +8485,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8491,13 +8509,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494560</v>
+        <v>494596</v>
       </c>
       <c r="R80" t="n">
-        <v>6834565</v>
+        <v>6834467</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8553,10 +8571,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522454</v>
+        <v>129521271</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8564,37 +8582,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494456</v>
+        <v>494237</v>
       </c>
       <c r="R81" t="n">
-        <v>6834177</v>
+        <v>6834397</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8638,19 +8656,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522450</v>
+        <v>129524246</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -8685,13 +8703,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494325</v>
+        <v>494560</v>
       </c>
       <c r="R82" t="n">
-        <v>6834177</v>
+        <v>6834565</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8747,54 +8765,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522644</v>
+        <v>129522454</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494450</v>
+        <v>494456</v>
       </c>
       <c r="R83" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8853,57 +8862,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129520989</v>
+        <v>129522450</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494262</v>
+        <v>494325</v>
       </c>
       <c r="R84" t="n">
-        <v>6834427</v>
+        <v>6834177</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8947,22 +8947,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129523899</v>
+        <v>129520902</v>
       </c>
       <c r="B85" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8970,37 +8970,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494543</v>
+        <v>494278</v>
       </c>
       <c r="R85" t="n">
-        <v>6834251</v>
+        <v>6834456</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9044,19 +9044,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129520902</v>
+        <v>129524525</v>
       </c>
       <c r="B86" t="n">
         <v>79044</v>
@@ -9087,14 +9087,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494278</v>
+        <v>494354</v>
       </c>
       <c r="R86" t="n">
-        <v>6834456</v>
+        <v>6834662</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9141,22 +9141,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129524525</v>
+        <v>129523899</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9164,37 +9164,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494354</v>
+        <v>494543</v>
       </c>
       <c r="R87" t="n">
-        <v>6834662</v>
+        <v>6834251</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129522147</v>
+        <v>129521936</v>
       </c>
       <c r="B88" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494385</v>
+        <v>494342</v>
       </c>
       <c r="R88" t="n">
-        <v>6834229</v>
+        <v>6834284</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521936</v>
+        <v>129521041</v>
       </c>
       <c r="B89" t="n">
         <v>79076</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494342</v>
+        <v>494251</v>
       </c>
       <c r="R89" t="n">
-        <v>6834284</v>
+        <v>6834413</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129521041</v>
+        <v>129522147</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,21 +9455,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494251</v>
+        <v>494385</v>
       </c>
       <c r="R90" t="n">
-        <v>6834413</v>
+        <v>6834229</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9541,59 +9541,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129524797</v>
+        <v>129521897</v>
       </c>
       <c r="B91" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494387</v>
+        <v>494323</v>
       </c>
       <c r="R91" t="n">
-        <v>6834437</v>
+        <v>6834131</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9640,22 +9626,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129522173</v>
+        <v>129521475</v>
       </c>
       <c r="B92" t="n">
-        <v>80149</v>
+        <v>78802</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9663,21 +9649,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9687,10 +9673,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494418</v>
+        <v>494181</v>
       </c>
       <c r="R92" t="n">
-        <v>6834113</v>
+        <v>6834367</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9749,45 +9735,59 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524791</v>
+        <v>129524797</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494381</v>
+        <v>494387</v>
       </c>
       <c r="R93" t="n">
-        <v>6834429</v>
+        <v>6834437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9943,45 +9943,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521897</v>
+        <v>129524791</v>
       </c>
       <c r="B95" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494323</v>
+        <v>494381</v>
       </c>
       <c r="R95" t="n">
-        <v>6834131</v>
+        <v>6834429</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,22 +10028,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521475</v>
+        <v>129522173</v>
       </c>
       <c r="B96" t="n">
-        <v>78802</v>
+        <v>80149</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494181</v>
+        <v>494418</v>
       </c>
       <c r="R96" t="n">
-        <v>6834367</v>
+        <v>6834113</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10137,10 +10137,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129524530</v>
+        <v>129524273</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10148,21 +10148,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10172,13 +10172,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494349</v>
+        <v>494549</v>
       </c>
       <c r="R97" t="n">
-        <v>6834653</v>
+        <v>6834588</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10234,10 +10234,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524273</v>
+        <v>129524130</v>
       </c>
       <c r="B98" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10245,37 +10245,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494549</v>
+        <v>494537</v>
       </c>
       <c r="R98" t="n">
-        <v>6834588</v>
+        <v>6834492</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10319,19 +10319,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129524130</v>
+        <v>129523005</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -10362,14 +10362,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494537</v>
+        <v>494491</v>
       </c>
       <c r="R99" t="n">
-        <v>6834492</v>
+        <v>6834229</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10416,19 +10416,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129523005</v>
+        <v>129524530</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494491</v>
+        <v>494349</v>
       </c>
       <c r="R100" t="n">
-        <v>6834229</v>
+        <v>6834653</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129521967</v>
+        <v>129522517</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494346</v>
+        <v>494455</v>
       </c>
       <c r="R102" t="n">
-        <v>6834277</v>
+        <v>6834176</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,22 +10716,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521418</v>
+        <v>129524122</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,21 +10739,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494176</v>
+        <v>494556</v>
       </c>
       <c r="R103" t="n">
-        <v>6834368</v>
+        <v>6834467</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10825,48 +10825,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521144</v>
+        <v>129522100</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494222</v>
+        <v>494368</v>
       </c>
       <c r="R104" t="n">
-        <v>6834390</v>
+        <v>6834126</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129522341</v>
+        <v>129521977</v>
       </c>
       <c r="B105" t="n">
-        <v>78801</v>
+        <v>80149</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494345</v>
+        <v>494334</v>
       </c>
       <c r="R105" t="n">
-        <v>6834202</v>
+        <v>6834144</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129524122</v>
+        <v>129521967</v>
       </c>
       <c r="B106" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494556</v>
+        <v>494346</v>
       </c>
       <c r="R106" t="n">
-        <v>6834467</v>
+        <v>6834277</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,44 +11104,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129522100</v>
+        <v>129521418</v>
       </c>
       <c r="B107" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,13 +11151,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494368</v>
+        <v>494176</v>
       </c>
       <c r="R107" t="n">
-        <v>6834126</v>
+        <v>6834368</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521977</v>
+        <v>129521144</v>
       </c>
       <c r="B108" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,34 +11224,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494334</v>
+        <v>494222</v>
       </c>
       <c r="R108" t="n">
-        <v>6834144</v>
+        <v>6834390</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11298,22 +11298,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522517</v>
+        <v>129522341</v>
       </c>
       <c r="B109" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11321,34 +11321,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494455</v>
+        <v>494345</v>
       </c>
       <c r="R109" t="n">
-        <v>6834176</v>
+        <v>6834202</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11395,12 +11395,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521664</v>
+        <v>129521663</v>
       </c>
       <c r="B118" t="n">
-        <v>91574</v>
+        <v>78802</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494255</v>
+        <v>494242</v>
       </c>
       <c r="R118" t="n">
-        <v>6834250</v>
+        <v>6834295</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524747</v>
+        <v>129523234</v>
       </c>
       <c r="B119" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494401</v>
+        <v>494472</v>
       </c>
       <c r="R119" t="n">
-        <v>6834640</v>
+        <v>6834268</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129524381</v>
+        <v>129521664</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494485</v>
+        <v>494255</v>
       </c>
       <c r="R120" t="n">
-        <v>6834612</v>
+        <v>6834250</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129521663</v>
+        <v>129524747</v>
       </c>
       <c r="B121" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494242</v>
+        <v>494401</v>
       </c>
       <c r="R121" t="n">
-        <v>6834295</v>
+        <v>6834640</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129523234</v>
+        <v>129524381</v>
       </c>
       <c r="B122" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494472</v>
+        <v>494485</v>
       </c>
       <c r="R122" t="n">
-        <v>6834268</v>
+        <v>6834612</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,22 +12665,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522736</v>
+        <v>129523308</v>
       </c>
       <c r="B123" t="n">
-        <v>91574</v>
+        <v>78710</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,13 +12712,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494443</v>
+        <v>494520</v>
       </c>
       <c r="R123" t="n">
-        <v>6834230</v>
+        <v>6834279</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129521002</v>
+        <v>129521635</v>
       </c>
       <c r="B124" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494241</v>
+        <v>494214</v>
       </c>
       <c r="R124" t="n">
-        <v>6834425</v>
+        <v>6834306</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129522903</v>
+        <v>129522012</v>
       </c>
       <c r="B125" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,34 +12882,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494466</v>
+        <v>494337</v>
       </c>
       <c r="R125" t="n">
-        <v>6834211</v>
+        <v>6834146</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12956,19 +12956,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521823</v>
+        <v>129521002</v>
       </c>
       <c r="B126" t="n">
         <v>79044</v>
@@ -12999,17 +12999,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494360</v>
+        <v>494241</v>
       </c>
       <c r="R126" t="n">
-        <v>6834206</v>
+        <v>6834425</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13053,22 +13053,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522783</v>
+        <v>129522903</v>
       </c>
       <c r="B127" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494456</v>
+        <v>494466</v>
       </c>
       <c r="R127" t="n">
-        <v>6834228</v>
+        <v>6834211</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129523308</v>
+        <v>129521823</v>
       </c>
       <c r="B128" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,37 +13173,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494520</v>
+        <v>494360</v>
       </c>
       <c r="R128" t="n">
-        <v>6834279</v>
+        <v>6834206</v>
       </c>
       <c r="S128" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13247,22 +13247,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129521635</v>
+        <v>129524581</v>
       </c>
       <c r="B129" t="n">
-        <v>78710</v>
+        <v>80149</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13294,13 +13294,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494214</v>
+        <v>494323</v>
       </c>
       <c r="R129" t="n">
-        <v>6834306</v>
+        <v>6834627</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13356,10 +13356,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129522012</v>
+        <v>129522736</v>
       </c>
       <c r="B130" t="n">
-        <v>80149</v>
+        <v>91574</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,34 +13367,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494337</v>
+        <v>494443</v>
       </c>
       <c r="R130" t="n">
-        <v>6834146</v>
+        <v>6834230</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13441,22 +13441,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129524581</v>
+        <v>129522783</v>
       </c>
       <c r="B131" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494323</v>
+        <v>494456</v>
       </c>
       <c r="R131" t="n">
-        <v>6834627</v>
+        <v>6834228</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B132" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R132" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521302</v>
+        <v>129520912</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -13678,17 +13678,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494215</v>
+        <v>494290</v>
       </c>
       <c r="R133" t="n">
-        <v>6834362</v>
+        <v>6834454</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13732,22 +13732,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129520912</v>
+        <v>129521752</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,34 +13755,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494290</v>
+        <v>494258</v>
       </c>
       <c r="R134" t="n">
-        <v>6834454</v>
+        <v>6834310</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13829,12 +13829,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129513412</v>
+        <v>129512298</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494427</v>
+        <v>494611</v>
       </c>
       <c r="R15" t="n">
-        <v>6834434</v>
+        <v>6834107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129512298</v>
+        <v>129513963</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494611</v>
+        <v>494311</v>
       </c>
       <c r="R16" t="n">
-        <v>6834107</v>
+        <v>6834701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129513963</v>
+        <v>129513412</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2367,14 +2367,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494311</v>
+        <v>494427</v>
       </c>
       <c r="R17" t="n">
-        <v>6834701</v>
+        <v>6834434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129511985</v>
+        <v>129511911</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494672</v>
+        <v>494614</v>
       </c>
       <c r="R21" t="n">
-        <v>6834352</v>
+        <v>6834378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129511911</v>
+        <v>129511985</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494614</v>
+        <v>494672</v>
       </c>
       <c r="R22" t="n">
-        <v>6834378</v>
+        <v>6834352</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129511957</v>
+        <v>129512105</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494635</v>
+        <v>494664</v>
       </c>
       <c r="R23" t="n">
-        <v>6834347</v>
+        <v>6834295</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129512105</v>
+        <v>129511957</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494664</v>
+        <v>494635</v>
       </c>
       <c r="R24" t="n">
-        <v>6834295</v>
+        <v>6834347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R31" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R32" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129512470</v>
+        <v>129512771</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494652</v>
+        <v>494466</v>
       </c>
       <c r="R35" t="n">
-        <v>6833984</v>
+        <v>6833989</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129512771</v>
+        <v>129512470</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494466</v>
+        <v>494652</v>
       </c>
       <c r="R36" t="n">
-        <v>6833989</v>
+        <v>6833984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129521092</v>
+        <v>129524342</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494222</v>
+        <v>494544</v>
       </c>
       <c r="R42" t="n">
-        <v>6834398</v>
+        <v>6834616</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4846,22 +4846,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129524342</v>
+        <v>129521092</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494544</v>
+        <v>494222</v>
       </c>
       <c r="R43" t="n">
-        <v>6834616</v>
+        <v>6834398</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129522893</v>
+        <v>129524595</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494477</v>
+        <v>494349</v>
       </c>
       <c r="R46" t="n">
-        <v>6834229</v>
+        <v>6834611</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524595</v>
+        <v>129524385</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494349</v>
+        <v>494528</v>
       </c>
       <c r="R47" t="n">
-        <v>6834611</v>
+        <v>6834660</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129524385</v>
+        <v>129522893</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494528</v>
+        <v>494477</v>
       </c>
       <c r="R48" t="n">
-        <v>6834660</v>
+        <v>6834229</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129521826</v>
+        <v>129522706</v>
       </c>
       <c r="B51" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494361</v>
+        <v>494454</v>
       </c>
       <c r="R51" t="n">
-        <v>6834336</v>
+        <v>6834225</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129520992</v>
+        <v>129522129</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,37 +5742,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494221</v>
+        <v>494397</v>
       </c>
       <c r="R52" t="n">
-        <v>6834431</v>
+        <v>6834116</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5816,19 +5816,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521655</v>
+        <v>129520992</v>
       </c>
       <c r="B53" t="n">
         <v>78710</v>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494247</v>
+        <v>494221</v>
       </c>
       <c r="R53" t="n">
-        <v>6834296</v>
+        <v>6834431</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5925,32 +5925,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521887</v>
+        <v>129521655</v>
       </c>
       <c r="B54" t="n">
-        <v>80178</v>
+        <v>78710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,13 +5960,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494350</v>
+        <v>494247</v>
       </c>
       <c r="R54" t="n">
-        <v>6834298</v>
+        <v>6834296</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6022,10 +6022,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522706</v>
+        <v>129521826</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6057,13 +6057,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494454</v>
+        <v>494361</v>
       </c>
       <c r="R55" t="n">
-        <v>6834225</v>
+        <v>6834336</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6119,45 +6119,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129522129</v>
+        <v>129521887</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494397</v>
+        <v>494350</v>
       </c>
       <c r="R56" t="n">
-        <v>6834116</v>
+        <v>6834298</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,60 +6204,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129522138</v>
+        <v>129524059</v>
       </c>
       <c r="B57" t="n">
-        <v>79634</v>
+        <v>98727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494375</v>
+        <v>494582</v>
       </c>
       <c r="R57" t="n">
-        <v>6834215</v>
+        <v>6834361</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6604,10 +6613,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129522151</v>
+        <v>129521656</v>
       </c>
       <c r="B61" t="n">
-        <v>78801</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,37 +6624,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494385</v>
+        <v>494219</v>
       </c>
       <c r="R61" t="n">
-        <v>6834229</v>
+        <v>6834291</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6689,60 +6698,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524189</v>
+        <v>129524392</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494606</v>
+        <v>494486</v>
       </c>
       <c r="R62" t="n">
-        <v>6834497</v>
+        <v>6834613</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6786,22 +6795,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129522857</v>
+        <v>129522151</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,21 +6818,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6833,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494475</v>
+        <v>494385</v>
       </c>
       <c r="R63" t="n">
-        <v>6834232</v>
+        <v>6834229</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6895,7 +6904,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524775</v>
+        <v>129524189</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6930,13 +6939,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494416</v>
+        <v>494606</v>
       </c>
       <c r="R64" t="n">
-        <v>6834464</v>
+        <v>6834497</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6992,45 +7001,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129524392</v>
+        <v>129522857</v>
       </c>
       <c r="B65" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494486</v>
+        <v>494475</v>
       </c>
       <c r="R65" t="n">
-        <v>6834613</v>
+        <v>6834232</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7077,22 +7086,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129521656</v>
+        <v>129524775</v>
       </c>
       <c r="B66" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,37 +7109,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494219</v>
+        <v>494416</v>
       </c>
       <c r="R66" t="n">
-        <v>6834291</v>
+        <v>6834464</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7174,69 +7183,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524059</v>
+        <v>129522138</v>
       </c>
       <c r="B67" t="n">
-        <v>98727</v>
+        <v>79634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494582</v>
+        <v>494375</v>
       </c>
       <c r="R67" t="n">
-        <v>6834361</v>
+        <v>6834215</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129522011</v>
+        <v>129524606</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,21 +7788,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494385</v>
+        <v>494333</v>
       </c>
       <c r="R73" t="n">
-        <v>6834293</v>
+        <v>6834609</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129521838</v>
+        <v>129522011</v>
       </c>
       <c r="B74" t="n">
         <v>79076</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494355</v>
+        <v>494385</v>
       </c>
       <c r="R74" t="n">
-        <v>6834299</v>
+        <v>6834293</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129523011</v>
+        <v>129521838</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,37 +7982,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494480</v>
+        <v>494355</v>
       </c>
       <c r="R75" t="n">
-        <v>6834232</v>
+        <v>6834299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8056,22 +8056,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129524606</v>
+        <v>129523011</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,34 +8079,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494333</v>
+        <v>494480</v>
       </c>
       <c r="R76" t="n">
-        <v>6834609</v>
+        <v>6834232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8153,22 +8153,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524119</v>
+        <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,37 +8176,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494556</v>
+        <v>494596</v>
       </c>
       <c r="R77" t="n">
         <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,69 +8250,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129520989</v>
+        <v>129521271</v>
       </c>
       <c r="B78" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494262</v>
+        <v>494237</v>
       </c>
       <c r="R78" t="n">
-        <v>6834427</v>
+        <v>6834397</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8356,66 +8347,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129522644</v>
+        <v>129524246</v>
       </c>
       <c r="B79" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494450</v>
+        <v>494560</v>
       </c>
       <c r="R79" t="n">
-        <v>6834178</v>
+        <v>6834565</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8462,22 +8444,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129524147</v>
+        <v>129522454</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8485,37 +8467,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494596</v>
+        <v>494456</v>
       </c>
       <c r="R80" t="n">
-        <v>6834467</v>
+        <v>6834177</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8559,22 +8541,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129521271</v>
+        <v>129522450</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8582,21 +8564,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8606,10 +8588,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494237</v>
+        <v>494325</v>
       </c>
       <c r="R81" t="n">
-        <v>6834397</v>
+        <v>6834177</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8668,10 +8650,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129524246</v>
+        <v>129524119</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8679,34 +8661,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494560</v>
+        <v>494556</v>
       </c>
       <c r="R82" t="n">
-        <v>6834565</v>
+        <v>6834467</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,57 +8735,66 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522454</v>
+        <v>129520989</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494456</v>
+        <v>494262</v>
       </c>
       <c r="R83" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8862,48 +8853,57 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522450</v>
+        <v>129522644</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494325</v>
+        <v>494450</v>
       </c>
       <c r="R84" t="n">
-        <v>6834177</v>
+        <v>6834178</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8947,12 +8947,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129521936</v>
+        <v>129522147</v>
       </c>
       <c r="B88" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494342</v>
+        <v>494385</v>
       </c>
       <c r="R88" t="n">
-        <v>6834284</v>
+        <v>6834229</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521041</v>
+        <v>129521936</v>
       </c>
       <c r="B89" t="n">
         <v>79076</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494251</v>
+        <v>494342</v>
       </c>
       <c r="R89" t="n">
-        <v>6834413</v>
+        <v>6834284</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129522147</v>
+        <v>129521041</v>
       </c>
       <c r="B90" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,21 +9455,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494385</v>
+        <v>494251</v>
       </c>
       <c r="R90" t="n">
-        <v>6834229</v>
+        <v>6834413</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9735,59 +9735,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524797</v>
+        <v>129522027</v>
       </c>
       <c r="B93" t="n">
-        <v>92835</v>
+        <v>80150</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494387</v>
+        <v>494337</v>
       </c>
       <c r="R93" t="n">
-        <v>6834437</v>
+        <v>6834149</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9834,22 +9820,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129522027</v>
+        <v>129524791</v>
       </c>
       <c r="B94" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9857,34 +9843,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494337</v>
+        <v>494381</v>
       </c>
       <c r="R94" t="n">
-        <v>6834149</v>
+        <v>6834429</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9931,22 +9917,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129524791</v>
+        <v>129522173</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9954,34 +9940,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494381</v>
+        <v>494418</v>
       </c>
       <c r="R95" t="n">
-        <v>6834429</v>
+        <v>6834113</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,57 +10014,71 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129522173</v>
+        <v>129524797</v>
       </c>
       <c r="B96" t="n">
-        <v>80149</v>
+        <v>92835</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494418</v>
+        <v>494387</v>
       </c>
       <c r="R96" t="n">
-        <v>6834113</v>
+        <v>6834437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10125,12 +10125,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129522517</v>
+        <v>129524122</v>
       </c>
       <c r="B102" t="n">
-        <v>78802</v>
+        <v>80150</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,21 +10642,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494455</v>
+        <v>494556</v>
       </c>
       <c r="R102" t="n">
-        <v>6834176</v>
+        <v>6834467</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129524122</v>
+        <v>129521144</v>
       </c>
       <c r="B103" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,34 +10739,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494556</v>
+        <v>494222</v>
       </c>
       <c r="R103" t="n">
-        <v>6834467</v>
+        <v>6834390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,12 +10813,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521977</v>
+        <v>129522517</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>78802</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,21 +10933,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494334</v>
+        <v>494455</v>
       </c>
       <c r="R105" t="n">
-        <v>6834144</v>
+        <v>6834176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521967</v>
+        <v>129521977</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494346</v>
+        <v>494334</v>
       </c>
       <c r="R106" t="n">
-        <v>6834277</v>
+        <v>6834144</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,19 +11104,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521418</v>
+        <v>129521967</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -11147,14 +11147,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494176</v>
+        <v>494346</v>
       </c>
       <c r="R107" t="n">
-        <v>6834368</v>
+        <v>6834277</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,19 +11201,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521144</v>
+        <v>129521418</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -11244,14 +11244,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494222</v>
+        <v>494176</v>
       </c>
       <c r="R108" t="n">
-        <v>6834390</v>
+        <v>6834368</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11298,12 +11298,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11407,45 +11407,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129523028</v>
+        <v>129524619</v>
       </c>
       <c r="B110" t="n">
-        <v>78052</v>
+        <v>98727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494500</v>
+        <v>494338</v>
       </c>
       <c r="R110" t="n">
-        <v>6834263</v>
+        <v>6834601</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,10 +11513,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129521874</v>
+        <v>129522819</v>
       </c>
       <c r="B111" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11524,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11548,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494355</v>
+        <v>494470</v>
       </c>
       <c r="R111" t="n">
-        <v>6834295</v>
+        <v>6834231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,54 +11610,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129524619</v>
+        <v>129521874</v>
       </c>
       <c r="B112" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494338</v>
+        <v>494355</v>
       </c>
       <c r="R112" t="n">
-        <v>6834601</v>
+        <v>6834295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11707,10 +11707,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129522819</v>
+        <v>129523028</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>78052</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11718,21 +11718,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11742,10 +11742,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494470</v>
+        <v>494500</v>
       </c>
       <c r="R113" t="n">
-        <v>6834231</v>
+        <v>6834263</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129524762</v>
+        <v>129521072</v>
       </c>
       <c r="B115" t="n">
         <v>79044</v>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494406</v>
+        <v>494234</v>
       </c>
       <c r="R115" t="n">
-        <v>6834477</v>
+        <v>6834416</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11998,7 +11998,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521147</v>
+        <v>129524762</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12029,14 +12029,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494225</v>
+        <v>494406</v>
       </c>
       <c r="R116" t="n">
-        <v>6834382</v>
+        <v>6834477</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12083,19 +12083,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129521072</v>
+        <v>129521147</v>
       </c>
       <c r="B117" t="n">
         <v>79044</v>
@@ -12126,14 +12126,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494234</v>
+        <v>494225</v>
       </c>
       <c r="R117" t="n">
-        <v>6834416</v>
+        <v>6834382</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12180,22 +12180,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521663</v>
+        <v>129524747</v>
       </c>
       <c r="B118" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494242</v>
+        <v>494401</v>
       </c>
       <c r="R118" t="n">
-        <v>6834295</v>
+        <v>6834640</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129523234</v>
+        <v>129521664</v>
       </c>
       <c r="B119" t="n">
-        <v>78802</v>
+        <v>91574</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494472</v>
+        <v>494255</v>
       </c>
       <c r="R119" t="n">
-        <v>6834268</v>
+        <v>6834250</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129521664</v>
+        <v>129524381</v>
       </c>
       <c r="B120" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494255</v>
+        <v>494485</v>
       </c>
       <c r="R120" t="n">
-        <v>6834250</v>
+        <v>6834612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129524747</v>
+        <v>129521663</v>
       </c>
       <c r="B121" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494401</v>
+        <v>494242</v>
       </c>
       <c r="R121" t="n">
-        <v>6834640</v>
+        <v>6834295</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129524381</v>
+        <v>129523234</v>
       </c>
       <c r="B122" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494485</v>
+        <v>494472</v>
       </c>
       <c r="R122" t="n">
-        <v>6834612</v>
+        <v>6834268</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,22 +12665,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129523308</v>
+        <v>129522783</v>
       </c>
       <c r="B123" t="n">
-        <v>78710</v>
+        <v>79076</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,13 +12712,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494520</v>
+        <v>494456</v>
       </c>
       <c r="R123" t="n">
-        <v>6834279</v>
+        <v>6834228</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129521635</v>
+        <v>129523308</v>
       </c>
       <c r="B124" t="n">
         <v>78710</v>
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494214</v>
+        <v>494520</v>
       </c>
       <c r="R124" t="n">
-        <v>6834306</v>
+        <v>6834279</v>
       </c>
       <c r="S124" t="n">
         <v>20</v>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129522012</v>
+        <v>129521635</v>
       </c>
       <c r="B125" t="n">
-        <v>80149</v>
+        <v>78710</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,37 +12882,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494337</v>
+        <v>494214</v>
       </c>
       <c r="R125" t="n">
-        <v>6834146</v>
+        <v>6834306</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12956,12 +12956,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522783</v>
+        <v>129522012</v>
       </c>
       <c r="B131" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,34 +13464,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494456</v>
+        <v>494337</v>
       </c>
       <c r="R131" t="n">
-        <v>6834228</v>
+        <v>6834146</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13538,22 +13538,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521302</v>
+        <v>129521752</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494215</v>
+        <v>494258</v>
       </c>
       <c r="R132" t="n">
-        <v>6834362</v>
+        <v>6834310</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13744,10 +13744,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B134" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,21 +13755,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13779,13 +13779,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R134" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521403</v>
+        <v>129522065</v>
       </c>
       <c r="B135" t="n">
-        <v>90585</v>
+        <v>78710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494199</v>
+        <v>494373</v>
       </c>
       <c r="R135" t="n">
-        <v>6834366</v>
+        <v>6834247</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13938,10 +13938,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524667</v>
+        <v>129521403</v>
       </c>
       <c r="B136" t="n">
-        <v>80150</v>
+        <v>90585</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13949,43 +13949,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494352</v>
+        <v>494199</v>
       </c>
       <c r="R136" t="n">
-        <v>6834596</v>
+        <v>6834366</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14044,10 +14035,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129522065</v>
+        <v>129524667</v>
       </c>
       <c r="B137" t="n">
-        <v>78710</v>
+        <v>80150</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14055,34 +14046,43 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494373</v>
+        <v>494352</v>
       </c>
       <c r="R137" t="n">
-        <v>6834247</v>
+        <v>6834596</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2724,7 +2724,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129511911</v>
+        <v>129511985</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494614</v>
+        <v>494672</v>
       </c>
       <c r="R21" t="n">
-        <v>6834378</v>
+        <v>6834352</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129511985</v>
+        <v>129511911</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494672</v>
+        <v>494614</v>
       </c>
       <c r="R22" t="n">
-        <v>6834352</v>
+        <v>6834378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129512105</v>
+        <v>129511957</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494664</v>
+        <v>494635</v>
       </c>
       <c r="R23" t="n">
-        <v>6834295</v>
+        <v>6834347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129511957</v>
+        <v>129512105</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494635</v>
+        <v>494664</v>
       </c>
       <c r="R24" t="n">
-        <v>6834347</v>
+        <v>6834295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3403,45 +3403,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129514113</v>
+        <v>129512658</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494256</v>
+        <v>494506</v>
       </c>
       <c r="R28" t="n">
-        <v>6834732</v>
+        <v>6834042</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,45 +3500,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129512658</v>
+        <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494506</v>
+        <v>494256</v>
       </c>
       <c r="R29" t="n">
-        <v>6834042</v>
+        <v>6834732</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R40" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522417</v>
+        <v>129522021</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494442</v>
+        <v>494337</v>
       </c>
       <c r="R41" t="n">
-        <v>6834141</v>
+        <v>6834149</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129524342</v>
+        <v>129521092</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494544</v>
+        <v>494222</v>
       </c>
       <c r="R42" t="n">
-        <v>6834616</v>
+        <v>6834398</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4846,22 +4846,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129521092</v>
+        <v>129524342</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494222</v>
+        <v>494544</v>
       </c>
       <c r="R43" t="n">
-        <v>6834398</v>
+        <v>6834616</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524385</v>
+        <v>129522893</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494528</v>
+        <v>494477</v>
       </c>
       <c r="R47" t="n">
-        <v>6834660</v>
+        <v>6834229</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129522893</v>
+        <v>129524385</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494477</v>
+        <v>494528</v>
       </c>
       <c r="R48" t="n">
-        <v>6834229</v>
+        <v>6834660</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129522706</v>
+        <v>129521826</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494454</v>
+        <v>494361</v>
       </c>
       <c r="R51" t="n">
-        <v>6834225</v>
+        <v>6834336</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129522129</v>
+        <v>129520992</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,37 +5742,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494397</v>
+        <v>494221</v>
       </c>
       <c r="R52" t="n">
-        <v>6834116</v>
+        <v>6834431</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5816,19 +5816,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129520992</v>
+        <v>129521655</v>
       </c>
       <c r="B53" t="n">
         <v>78710</v>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494221</v>
+        <v>494247</v>
       </c>
       <c r="R53" t="n">
-        <v>6834431</v>
+        <v>6834296</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521655</v>
+        <v>129522706</v>
       </c>
       <c r="B54" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494247</v>
+        <v>494454</v>
       </c>
       <c r="R54" t="n">
-        <v>6834296</v>
+        <v>6834225</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6022,10 +6022,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129521826</v>
+        <v>129522129</v>
       </c>
       <c r="B55" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6033,34 +6033,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494361</v>
+        <v>494397</v>
       </c>
       <c r="R55" t="n">
-        <v>6834336</v>
+        <v>6834116</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6107,12 +6107,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6216,57 +6216,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129524059</v>
+        <v>129521656</v>
       </c>
       <c r="B57" t="n">
-        <v>98727</v>
+        <v>80150</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494582</v>
+        <v>494219</v>
       </c>
       <c r="R57" t="n">
-        <v>6834361</v>
+        <v>6834291</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6310,57 +6301,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129521358</v>
+        <v>129524059</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494221</v>
+        <v>494582</v>
       </c>
       <c r="R58" t="n">
-        <v>6834353</v>
+        <v>6834361</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6419,48 +6419,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129521131</v>
+        <v>129524392</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>92835</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494230</v>
+        <v>494486</v>
       </c>
       <c r="R59" t="n">
-        <v>6834385</v>
+        <v>6834613</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6504,19 +6504,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129522432</v>
+        <v>129521358</v>
       </c>
       <c r="B60" t="n">
         <v>79076</v>
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494325</v>
+        <v>494221</v>
       </c>
       <c r="R60" t="n">
-        <v>6834177</v>
+        <v>6834353</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6613,10 +6613,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521656</v>
+        <v>129521131</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,37 +6624,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494219</v>
+        <v>494230</v>
       </c>
       <c r="R61" t="n">
-        <v>6834291</v>
+        <v>6834385</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6698,60 +6698,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524392</v>
+        <v>129522432</v>
       </c>
       <c r="B62" t="n">
-        <v>92835</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494486</v>
+        <v>494325</v>
       </c>
       <c r="R62" t="n">
-        <v>6834613</v>
+        <v>6834177</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6795,12 +6795,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B68" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R68" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B69" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R69" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129521804</v>
+        <v>129524680</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,21 +7497,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7521,13 +7521,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494297</v>
+        <v>494357</v>
       </c>
       <c r="R70" t="n">
-        <v>6834314</v>
+        <v>6834592</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129520975</v>
+        <v>129521986</v>
       </c>
       <c r="B71" t="n">
-        <v>78801</v>
+        <v>80150</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,37 +7594,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494243</v>
+        <v>494336</v>
       </c>
       <c r="R71" t="n">
-        <v>6834445</v>
+        <v>6834146</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7668,12 +7668,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129524606</v>
+        <v>129523011</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494333</v>
+        <v>494480</v>
       </c>
       <c r="R73" t="n">
-        <v>6834609</v>
+        <v>6834232</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,22 +7862,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129522011</v>
+        <v>129524606</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,21 +7885,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494385</v>
+        <v>494333</v>
       </c>
       <c r="R74" t="n">
-        <v>6834293</v>
+        <v>6834609</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7971,7 +7971,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129521838</v>
+        <v>129522011</v>
       </c>
       <c r="B75" t="n">
         <v>79076</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494355</v>
+        <v>494385</v>
       </c>
       <c r="R75" t="n">
-        <v>6834299</v>
+        <v>6834293</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129523011</v>
+        <v>129521838</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,37 +8079,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494480</v>
+        <v>494355</v>
       </c>
       <c r="R76" t="n">
-        <v>6834232</v>
+        <v>6834299</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8153,12 +8153,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8359,45 +8359,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524246</v>
+        <v>129522644</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494560</v>
+        <v>494450</v>
       </c>
       <c r="R79" t="n">
-        <v>6834565</v>
+        <v>6834178</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8444,57 +8453,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522454</v>
+        <v>129520989</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494456</v>
+        <v>494262</v>
       </c>
       <c r="R80" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8553,7 +8571,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522450</v>
+        <v>129524246</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -8588,13 +8606,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494325</v>
+        <v>494560</v>
       </c>
       <c r="R81" t="n">
-        <v>6834177</v>
+        <v>6834565</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8650,10 +8668,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129524119</v>
+        <v>129522454</v>
       </c>
       <c r="B82" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8661,21 +8679,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8685,10 +8703,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494556</v>
+        <v>494456</v>
       </c>
       <c r="R82" t="n">
-        <v>6834467</v>
+        <v>6834177</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8747,57 +8765,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129520989</v>
+        <v>129522450</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494262</v>
+        <v>494325</v>
       </c>
       <c r="R83" t="n">
-        <v>6834427</v>
+        <v>6834177</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8841,66 +8850,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522644</v>
+        <v>129524119</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494450</v>
+        <v>494556</v>
       </c>
       <c r="R84" t="n">
-        <v>6834178</v>
+        <v>6834467</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129520902</v>
+        <v>129523899</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8970,37 +8970,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494278</v>
+        <v>494543</v>
       </c>
       <c r="R85" t="n">
-        <v>6834456</v>
+        <v>6834251</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9044,19 +9044,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129524525</v>
+        <v>129520902</v>
       </c>
       <c r="B86" t="n">
         <v>79044</v>
@@ -9087,14 +9087,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494354</v>
+        <v>494278</v>
       </c>
       <c r="R86" t="n">
-        <v>6834662</v>
+        <v>6834456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9141,22 +9141,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129523899</v>
+        <v>129524525</v>
       </c>
       <c r="B87" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9164,37 +9164,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494543</v>
+        <v>494354</v>
       </c>
       <c r="R87" t="n">
-        <v>6834251</v>
+        <v>6834662</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129521897</v>
+        <v>129522027</v>
       </c>
       <c r="B91" t="n">
-        <v>98727</v>
+        <v>80150</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494323</v>
+        <v>494337</v>
       </c>
       <c r="R91" t="n">
-        <v>6834131</v>
+        <v>6834149</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9638,45 +9638,59 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129521475</v>
+        <v>129524797</v>
       </c>
       <c r="B92" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494181</v>
+        <v>494387</v>
       </c>
       <c r="R92" t="n">
-        <v>6834367</v>
+        <v>6834437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,22 +9737,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129522027</v>
+        <v>129522173</v>
       </c>
       <c r="B93" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9746,21 +9760,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9770,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494337</v>
+        <v>494418</v>
       </c>
       <c r="R93" t="n">
-        <v>6834149</v>
+        <v>6834113</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9929,32 +9943,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129522173</v>
+        <v>129521897</v>
       </c>
       <c r="B95" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9964,10 +9978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494418</v>
+        <v>494323</v>
       </c>
       <c r="R95" t="n">
-        <v>6834113</v>
+        <v>6834131</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10026,59 +10040,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129524797</v>
+        <v>129521475</v>
       </c>
       <c r="B96" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494387</v>
+        <v>494181</v>
       </c>
       <c r="R96" t="n">
-        <v>6834437</v>
+        <v>6834367</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10125,12 +10125,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521144</v>
+        <v>129521967</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494222</v>
+        <v>494346</v>
       </c>
       <c r="R103" t="n">
-        <v>6834390</v>
+        <v>6834277</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10825,32 +10825,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129522100</v>
+        <v>129521418</v>
       </c>
       <c r="B104" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494368</v>
+        <v>494176</v>
       </c>
       <c r="R104" t="n">
-        <v>6834126</v>
+        <v>6834368</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129522517</v>
+        <v>129521144</v>
       </c>
       <c r="B105" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494455</v>
+        <v>494222</v>
       </c>
       <c r="R105" t="n">
-        <v>6834176</v>
+        <v>6834390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521977</v>
+        <v>129522341</v>
       </c>
       <c r="B106" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494334</v>
+        <v>494345</v>
       </c>
       <c r="R106" t="n">
-        <v>6834144</v>
+        <v>6834202</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521967</v>
+        <v>129521977</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,34 +11127,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494346</v>
+        <v>494334</v>
       </c>
       <c r="R107" t="n">
-        <v>6834277</v>
+        <v>6834144</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,22 +11201,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521418</v>
+        <v>129522517</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,21 +11224,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,10 +11248,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494176</v>
+        <v>494455</v>
       </c>
       <c r="R108" t="n">
-        <v>6834368</v>
+        <v>6834176</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11310,48 +11310,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522341</v>
+        <v>129522100</v>
       </c>
       <c r="B109" t="n">
-        <v>78801</v>
+        <v>58097</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494345</v>
+        <v>494368</v>
       </c>
       <c r="R109" t="n">
-        <v>6834202</v>
+        <v>6834126</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11395,66 +11395,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B110" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R110" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11513,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129522819</v>
+        <v>129523028</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>78052</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11524,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11548,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494470</v>
+        <v>494500</v>
       </c>
       <c r="R111" t="n">
-        <v>6834231</v>
+        <v>6834263</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11707,45 +11698,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129523028</v>
+        <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>78052</v>
+        <v>98727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494500</v>
+        <v>494338</v>
       </c>
       <c r="R113" t="n">
-        <v>6834263</v>
+        <v>6834601</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524240</v>
+        <v>129524762</v>
       </c>
       <c r="B114" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494559</v>
+        <v>494406</v>
       </c>
       <c r="R114" t="n">
-        <v>6834519</v>
+        <v>6834477</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521072</v>
+        <v>129521147</v>
       </c>
       <c r="B115" t="n">
         <v>79044</v>
@@ -11932,14 +11932,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494234</v>
+        <v>494225</v>
       </c>
       <c r="R115" t="n">
-        <v>6834416</v>
+        <v>6834382</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11986,19 +11986,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129524762</v>
+        <v>129521072</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12033,10 +12033,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494406</v>
+        <v>494234</v>
       </c>
       <c r="R116" t="n">
-        <v>6834477</v>
+        <v>6834416</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129521147</v>
+        <v>129524240</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,37 +12106,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494225</v>
+        <v>494559</v>
       </c>
       <c r="R117" t="n">
-        <v>6834382</v>
+        <v>6834519</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12180,12 +12180,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12289,10 +12289,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129521664</v>
+        <v>129524381</v>
       </c>
       <c r="B119" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,21 +12300,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12324,10 +12324,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494255</v>
+        <v>494485</v>
       </c>
       <c r="R119" t="n">
-        <v>6834250</v>
+        <v>6834612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12386,10 +12386,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129524381</v>
+        <v>129521664</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494485</v>
+        <v>494255</v>
       </c>
       <c r="R120" t="n">
-        <v>6834612</v>
+        <v>6834250</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13259,7 +13259,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129524581</v>
+        <v>129522012</v>
       </c>
       <c r="B129" t="n">
         <v>80149</v>
@@ -13290,14 +13290,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494323</v>
+        <v>494337</v>
       </c>
       <c r="R129" t="n">
-        <v>6834627</v>
+        <v>6834146</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13344,22 +13344,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129522736</v>
+        <v>129524581</v>
       </c>
       <c r="B130" t="n">
-        <v>91574</v>
+        <v>80149</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494443</v>
+        <v>494323</v>
       </c>
       <c r="R130" t="n">
-        <v>6834230</v>
+        <v>6834627</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522012</v>
+        <v>129522736</v>
       </c>
       <c r="B131" t="n">
-        <v>80149</v>
+        <v>91574</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,34 +13464,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494337</v>
+        <v>494443</v>
       </c>
       <c r="R131" t="n">
-        <v>6834146</v>
+        <v>6834230</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13538,12 +13538,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129520912</v>
+        <v>129521302</v>
       </c>
       <c r="B133" t="n">
         <v>79044</v>
@@ -13678,17 +13678,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494290</v>
+        <v>494215</v>
       </c>
       <c r="R133" t="n">
-        <v>6834454</v>
+        <v>6834362</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13732,19 +13732,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521302</v>
+        <v>129520912</v>
       </c>
       <c r="B134" t="n">
         <v>79044</v>
@@ -13775,17 +13775,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494215</v>
+        <v>494290</v>
       </c>
       <c r="R134" t="n">
-        <v>6834362</v>
+        <v>6834454</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13829,57 +13829,57 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129522065</v>
+        <v>129521085</v>
       </c>
       <c r="B135" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494373</v>
+        <v>494228</v>
       </c>
       <c r="R135" t="n">
-        <v>6834247</v>
+        <v>6834405</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14141,45 +14141,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129521085</v>
+        <v>129522065</v>
       </c>
       <c r="B138" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494228</v>
+        <v>494373</v>
       </c>
       <c r="R138" t="n">
-        <v>6834405</v>
+        <v>6834247</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14226,12 +14226,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513963</v>
+        <v>129513412</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494311</v>
+        <v>494427</v>
       </c>
       <c r="R16" t="n">
-        <v>6834701</v>
+        <v>6834434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129513412</v>
+        <v>129513963</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2367,14 +2367,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494427</v>
+        <v>494311</v>
       </c>
       <c r="R17" t="n">
-        <v>6834434</v>
+        <v>6834701</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522417</v>
+        <v>129522021</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494442</v>
+        <v>494337</v>
       </c>
       <c r="R40" t="n">
-        <v>6834141</v>
+        <v>6834149</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R41" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129524595</v>
+        <v>129522893</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494349</v>
+        <v>494477</v>
       </c>
       <c r="R46" t="n">
-        <v>6834611</v>
+        <v>6834229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129522893</v>
+        <v>129524595</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494477</v>
+        <v>494349</v>
       </c>
       <c r="R47" t="n">
-        <v>6834229</v>
+        <v>6834611</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129521826</v>
+        <v>129520992</v>
       </c>
       <c r="B51" t="n">
-        <v>80150</v>
+        <v>78710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494361</v>
+        <v>494221</v>
       </c>
       <c r="R51" t="n">
-        <v>6834336</v>
+        <v>6834431</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129520992</v>
+        <v>129521655</v>
       </c>
       <c r="B52" t="n">
         <v>78710</v>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494221</v>
+        <v>494247</v>
       </c>
       <c r="R52" t="n">
-        <v>6834431</v>
+        <v>6834296</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521655</v>
+        <v>129521826</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>80150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5839,21 +5839,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494247</v>
+        <v>494361</v>
       </c>
       <c r="R53" t="n">
-        <v>6834296</v>
+        <v>6834336</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,32 +5925,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522706</v>
+        <v>129521887</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,13 +5960,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494454</v>
+        <v>494350</v>
       </c>
       <c r="R54" t="n">
-        <v>6834225</v>
+        <v>6834298</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522129</v>
+        <v>129522706</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6053,17 +6053,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494397</v>
+        <v>494454</v>
       </c>
       <c r="R55" t="n">
-        <v>6834116</v>
+        <v>6834225</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6107,57 +6107,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521887</v>
+        <v>129522129</v>
       </c>
       <c r="B56" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494350</v>
+        <v>494397</v>
       </c>
       <c r="R56" t="n">
-        <v>6834298</v>
+        <v>6834116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,22 +6204,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521656</v>
+        <v>129521358</v>
       </c>
       <c r="B57" t="n">
-        <v>80150</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,37 +6227,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494219</v>
+        <v>494221</v>
       </c>
       <c r="R57" t="n">
-        <v>6834291</v>
+        <v>6834353</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6301,69 +6301,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129524059</v>
+        <v>129521131</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494582</v>
+        <v>494230</v>
       </c>
       <c r="R58" t="n">
-        <v>6834361</v>
+        <v>6834385</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6419,48 +6410,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129524392</v>
+        <v>129522432</v>
       </c>
       <c r="B59" t="n">
-        <v>92835</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494486</v>
+        <v>494325</v>
       </c>
       <c r="R59" t="n">
-        <v>6834613</v>
+        <v>6834177</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6504,22 +6495,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129521358</v>
+        <v>129521656</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6527,37 +6518,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494221</v>
+        <v>494219</v>
       </c>
       <c r="R60" t="n">
-        <v>6834353</v>
+        <v>6834291</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6601,60 +6592,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521131</v>
+        <v>129524392</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>92835</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494230</v>
+        <v>494486</v>
       </c>
       <c r="R61" t="n">
-        <v>6834385</v>
+        <v>6834613</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6698,22 +6689,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129522432</v>
+        <v>129524189</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6712,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,10 +6736,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494325</v>
+        <v>494606</v>
       </c>
       <c r="R62" t="n">
-        <v>6834177</v>
+        <v>6834497</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6904,7 +6895,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524189</v>
+        <v>129522857</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6939,13 +6930,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494606</v>
+        <v>494475</v>
       </c>
       <c r="R64" t="n">
-        <v>6834497</v>
+        <v>6834232</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7001,7 +6992,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129522857</v>
+        <v>129524775</v>
       </c>
       <c r="B65" t="n">
         <v>79044</v>
@@ -7036,10 +7027,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494475</v>
+        <v>494416</v>
       </c>
       <c r="R65" t="n">
-        <v>6834232</v>
+        <v>6834464</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7098,45 +7089,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129524775</v>
+        <v>129524059</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494416</v>
+        <v>494582</v>
       </c>
       <c r="R66" t="n">
-        <v>6834464</v>
+        <v>6834361</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521804</v>
+        <v>129521986</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494297</v>
+        <v>494336</v>
       </c>
       <c r="R68" t="n">
-        <v>6834314</v>
+        <v>6834146</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129520975</v>
+        <v>129524680</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>80149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494243</v>
+        <v>494357</v>
       </c>
       <c r="R69" t="n">
-        <v>6834445</v>
+        <v>6834592</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B70" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,21 +7497,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7521,13 +7521,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R70" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B71" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,37 +7594,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R71" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7668,12 +7668,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129524606</v>
+        <v>129522011</v>
       </c>
       <c r="B74" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,21 +7885,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494333</v>
+        <v>494385</v>
       </c>
       <c r="R74" t="n">
-        <v>6834609</v>
+        <v>6834293</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7971,7 +7971,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129522011</v>
+        <v>129521838</v>
       </c>
       <c r="B75" t="n">
         <v>79076</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494385</v>
+        <v>494355</v>
       </c>
       <c r="R75" t="n">
-        <v>6834293</v>
+        <v>6834299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129521838</v>
+        <v>129524606</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,21 +8079,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8103,13 +8103,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494355</v>
+        <v>494333</v>
       </c>
       <c r="R76" t="n">
-        <v>6834299</v>
+        <v>6834609</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8165,10 +8165,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524147</v>
+        <v>129524119</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,37 +8176,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494596</v>
+        <v>494556</v>
       </c>
       <c r="R77" t="n">
         <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,19 +8250,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129521271</v>
+        <v>129524147</v>
       </c>
       <c r="B78" t="n">
         <v>79076</v>
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494237</v>
+        <v>494596</v>
       </c>
       <c r="R78" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8359,57 +8359,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129522644</v>
+        <v>129521271</v>
       </c>
       <c r="B79" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494450</v>
+        <v>494237</v>
       </c>
       <c r="R79" t="n">
-        <v>6834178</v>
+        <v>6834397</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8453,66 +8444,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129520989</v>
+        <v>129524246</v>
       </c>
       <c r="B80" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494262</v>
+        <v>494560</v>
       </c>
       <c r="R80" t="n">
-        <v>6834427</v>
+        <v>6834565</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8559,19 +8541,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129524246</v>
+        <v>129522454</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -8602,14 +8584,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494560</v>
+        <v>494456</v>
       </c>
       <c r="R81" t="n">
-        <v>6834565</v>
+        <v>6834177</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8656,19 +8638,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -8699,17 +8681,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R82" t="n">
         <v>6834177</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8753,60 +8735,69 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522450</v>
+        <v>129520989</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494325</v>
+        <v>494262</v>
       </c>
       <c r="R83" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8850,57 +8841,66 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129524119</v>
+        <v>129522644</v>
       </c>
       <c r="B84" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494556</v>
+        <v>494450</v>
       </c>
       <c r="R84" t="n">
-        <v>6834467</v>
+        <v>6834178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129523899</v>
+        <v>129520902</v>
       </c>
       <c r="B85" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8970,37 +8970,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494543</v>
+        <v>494278</v>
       </c>
       <c r="R85" t="n">
-        <v>6834251</v>
+        <v>6834456</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9044,19 +9044,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129520902</v>
+        <v>129524525</v>
       </c>
       <c r="B86" t="n">
         <v>79044</v>
@@ -9087,14 +9087,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494278</v>
+        <v>494354</v>
       </c>
       <c r="R86" t="n">
-        <v>6834456</v>
+        <v>6834662</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9141,22 +9141,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129524525</v>
+        <v>129523899</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9164,37 +9164,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494354</v>
+        <v>494543</v>
       </c>
       <c r="R87" t="n">
-        <v>6834662</v>
+        <v>6834251</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129522147</v>
+        <v>129521936</v>
       </c>
       <c r="B88" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494385</v>
+        <v>494342</v>
       </c>
       <c r="R88" t="n">
-        <v>6834229</v>
+        <v>6834284</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521936</v>
+        <v>129521041</v>
       </c>
       <c r="B89" t="n">
         <v>79076</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494342</v>
+        <v>494251</v>
       </c>
       <c r="R89" t="n">
-        <v>6834284</v>
+        <v>6834413</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129521041</v>
+        <v>129522147</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>78802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,21 +9455,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494251</v>
+        <v>494385</v>
       </c>
       <c r="R90" t="n">
-        <v>6834413</v>
+        <v>6834229</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9541,45 +9541,59 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522027</v>
+        <v>129524797</v>
       </c>
       <c r="B91" t="n">
-        <v>80150</v>
+        <v>92835</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494337</v>
+        <v>494387</v>
       </c>
       <c r="R91" t="n">
-        <v>6834149</v>
+        <v>6834437</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,71 +9640,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524797</v>
+        <v>129522027</v>
       </c>
       <c r="B92" t="n">
-        <v>92835</v>
+        <v>80150</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494387</v>
+        <v>494337</v>
       </c>
       <c r="R92" t="n">
-        <v>6834437</v>
+        <v>6834149</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9737,12 +9737,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10137,48 +10137,57 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129524273</v>
+        <v>129522632</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494549</v>
+        <v>494455</v>
       </c>
       <c r="R97" t="n">
-        <v>6834588</v>
+        <v>6834185</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10222,22 +10231,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524130</v>
+        <v>129524273</v>
       </c>
       <c r="B98" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10245,37 +10254,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494537</v>
+        <v>494549</v>
       </c>
       <c r="R98" t="n">
-        <v>6834492</v>
+        <v>6834588</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10319,12 +10328,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10525,54 +10534,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129522632</v>
+        <v>129524130</v>
       </c>
       <c r="B101" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494455</v>
+        <v>494537</v>
       </c>
       <c r="R101" t="n">
-        <v>6834185</v>
+        <v>6834492</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129524122</v>
+        <v>129521967</v>
       </c>
       <c r="B102" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494556</v>
+        <v>494346</v>
       </c>
       <c r="R102" t="n">
-        <v>6834467</v>
+        <v>6834277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,19 +10716,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521967</v>
+        <v>129521418</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -10759,14 +10759,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494346</v>
+        <v>494176</v>
       </c>
       <c r="R103" t="n">
-        <v>6834277</v>
+        <v>6834368</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,19 +10813,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521418</v>
+        <v>129521144</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -10856,14 +10856,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494176</v>
+        <v>494222</v>
       </c>
       <c r="R104" t="n">
-        <v>6834368</v>
+        <v>6834390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521144</v>
+        <v>129522341</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,21 +10933,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494222</v>
+        <v>494345</v>
       </c>
       <c r="R105" t="n">
-        <v>6834390</v>
+        <v>6834202</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129522341</v>
+        <v>129522517</v>
       </c>
       <c r="B106" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494345</v>
+        <v>494455</v>
       </c>
       <c r="R106" t="n">
-        <v>6834202</v>
+        <v>6834176</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521977</v>
+        <v>129524122</v>
       </c>
       <c r="B107" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494334</v>
+        <v>494556</v>
       </c>
       <c r="R107" t="n">
-        <v>6834144</v>
+        <v>6834467</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522517</v>
+        <v>129521977</v>
       </c>
       <c r="B108" t="n">
-        <v>78802</v>
+        <v>80149</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,21 +11224,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,10 +11248,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494455</v>
+        <v>494334</v>
       </c>
       <c r="R108" t="n">
-        <v>6834176</v>
+        <v>6834144</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11407,10 +11407,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129522819</v>
+        <v>129523028</v>
       </c>
       <c r="B110" t="n">
-        <v>79044</v>
+        <v>78052</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11418,21 +11418,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494470</v>
+        <v>494500</v>
       </c>
       <c r="R110" t="n">
-        <v>6834231</v>
+        <v>6834263</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129523028</v>
+        <v>129521874</v>
       </c>
       <c r="B111" t="n">
-        <v>78052</v>
+        <v>80149</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494500</v>
+        <v>494355</v>
       </c>
       <c r="R111" t="n">
-        <v>6834263</v>
+        <v>6834295</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129521874</v>
+        <v>129522819</v>
       </c>
       <c r="B112" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494355</v>
+        <v>494470</v>
       </c>
       <c r="R112" t="n">
-        <v>6834295</v>
+        <v>6834231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524762</v>
+        <v>129524240</v>
       </c>
       <c r="B114" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494406</v>
+        <v>494559</v>
       </c>
       <c r="R114" t="n">
-        <v>6834477</v>
+        <v>6834519</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521072</v>
+        <v>129524762</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12033,10 +12033,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494234</v>
+        <v>494406</v>
       </c>
       <c r="R116" t="n">
-        <v>6834416</v>
+        <v>6834477</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129524240</v>
+        <v>129521072</v>
       </c>
       <c r="B117" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12130,13 +12130,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494559</v>
+        <v>494234</v>
       </c>
       <c r="R117" t="n">
-        <v>6834519</v>
+        <v>6834416</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129524747</v>
+        <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494401</v>
+        <v>494255</v>
       </c>
       <c r="R118" t="n">
-        <v>6834640</v>
+        <v>6834250</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12289,7 +12289,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524381</v>
+        <v>129524747</v>
       </c>
       <c r="B119" t="n">
         <v>79044</v>
@@ -12320,14 +12320,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494485</v>
+        <v>494401</v>
       </c>
       <c r="R119" t="n">
-        <v>6834612</v>
+        <v>6834640</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12386,10 +12386,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129521664</v>
+        <v>129524381</v>
       </c>
       <c r="B120" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494255</v>
+        <v>494485</v>
       </c>
       <c r="R120" t="n">
-        <v>6834250</v>
+        <v>6834612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129523308</v>
+        <v>129522903</v>
       </c>
       <c r="B124" t="n">
-        <v>78710</v>
+        <v>79044</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494520</v>
+        <v>494466</v>
       </c>
       <c r="R124" t="n">
-        <v>6834279</v>
+        <v>6834211</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129521635</v>
+        <v>129522736</v>
       </c>
       <c r="B125" t="n">
-        <v>78710</v>
+        <v>91574</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,13 +12906,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494214</v>
+        <v>494443</v>
       </c>
       <c r="R125" t="n">
-        <v>6834306</v>
+        <v>6834230</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521002</v>
+        <v>129522012</v>
       </c>
       <c r="B126" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,34 +12979,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494241</v>
+        <v>494337</v>
       </c>
       <c r="R126" t="n">
-        <v>6834425</v>
+        <v>6834146</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13053,22 +13053,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522903</v>
+        <v>129524581</v>
       </c>
       <c r="B127" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494466</v>
+        <v>494323</v>
       </c>
       <c r="R127" t="n">
-        <v>6834211</v>
+        <v>6834627</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129521823</v>
+        <v>129521002</v>
       </c>
       <c r="B128" t="n">
         <v>79044</v>
@@ -13193,17 +13193,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494360</v>
+        <v>494241</v>
       </c>
       <c r="R128" t="n">
-        <v>6834206</v>
+        <v>6834425</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13247,22 +13247,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129522012</v>
+        <v>129521823</v>
       </c>
       <c r="B129" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13294,13 +13294,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494337</v>
+        <v>494360</v>
       </c>
       <c r="R129" t="n">
-        <v>6834146</v>
+        <v>6834206</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13356,10 +13356,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129524581</v>
+        <v>129523308</v>
       </c>
       <c r="B130" t="n">
-        <v>80149</v>
+        <v>78710</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13391,13 +13391,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494323</v>
+        <v>494520</v>
       </c>
       <c r="R130" t="n">
-        <v>6834627</v>
+        <v>6834279</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522736</v>
+        <v>129521635</v>
       </c>
       <c r="B131" t="n">
-        <v>91574</v>
+        <v>78710</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,13 +13488,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494443</v>
+        <v>494214</v>
       </c>
       <c r="R131" t="n">
-        <v>6834230</v>
+        <v>6834306</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13841,45 +13841,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521085</v>
+        <v>129522065</v>
       </c>
       <c r="B135" t="n">
-        <v>98727</v>
+        <v>78710</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494228</v>
+        <v>494373</v>
       </c>
       <c r="R135" t="n">
-        <v>6834405</v>
+        <v>6834247</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14141,45 +14141,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129522065</v>
+        <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>78710</v>
+        <v>98727</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494373</v>
+        <v>494228</v>
       </c>
       <c r="R138" t="n">
-        <v>6834247</v>
+        <v>6834405</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14226,12 +14226,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513412</v>
+        <v>129513963</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494427</v>
+        <v>494311</v>
       </c>
       <c r="R16" t="n">
-        <v>6834434</v>
+        <v>6834701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129513963</v>
+        <v>129513412</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2367,14 +2367,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494311</v>
+        <v>494427</v>
       </c>
       <c r="R17" t="n">
-        <v>6834701</v>
+        <v>6834434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R31" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R32" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129513342</v>
+        <v>129512470</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494384</v>
+        <v>494652</v>
       </c>
       <c r="R34" t="n">
-        <v>6834354</v>
+        <v>6833984</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129512771</v>
+        <v>129513342</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494466</v>
+        <v>494384</v>
       </c>
       <c r="R35" t="n">
-        <v>6833989</v>
+        <v>6834354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129512470</v>
+        <v>129512771</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494652</v>
+        <v>494466</v>
       </c>
       <c r="R36" t="n">
-        <v>6833984</v>
+        <v>6833989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R39" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R40" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522417</v>
+        <v>129520952</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494442</v>
+        <v>494291</v>
       </c>
       <c r="R41" t="n">
-        <v>6834141</v>
+        <v>6834454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129521092</v>
+        <v>129524342</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494222</v>
+        <v>494544</v>
       </c>
       <c r="R42" t="n">
-        <v>6834398</v>
+        <v>6834616</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4846,22 +4846,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129524342</v>
+        <v>129521092</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494544</v>
+        <v>494222</v>
       </c>
       <c r="R43" t="n">
-        <v>6834616</v>
+        <v>6834398</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129522893</v>
+        <v>129524595</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494477</v>
+        <v>494349</v>
       </c>
       <c r="R46" t="n">
-        <v>6834229</v>
+        <v>6834611</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524595</v>
+        <v>129524385</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494349</v>
+        <v>494528</v>
       </c>
       <c r="R47" t="n">
-        <v>6834611</v>
+        <v>6834660</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129524385</v>
+        <v>129522256</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494528</v>
+        <v>494384</v>
       </c>
       <c r="R48" t="n">
-        <v>6834660</v>
+        <v>6834211</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129522256</v>
+        <v>129521425</v>
       </c>
       <c r="B49" t="n">
         <v>78802</v>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494384</v>
+        <v>494187</v>
       </c>
       <c r="R49" t="n">
-        <v>6834211</v>
+        <v>6834373</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129521425</v>
+        <v>129522893</v>
       </c>
       <c r="B50" t="n">
-        <v>78802</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494187</v>
+        <v>494477</v>
       </c>
       <c r="R50" t="n">
-        <v>6834373</v>
+        <v>6834229</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6216,10 +6216,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521358</v>
+        <v>129522857</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,21 +6227,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494221</v>
+        <v>494475</v>
       </c>
       <c r="R57" t="n">
-        <v>6834353</v>
+        <v>6834232</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129521131</v>
+        <v>129521656</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>80150</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,37 +6324,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494230</v>
+        <v>494219</v>
       </c>
       <c r="R58" t="n">
-        <v>6834385</v>
+        <v>6834291</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6398,19 +6398,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522432</v>
+        <v>129521358</v>
       </c>
       <c r="B59" t="n">
         <v>79076</v>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494325</v>
+        <v>494221</v>
       </c>
       <c r="R59" t="n">
-        <v>6834177</v>
+        <v>6834353</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129521656</v>
+        <v>129521131</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6518,37 +6518,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494219</v>
+        <v>494230</v>
       </c>
       <c r="R60" t="n">
-        <v>6834291</v>
+        <v>6834385</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6592,60 +6592,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129524392</v>
+        <v>129522432</v>
       </c>
       <c r="B61" t="n">
-        <v>92835</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494486</v>
+        <v>494325</v>
       </c>
       <c r="R61" t="n">
-        <v>6834613</v>
+        <v>6834177</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6689,60 +6689,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524189</v>
+        <v>129524392</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494606</v>
+        <v>494486</v>
       </c>
       <c r="R62" t="n">
-        <v>6834497</v>
+        <v>6834613</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6786,12 +6786,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129522857</v>
+        <v>129524189</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6930,13 +6930,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494475</v>
+        <v>494606</v>
       </c>
       <c r="R64" t="n">
-        <v>6834232</v>
+        <v>6834497</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521986</v>
+        <v>129524680</v>
       </c>
       <c r="B68" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,34 +7303,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494336</v>
+        <v>494357</v>
       </c>
       <c r="R68" t="n">
-        <v>6834146</v>
+        <v>6834592</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B69" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R69" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129520975</v>
+        <v>129521986</v>
       </c>
       <c r="B70" t="n">
-        <v>78801</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,37 +7497,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494243</v>
+        <v>494336</v>
       </c>
       <c r="R70" t="n">
-        <v>6834445</v>
+        <v>6834146</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,60 +7571,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129521804</v>
+        <v>129522294</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494297</v>
+        <v>494419</v>
       </c>
       <c r="R71" t="n">
-        <v>6834314</v>
+        <v>6834113</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7668,60 +7668,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129522294</v>
+        <v>129521804</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494419</v>
+        <v>494297</v>
       </c>
       <c r="R72" t="n">
-        <v>6834113</v>
+        <v>6834314</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7765,22 +7765,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129523011</v>
+        <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494480</v>
+        <v>494385</v>
       </c>
       <c r="R73" t="n">
-        <v>6834232</v>
+        <v>6834293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,19 +7862,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129522011</v>
+        <v>129521838</v>
       </c>
       <c r="B74" t="n">
         <v>79076</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494385</v>
+        <v>494355</v>
       </c>
       <c r="R74" t="n">
-        <v>6834293</v>
+        <v>6834299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129521838</v>
+        <v>129524606</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494355</v>
+        <v>494333</v>
       </c>
       <c r="R75" t="n">
-        <v>6834299</v>
+        <v>6834609</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129524606</v>
+        <v>129523011</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,34 +8079,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494333</v>
+        <v>494480</v>
       </c>
       <c r="R76" t="n">
-        <v>6834609</v>
+        <v>6834232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8153,22 +8153,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524119</v>
+        <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,37 +8176,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494556</v>
+        <v>494596</v>
       </c>
       <c r="R77" t="n">
         <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,19 +8250,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129524147</v>
+        <v>129521271</v>
       </c>
       <c r="B78" t="n">
         <v>79076</v>
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494596</v>
+        <v>494237</v>
       </c>
       <c r="R78" t="n">
-        <v>6834467</v>
+        <v>6834397</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129521271</v>
+        <v>129524119</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,37 +8370,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494237</v>
+        <v>494556</v>
       </c>
       <c r="R79" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8444,12 +8444,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8747,7 +8747,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129520989</v>
+        <v>129522644</v>
       </c>
       <c r="B83" t="n">
         <v>98727</v>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8791,10 +8791,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494262</v>
+        <v>494450</v>
       </c>
       <c r="R83" t="n">
-        <v>6834427</v>
+        <v>6834178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8853,7 +8853,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522644</v>
+        <v>129520989</v>
       </c>
       <c r="B84" t="n">
         <v>98727</v>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494450</v>
+        <v>494262</v>
       </c>
       <c r="R84" t="n">
-        <v>6834178</v>
+        <v>6834427</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9541,59 +9541,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129524797</v>
+        <v>129522027</v>
       </c>
       <c r="B91" t="n">
-        <v>92835</v>
+        <v>80150</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494387</v>
+        <v>494337</v>
       </c>
       <c r="R91" t="n">
-        <v>6834437</v>
+        <v>6834149</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9640,57 +9626,71 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129522027</v>
+        <v>129524797</v>
       </c>
       <c r="B92" t="n">
-        <v>80150</v>
+        <v>92835</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494337</v>
+        <v>494387</v>
       </c>
       <c r="R92" t="n">
-        <v>6834149</v>
+        <v>6834437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9737,22 +9737,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129522173</v>
+        <v>129524791</v>
       </c>
       <c r="B93" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9760,34 +9760,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494418</v>
+        <v>494381</v>
       </c>
       <c r="R93" t="n">
-        <v>6834113</v>
+        <v>6834429</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9834,57 +9834,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129524791</v>
+        <v>129521897</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494381</v>
+        <v>494323</v>
       </c>
       <c r="R94" t="n">
-        <v>6834429</v>
+        <v>6834131</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9931,44 +9931,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521897</v>
+        <v>129521475</v>
       </c>
       <c r="B95" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494323</v>
+        <v>494181</v>
       </c>
       <c r="R95" t="n">
-        <v>6834131</v>
+        <v>6834367</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10040,10 +10040,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521475</v>
+        <v>129522173</v>
       </c>
       <c r="B96" t="n">
-        <v>78802</v>
+        <v>80149</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494181</v>
+        <v>494418</v>
       </c>
       <c r="R96" t="n">
-        <v>6834367</v>
+        <v>6834113</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10137,57 +10137,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129522632</v>
+        <v>129524273</v>
       </c>
       <c r="B97" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494455</v>
+        <v>494549</v>
       </c>
       <c r="R97" t="n">
-        <v>6834185</v>
+        <v>6834588</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10231,22 +10222,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524273</v>
+        <v>129524130</v>
       </c>
       <c r="B98" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10254,37 +10245,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494549</v>
+        <v>494537</v>
       </c>
       <c r="R98" t="n">
-        <v>6834588</v>
+        <v>6834492</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10328,12 +10319,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10534,45 +10525,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129524130</v>
+        <v>129522632</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494537</v>
+        <v>494455</v>
       </c>
       <c r="R101" t="n">
-        <v>6834492</v>
+        <v>6834185</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129521967</v>
+        <v>129524122</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494346</v>
+        <v>494556</v>
       </c>
       <c r="R102" t="n">
-        <v>6834277</v>
+        <v>6834467</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,22 +10716,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521418</v>
+        <v>129521977</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,21 +10739,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494176</v>
+        <v>494334</v>
       </c>
       <c r="R103" t="n">
-        <v>6834368</v>
+        <v>6834144</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521144</v>
+        <v>129522341</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,21 +10836,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10860,10 +10860,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494222</v>
+        <v>494345</v>
       </c>
       <c r="R104" t="n">
-        <v>6834390</v>
+        <v>6834202</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129522341</v>
+        <v>129522517</v>
       </c>
       <c r="B105" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494345</v>
+        <v>494455</v>
       </c>
       <c r="R105" t="n">
-        <v>6834202</v>
+        <v>6834176</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129522517</v>
+        <v>129521967</v>
       </c>
       <c r="B106" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494455</v>
+        <v>494346</v>
       </c>
       <c r="R106" t="n">
-        <v>6834176</v>
+        <v>6834277</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129524122</v>
+        <v>129521418</v>
       </c>
       <c r="B107" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494556</v>
+        <v>494176</v>
       </c>
       <c r="R107" t="n">
-        <v>6834467</v>
+        <v>6834368</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521977</v>
+        <v>129521144</v>
       </c>
       <c r="B108" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,34 +11224,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494334</v>
+        <v>494222</v>
       </c>
       <c r="R108" t="n">
-        <v>6834144</v>
+        <v>6834390</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11298,12 +11298,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11601,45 +11601,54 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129522819</v>
+        <v>129524619</v>
       </c>
       <c r="B112" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494470</v>
+        <v>494338</v>
       </c>
       <c r="R112" t="n">
-        <v>6834231</v>
+        <v>6834601</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11698,54 +11707,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B113" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R113" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521147</v>
+        <v>129524762</v>
       </c>
       <c r="B115" t="n">
         <v>79044</v>
@@ -11932,14 +11932,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494225</v>
+        <v>494406</v>
       </c>
       <c r="R115" t="n">
-        <v>6834382</v>
+        <v>6834477</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11986,19 +11986,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129524762</v>
+        <v>129521147</v>
       </c>
       <c r="B116" t="n">
         <v>79044</v>
@@ -12029,14 +12029,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494406</v>
+        <v>494225</v>
       </c>
       <c r="R116" t="n">
-        <v>6834477</v>
+        <v>6834382</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12083,12 +12083,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522783</v>
+        <v>129522736</v>
       </c>
       <c r="B123" t="n">
-        <v>79076</v>
+        <v>91574</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494456</v>
+        <v>494443</v>
       </c>
       <c r="R123" t="n">
-        <v>6834228</v>
+        <v>6834230</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522903</v>
+        <v>129522012</v>
       </c>
       <c r="B124" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,34 +12785,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494466</v>
+        <v>494337</v>
       </c>
       <c r="R124" t="n">
-        <v>6834211</v>
+        <v>6834146</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12859,22 +12859,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129522736</v>
+        <v>129524581</v>
       </c>
       <c r="B125" t="n">
-        <v>91574</v>
+        <v>80149</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494443</v>
+        <v>494323</v>
       </c>
       <c r="R125" t="n">
-        <v>6834230</v>
+        <v>6834627</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129522012</v>
+        <v>129521002</v>
       </c>
       <c r="B126" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,34 +12979,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494337</v>
+        <v>494241</v>
       </c>
       <c r="R126" t="n">
-        <v>6834146</v>
+        <v>6834425</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13053,22 +13053,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129524581</v>
+        <v>129522903</v>
       </c>
       <c r="B127" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494323</v>
+        <v>494466</v>
       </c>
       <c r="R127" t="n">
-        <v>6834627</v>
+        <v>6834211</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129521002</v>
+        <v>129521823</v>
       </c>
       <c r="B128" t="n">
         <v>79044</v>
@@ -13193,17 +13193,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494241</v>
+        <v>494360</v>
       </c>
       <c r="R128" t="n">
-        <v>6834425</v>
+        <v>6834206</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13247,22 +13247,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129521823</v>
+        <v>129522783</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,37 +13270,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494360</v>
+        <v>494456</v>
       </c>
       <c r="R129" t="n">
-        <v>6834206</v>
+        <v>6834228</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13344,12 +13344,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129522065</v>
+        <v>129521403</v>
       </c>
       <c r="B135" t="n">
-        <v>78710</v>
+        <v>90585</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494373</v>
+        <v>494199</v>
       </c>
       <c r="R135" t="n">
-        <v>6834247</v>
+        <v>6834366</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13938,10 +13938,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129521403</v>
+        <v>129524667</v>
       </c>
       <c r="B136" t="n">
-        <v>90585</v>
+        <v>80150</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13949,34 +13949,43 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494199</v>
+        <v>494352</v>
       </c>
       <c r="R136" t="n">
-        <v>6834366</v>
+        <v>6834596</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14035,10 +14044,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524667</v>
+        <v>129522065</v>
       </c>
       <c r="B137" t="n">
-        <v>80150</v>
+        <v>78710</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14046,43 +14055,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494352</v>
+        <v>494373</v>
       </c>
       <c r="R137" t="n">
-        <v>6834596</v>
+        <v>6834247</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1739,7 +1739,7 @@
         <v>129476557</v>
       </c>
       <c r="B11" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>129512476</v>
       </c>
       <c r="B14" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>129512298</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>129513963</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>129513412</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>129512195</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129512125</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>129513122</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>129511985</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>129511911</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>129511957</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>129512105</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>129512361</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>129512918</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>129511943</v>
       </c>
       <c r="B27" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>129512658</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>129513370</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>129512549</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129512676</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>129513741</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129512470</v>
+        <v>129513342</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494652</v>
+        <v>494384</v>
       </c>
       <c r="R34" t="n">
-        <v>6833984</v>
+        <v>6834354</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129513342</v>
+        <v>129512771</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494384</v>
+        <v>494466</v>
       </c>
       <c r="R35" t="n">
-        <v>6834354</v>
+        <v>6833989</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129512771</v>
+        <v>129512470</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494466</v>
+        <v>494652</v>
       </c>
       <c r="R36" t="n">
-        <v>6833989</v>
+        <v>6833984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
         <v>129512788</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129512556</v>
       </c>
       <c r="B38" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129522021</v>
+        <v>129520952</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494337</v>
+        <v>494291</v>
       </c>
       <c r="R39" t="n">
-        <v>6834149</v>
+        <v>6834454</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522417</v>
+        <v>129522021</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>57890</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494442</v>
+        <v>494337</v>
       </c>
       <c r="R40" t="n">
-        <v>6834141</v>
+        <v>6834149</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129520952</v>
+        <v>129522417</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494291</v>
+        <v>494442</v>
       </c>
       <c r="R41" t="n">
-        <v>6834454</v>
+        <v>6834141</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,7 +4764,7 @@
         <v>129524342</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129521092</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>129524785</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>129524779</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129524595</v>
+        <v>129522893</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>79102</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494349</v>
+        <v>494477</v>
       </c>
       <c r="R46" t="n">
-        <v>6834611</v>
+        <v>6834229</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524385</v>
+        <v>129522256</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494528</v>
+        <v>494384</v>
       </c>
       <c r="R47" t="n">
-        <v>6834660</v>
+        <v>6834211</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129522256</v>
+        <v>129521425</v>
       </c>
       <c r="B48" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494384</v>
+        <v>494187</v>
       </c>
       <c r="R48" t="n">
-        <v>6834211</v>
+        <v>6834373</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129521425</v>
+        <v>129524595</v>
       </c>
       <c r="B49" t="n">
-        <v>78802</v>
+        <v>80175</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494187</v>
+        <v>494349</v>
       </c>
       <c r="R49" t="n">
-        <v>6834373</v>
+        <v>6834611</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129522893</v>
+        <v>129524385</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494477</v>
+        <v>494528</v>
       </c>
       <c r="R50" t="n">
-        <v>6834229</v>
+        <v>6834660</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129520992</v>
+        <v>129521826</v>
       </c>
       <c r="B51" t="n">
-        <v>78710</v>
+        <v>80176</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494221</v>
+        <v>494361</v>
       </c>
       <c r="R51" t="n">
-        <v>6834431</v>
+        <v>6834336</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,32 +5731,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521655</v>
+        <v>129521887</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>80204</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494247</v>
+        <v>494350</v>
       </c>
       <c r="R52" t="n">
-        <v>6834296</v>
+        <v>6834298</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521826</v>
+        <v>129520992</v>
       </c>
       <c r="B53" t="n">
-        <v>80150</v>
+        <v>78736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5839,21 +5839,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494361</v>
+        <v>494221</v>
       </c>
       <c r="R53" t="n">
-        <v>6834336</v>
+        <v>6834431</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,32 +5925,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521887</v>
+        <v>129521655</v>
       </c>
       <c r="B54" t="n">
-        <v>80178</v>
+        <v>78736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,13 +5960,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494350</v>
+        <v>494247</v>
       </c>
       <c r="R54" t="n">
-        <v>6834298</v>
+        <v>6834296</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>129522706</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>129522129</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6216,10 +6216,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129522857</v>
+        <v>129521358</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79102</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,21 +6227,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494475</v>
+        <v>494221</v>
       </c>
       <c r="R57" t="n">
-        <v>6834232</v>
+        <v>6834353</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129521656</v>
+        <v>129521131</v>
       </c>
       <c r="B58" t="n">
-        <v>80150</v>
+        <v>79102</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,37 +6324,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494219</v>
+        <v>494230</v>
       </c>
       <c r="R58" t="n">
-        <v>6834291</v>
+        <v>6834385</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6398,22 +6398,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129521358</v>
+        <v>129522432</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494221</v>
+        <v>494325</v>
       </c>
       <c r="R59" t="n">
-        <v>6834353</v>
+        <v>6834177</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6507,48 +6507,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129521131</v>
+        <v>129524392</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>92863</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494230</v>
+        <v>494486</v>
       </c>
       <c r="R60" t="n">
-        <v>6834385</v>
+        <v>6834613</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6592,22 +6592,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129522432</v>
+        <v>129522151</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>78827</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,21 +6615,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6639,13 +6639,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494325</v>
+        <v>494385</v>
       </c>
       <c r="R61" t="n">
-        <v>6834177</v>
+        <v>6834229</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6701,48 +6701,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524392</v>
+        <v>129524189</v>
       </c>
       <c r="B62" t="n">
-        <v>92835</v>
+        <v>79070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494486</v>
+        <v>494606</v>
       </c>
       <c r="R62" t="n">
-        <v>6834613</v>
+        <v>6834497</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6786,22 +6786,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129522151</v>
+        <v>129522857</v>
       </c>
       <c r="B63" t="n">
-        <v>78801</v>
+        <v>79070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,21 +6809,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494385</v>
+        <v>494475</v>
       </c>
       <c r="R63" t="n">
-        <v>6834229</v>
+        <v>6834232</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6895,10 +6895,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524189</v>
+        <v>129524775</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6930,13 +6930,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494606</v>
+        <v>494416</v>
       </c>
       <c r="R64" t="n">
-        <v>6834497</v>
+        <v>6834464</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129524775</v>
+        <v>129521656</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>80176</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,37 +7003,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494416</v>
+        <v>494219</v>
       </c>
       <c r="R65" t="n">
-        <v>6834464</v>
+        <v>6834291</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7077,69 +7077,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129524059</v>
+        <v>129522138</v>
       </c>
       <c r="B66" t="n">
-        <v>98727</v>
+        <v>79660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494582</v>
+        <v>494375</v>
       </c>
       <c r="R66" t="n">
-        <v>6834361</v>
+        <v>6834215</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7195,48 +7186,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129522138</v>
+        <v>129524059</v>
       </c>
       <c r="B67" t="n">
-        <v>79634</v>
+        <v>98756</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494375</v>
+        <v>494582</v>
       </c>
       <c r="R67" t="n">
-        <v>6834215</v>
+        <v>6834361</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129524680</v>
+        <v>129521986</v>
       </c>
       <c r="B68" t="n">
-        <v>80149</v>
+        <v>80176</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,34 +7303,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494357</v>
+        <v>494336</v>
       </c>
       <c r="R68" t="n">
-        <v>6834592</v>
+        <v>6834146</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129520975</v>
+        <v>129524680</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>80175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494243</v>
+        <v>494357</v>
       </c>
       <c r="R69" t="n">
-        <v>6834445</v>
+        <v>6834592</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>79070</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,37 +7497,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R70" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,60 +7571,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129522294</v>
+        <v>129520975</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>78827</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494419</v>
+        <v>494243</v>
       </c>
       <c r="R71" t="n">
-        <v>6834113</v>
+        <v>6834445</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7668,60 +7668,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129521804</v>
+        <v>129522294</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494297</v>
+        <v>494419</v>
       </c>
       <c r="R72" t="n">
-        <v>6834314</v>
+        <v>6834113</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7765,12 +7765,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7780,7 +7780,7 @@
         <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>129521838</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>129524606</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>129523011</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>129521271</v>
       </c>
       <c r="B78" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524119</v>
+        <v>129524246</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,34 +8370,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494556</v>
+        <v>494560</v>
       </c>
       <c r="R79" t="n">
-        <v>6834467</v>
+        <v>6834565</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8444,22 +8444,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129524246</v>
+        <v>129522454</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8487,14 +8487,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494560</v>
+        <v>494456</v>
       </c>
       <c r="R80" t="n">
-        <v>6834565</v>
+        <v>6834177</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8541,22 +8541,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8584,17 +8584,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R81" t="n">
         <v>6834177</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8638,22 +8638,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522450</v>
+        <v>129524119</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8661,37 +8661,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494325</v>
+        <v>494556</v>
       </c>
       <c r="R82" t="n">
-        <v>6834177</v>
+        <v>6834467</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8735,12 +8735,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8750,7 +8750,7 @@
         <v>129522644</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>129520989</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>129520902</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>129524525</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>129523899</v>
       </c>
       <c r="B87" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>129521936</v>
       </c>
       <c r="B88" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>129521041</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>129522147</v>
       </c>
       <c r="B90" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>129522027</v>
       </c>
       <c r="B91" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>129524797</v>
       </c>
       <c r="B92" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>129524791</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9846,32 +9846,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129521897</v>
+        <v>129522173</v>
       </c>
       <c r="B94" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494323</v>
+        <v>494418</v>
       </c>
       <c r="R94" t="n">
-        <v>6834131</v>
+        <v>6834113</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9943,32 +9943,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521475</v>
+        <v>129521897</v>
       </c>
       <c r="B95" t="n">
-        <v>78802</v>
+        <v>98756</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494181</v>
+        <v>494323</v>
       </c>
       <c r="R95" t="n">
-        <v>6834367</v>
+        <v>6834131</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10040,10 +10040,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129522173</v>
+        <v>129521475</v>
       </c>
       <c r="B96" t="n">
-        <v>80149</v>
+        <v>78828</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494418</v>
+        <v>494181</v>
       </c>
       <c r="R96" t="n">
-        <v>6834113</v>
+        <v>6834367</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10140,7 +10140,7 @@
         <v>129524273</v>
       </c>
       <c r="B97" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>129524130</v>
       </c>
       <c r="B98" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>129523005</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>129524530</v>
       </c>
       <c r="B100" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>129522632</v>
       </c>
       <c r="B101" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>129524122</v>
       </c>
       <c r="B102" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>129521977</v>
       </c>
       <c r="B103" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129522341</v>
+        <v>129521967</v>
       </c>
       <c r="B104" t="n">
-        <v>78801</v>
+        <v>79070</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,21 +10836,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10860,10 +10860,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494345</v>
+        <v>494346</v>
       </c>
       <c r="R104" t="n">
-        <v>6834202</v>
+        <v>6834277</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129522517</v>
+        <v>129521418</v>
       </c>
       <c r="B105" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,21 +10933,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494455</v>
+        <v>494176</v>
       </c>
       <c r="R105" t="n">
-        <v>6834176</v>
+        <v>6834368</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521967</v>
+        <v>129521144</v>
       </c>
       <c r="B106" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494346</v>
+        <v>494222</v>
       </c>
       <c r="R106" t="n">
-        <v>6834277</v>
+        <v>6834390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11116,10 +11116,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521418</v>
+        <v>129522341</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>78827</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,34 +11127,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494176</v>
+        <v>494345</v>
       </c>
       <c r="R107" t="n">
-        <v>6834368</v>
+        <v>6834202</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,60 +11201,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521144</v>
+        <v>129522100</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>58100</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494222</v>
+        <v>494368</v>
       </c>
       <c r="R108" t="n">
-        <v>6834390</v>
+        <v>6834126</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11298,44 +11298,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522100</v>
+        <v>129522517</v>
       </c>
       <c r="B109" t="n">
-        <v>58097</v>
+        <v>78828</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494368</v>
+        <v>494455</v>
       </c>
       <c r="R109" t="n">
-        <v>6834126</v>
+        <v>6834176</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>129523028</v>
       </c>
       <c r="B110" t="n">
-        <v>78052</v>
+        <v>78078</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>129521874</v>
       </c>
       <c r="B111" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11601,54 +11601,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B112" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R112" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11707,45 +11698,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129522819</v>
+        <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494470</v>
+        <v>494338</v>
       </c>
       <c r="R113" t="n">
-        <v>6834231</v>
+        <v>6834601</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11807,7 +11807,7 @@
         <v>129524240</v>
       </c>
       <c r="B114" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>129524762</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>129521147</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>129521072</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>129524747</v>
       </c>
       <c r="B119" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>129524381</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>129521663</v>
       </c>
       <c r="B121" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>129523234</v>
       </c>
       <c r="B122" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522736</v>
+        <v>129522012</v>
       </c>
       <c r="B123" t="n">
-        <v>91574</v>
+        <v>80175</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,34 +12688,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494443</v>
+        <v>494337</v>
       </c>
       <c r="R123" t="n">
-        <v>6834230</v>
+        <v>6834146</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12762,22 +12762,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522012</v>
+        <v>129521002</v>
       </c>
       <c r="B124" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,34 +12785,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494337</v>
+        <v>494241</v>
       </c>
       <c r="R124" t="n">
-        <v>6834146</v>
+        <v>6834425</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12859,22 +12859,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129524581</v>
+        <v>129522903</v>
       </c>
       <c r="B125" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494323</v>
+        <v>494466</v>
       </c>
       <c r="R125" t="n">
-        <v>6834627</v>
+        <v>6834211</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521002</v>
+        <v>129521823</v>
       </c>
       <c r="B126" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12999,17 +12999,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494241</v>
+        <v>494360</v>
       </c>
       <c r="R126" t="n">
-        <v>6834425</v>
+        <v>6834206</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13053,22 +13053,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522903</v>
+        <v>129522736</v>
       </c>
       <c r="B127" t="n">
-        <v>79044</v>
+        <v>91602</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494466</v>
+        <v>494443</v>
       </c>
       <c r="R127" t="n">
-        <v>6834211</v>
+        <v>6834230</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129521823</v>
+        <v>129524581</v>
       </c>
       <c r="B128" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,37 +13173,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494360</v>
+        <v>494323</v>
       </c>
       <c r="R128" t="n">
-        <v>6834206</v>
+        <v>6834627</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13247,12 +13247,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -13262,7 +13262,7 @@
         <v>129522783</v>
       </c>
       <c r="B129" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>129523308</v>
       </c>
       <c r="B130" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>129521635</v>
       </c>
       <c r="B131" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B132" t="n">
-        <v>78710</v>
+        <v>79070</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R132" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521302</v>
+        <v>129520912</v>
       </c>
       <c r="B133" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13678,17 +13678,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494215</v>
+        <v>494290</v>
       </c>
       <c r="R133" t="n">
-        <v>6834362</v>
+        <v>6834454</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13732,22 +13732,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129520912</v>
+        <v>129521752</v>
       </c>
       <c r="B134" t="n">
-        <v>79044</v>
+        <v>78736</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,34 +13755,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494290</v>
+        <v>494258</v>
       </c>
       <c r="R134" t="n">
-        <v>6834454</v>
+        <v>6834310</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13829,22 +13829,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521403</v>
+        <v>129522065</v>
       </c>
       <c r="B135" t="n">
-        <v>90585</v>
+        <v>78736</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494199</v>
+        <v>494373</v>
       </c>
       <c r="R135" t="n">
-        <v>6834366</v>
+        <v>6834247</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13938,10 +13938,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524667</v>
+        <v>129521403</v>
       </c>
       <c r="B136" t="n">
-        <v>80150</v>
+        <v>90613</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13949,43 +13949,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494352</v>
+        <v>494199</v>
       </c>
       <c r="R136" t="n">
-        <v>6834596</v>
+        <v>6834366</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14044,10 +14035,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129522065</v>
+        <v>129524667</v>
       </c>
       <c r="B137" t="n">
-        <v>78710</v>
+        <v>80176</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14055,34 +14046,43 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494373</v>
+        <v>494352</v>
       </c>
       <c r="R137" t="n">
-        <v>6834247</v>
+        <v>6834596</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14144,7 +14144,7 @@
         <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -6216,45 +6216,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521358</v>
+        <v>129524392</v>
       </c>
       <c r="B57" t="n">
-        <v>79102</v>
+        <v>92863</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494221</v>
+        <v>494486</v>
       </c>
       <c r="R57" t="n">
-        <v>6834353</v>
+        <v>6834613</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6301,19 +6301,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129521131</v>
+        <v>129521358</v>
       </c>
       <c r="B58" t="n">
         <v>79102</v>
@@ -6348,13 +6348,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494230</v>
+        <v>494221</v>
       </c>
       <c r="R58" t="n">
-        <v>6834385</v>
+        <v>6834353</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522432</v>
+        <v>129521131</v>
       </c>
       <c r="B59" t="n">
         <v>79102</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494325</v>
+        <v>494230</v>
       </c>
       <c r="R59" t="n">
-        <v>6834177</v>
+        <v>6834385</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6507,48 +6507,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524392</v>
+        <v>129522432</v>
       </c>
       <c r="B60" t="n">
-        <v>92863</v>
+        <v>79102</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494486</v>
+        <v>494325</v>
       </c>
       <c r="R60" t="n">
-        <v>6834613</v>
+        <v>6834177</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6592,22 +6592,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129522151</v>
+        <v>129521656</v>
       </c>
       <c r="B61" t="n">
-        <v>78827</v>
+        <v>80176</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494385</v>
+        <v>494219</v>
       </c>
       <c r="R61" t="n">
-        <v>6834229</v>
+        <v>6834291</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6689,22 +6689,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524189</v>
+        <v>129522151</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>78827</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6712,21 +6712,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6736,13 +6736,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494606</v>
+        <v>494385</v>
       </c>
       <c r="R62" t="n">
-        <v>6834497</v>
+        <v>6834229</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129522857</v>
+        <v>129524189</v>
       </c>
       <c r="B63" t="n">
         <v>79070</v>
@@ -6833,13 +6833,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494475</v>
+        <v>494606</v>
       </c>
       <c r="R63" t="n">
-        <v>6834232</v>
+        <v>6834497</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524775</v>
+        <v>129522857</v>
       </c>
       <c r="B64" t="n">
         <v>79070</v>
@@ -6930,10 +6930,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494416</v>
+        <v>494475</v>
       </c>
       <c r="R64" t="n">
-        <v>6834464</v>
+        <v>6834232</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129521656</v>
+        <v>129524775</v>
       </c>
       <c r="B65" t="n">
-        <v>80176</v>
+        <v>79070</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,37 +7003,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494219</v>
+        <v>494416</v>
       </c>
       <c r="R65" t="n">
-        <v>6834291</v>
+        <v>6834464</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7077,12 +7077,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522027</v>
+        <v>129521897</v>
       </c>
       <c r="B91" t="n">
-        <v>80176</v>
+        <v>98756</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494337</v>
+        <v>494323</v>
       </c>
       <c r="R91" t="n">
-        <v>6834149</v>
+        <v>6834131</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9638,59 +9638,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524797</v>
+        <v>129522027</v>
       </c>
       <c r="B92" t="n">
-        <v>92863</v>
+        <v>80176</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494387</v>
+        <v>494337</v>
       </c>
       <c r="R92" t="n">
-        <v>6834437</v>
+        <v>6834149</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9737,57 +9723,71 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524791</v>
+        <v>129524797</v>
       </c>
       <c r="B93" t="n">
-        <v>79070</v>
+        <v>92863</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494381</v>
+        <v>494387</v>
       </c>
       <c r="R93" t="n">
-        <v>6834429</v>
+        <v>6834437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,10 +9846,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129522173</v>
+        <v>129524791</v>
       </c>
       <c r="B94" t="n">
-        <v>80175</v>
+        <v>79070</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9857,34 +9857,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494418</v>
+        <v>494381</v>
       </c>
       <c r="R94" t="n">
-        <v>6834113</v>
+        <v>6834429</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9931,44 +9931,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521897</v>
+        <v>129522173</v>
       </c>
       <c r="B95" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494323</v>
+        <v>494418</v>
       </c>
       <c r="R95" t="n">
-        <v>6834131</v>
+        <v>6834113</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10137,48 +10137,57 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129524273</v>
+        <v>129522632</v>
       </c>
       <c r="B97" t="n">
-        <v>79102</v>
+        <v>98756</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494549</v>
+        <v>494455</v>
       </c>
       <c r="R97" t="n">
-        <v>6834588</v>
+        <v>6834185</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10222,22 +10231,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524130</v>
+        <v>129524273</v>
       </c>
       <c r="B98" t="n">
-        <v>79070</v>
+        <v>79102</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10245,37 +10254,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494537</v>
+        <v>494549</v>
       </c>
       <c r="R98" t="n">
-        <v>6834492</v>
+        <v>6834588</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10319,19 +10328,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129523005</v>
+        <v>129524130</v>
       </c>
       <c r="B99" t="n">
         <v>79070</v>
@@ -10362,14 +10371,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494491</v>
+        <v>494537</v>
       </c>
       <c r="R99" t="n">
-        <v>6834229</v>
+        <v>6834492</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10416,19 +10425,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129524530</v>
+        <v>129523005</v>
       </c>
       <c r="B100" t="n">
         <v>79070</v>
@@ -10463,10 +10472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494349</v>
+        <v>494491</v>
       </c>
       <c r="R100" t="n">
-        <v>6834653</v>
+        <v>6834229</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10525,54 +10534,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129522632</v>
+        <v>129524530</v>
       </c>
       <c r="B101" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494455</v>
+        <v>494349</v>
       </c>
       <c r="R101" t="n">
-        <v>6834185</v>
+        <v>6834653</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10619,12 +10619,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521977</v>
+        <v>129521967</v>
       </c>
       <c r="B103" t="n">
-        <v>80175</v>
+        <v>79070</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,34 +10739,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494334</v>
+        <v>494346</v>
       </c>
       <c r="R103" t="n">
-        <v>6834144</v>
+        <v>6834277</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,19 +10813,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521967</v>
+        <v>129521418</v>
       </c>
       <c r="B104" t="n">
         <v>79070</v>
@@ -10856,14 +10856,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494346</v>
+        <v>494176</v>
       </c>
       <c r="R104" t="n">
-        <v>6834277</v>
+        <v>6834368</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,19 +10910,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521418</v>
+        <v>129521144</v>
       </c>
       <c r="B105" t="n">
         <v>79070</v>
@@ -10953,14 +10953,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494176</v>
+        <v>494222</v>
       </c>
       <c r="R105" t="n">
-        <v>6834368</v>
+        <v>6834390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521144</v>
+        <v>129522341</v>
       </c>
       <c r="B106" t="n">
-        <v>79070</v>
+        <v>78827</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,21 +11030,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494222</v>
+        <v>494345</v>
       </c>
       <c r="R106" t="n">
-        <v>6834390</v>
+        <v>6834202</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11116,10 +11116,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129522341</v>
+        <v>129521977</v>
       </c>
       <c r="B107" t="n">
-        <v>78827</v>
+        <v>80175</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,34 +11127,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494345</v>
+        <v>494334</v>
       </c>
       <c r="R107" t="n">
-        <v>6834202</v>
+        <v>6834144</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,12 +11201,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11407,45 +11407,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129523028</v>
+        <v>129524619</v>
       </c>
       <c r="B110" t="n">
-        <v>78078</v>
+        <v>98756</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494500</v>
+        <v>494338</v>
       </c>
       <c r="R110" t="n">
-        <v>6834263</v>
+        <v>6834601</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,10 +11513,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129521874</v>
+        <v>129522819</v>
       </c>
       <c r="B111" t="n">
-        <v>80175</v>
+        <v>79070</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11524,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11548,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494355</v>
+        <v>494470</v>
       </c>
       <c r="R111" t="n">
-        <v>6834295</v>
+        <v>6834231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11610,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129522819</v>
+        <v>129523028</v>
       </c>
       <c r="B112" t="n">
-        <v>79070</v>
+        <v>78078</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11621,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11645,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494470</v>
+        <v>494500</v>
       </c>
       <c r="R112" t="n">
-        <v>6834231</v>
+        <v>6834263</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11698,54 +11707,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129524619</v>
+        <v>129521874</v>
       </c>
       <c r="B113" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494338</v>
+        <v>494355</v>
       </c>
       <c r="R113" t="n">
-        <v>6834601</v>
+        <v>6834295</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524240</v>
+        <v>129524762</v>
       </c>
       <c r="B114" t="n">
-        <v>79102</v>
+        <v>79070</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494559</v>
+        <v>494406</v>
       </c>
       <c r="R114" t="n">
-        <v>6834519</v>
+        <v>6834477</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11901,10 +11901,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129524762</v>
+        <v>129524240</v>
       </c>
       <c r="B115" t="n">
-        <v>79070</v>
+        <v>79102</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11912,21 +11912,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494406</v>
+        <v>494559</v>
       </c>
       <c r="R115" t="n">
-        <v>6834477</v>
+        <v>6834519</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1739,7 +1739,7 @@
         <v>129476557</v>
       </c>
       <c r="B11" t="n">
-        <v>80211</v>
+        <v>80216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>129512476</v>
       </c>
       <c r="B14" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>129512298</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>129513963</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>129513412</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>129512195</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129512125</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>129513122</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>129511985</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>129511911</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>129511957</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>129512105</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>129512361</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129512918</v>
+        <v>129511943</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494417</v>
+        <v>494635</v>
       </c>
       <c r="R26" t="n">
-        <v>6833948</v>
+        <v>6834347</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129511943</v>
+        <v>129512918</v>
       </c>
       <c r="B27" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,21 +3317,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494635</v>
+        <v>494417</v>
       </c>
       <c r="R27" t="n">
-        <v>6834347</v>
+        <v>6833948</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,7 +3406,7 @@
         <v>129512658</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>129513370</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B31" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R31" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R32" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
         <v>129513741</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>129513342</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>129512771</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>129512470</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>129512788</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129512556</v>
       </c>
       <c r="B38" t="n">
-        <v>80211</v>
+        <v>80216</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>129520952</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>129522021</v>
       </c>
       <c r="B40" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>129522417</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>129524342</v>
       </c>
       <c r="B42" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129521092</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>129524785</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>129524779</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129522893</v>
+        <v>129524385</v>
       </c>
       <c r="B46" t="n">
-        <v>79102</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494477</v>
+        <v>494528</v>
       </c>
       <c r="R46" t="n">
-        <v>6834229</v>
+        <v>6834660</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129522256</v>
+        <v>129524595</v>
       </c>
       <c r="B47" t="n">
-        <v>78828</v>
+        <v>80180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494384</v>
+        <v>494349</v>
       </c>
       <c r="R47" t="n">
-        <v>6834211</v>
+        <v>6834611</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129521425</v>
+        <v>129522893</v>
       </c>
       <c r="B48" t="n">
-        <v>78828</v>
+        <v>79107</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494187</v>
+        <v>494477</v>
       </c>
       <c r="R48" t="n">
-        <v>6834373</v>
+        <v>6834229</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129524595</v>
+        <v>129522256</v>
       </c>
       <c r="B49" t="n">
-        <v>80175</v>
+        <v>78833</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494349</v>
+        <v>494384</v>
       </c>
       <c r="R49" t="n">
-        <v>6834611</v>
+        <v>6834211</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129524385</v>
+        <v>129521425</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494528</v>
+        <v>494187</v>
       </c>
       <c r="R50" t="n">
-        <v>6834660</v>
+        <v>6834373</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>129521826</v>
       </c>
       <c r="B51" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5731,32 +5731,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521887</v>
+        <v>129520992</v>
       </c>
       <c r="B52" t="n">
-        <v>80204</v>
+        <v>78741</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494350</v>
+        <v>494221</v>
       </c>
       <c r="R52" t="n">
-        <v>6834298</v>
+        <v>6834431</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129520992</v>
+        <v>129521655</v>
       </c>
       <c r="B53" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494221</v>
+        <v>494247</v>
       </c>
       <c r="R53" t="n">
-        <v>6834431</v>
+        <v>6834296</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521655</v>
+        <v>129522706</v>
       </c>
       <c r="B54" t="n">
-        <v>78736</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494247</v>
+        <v>494454</v>
       </c>
       <c r="R54" t="n">
-        <v>6834296</v>
+        <v>6834225</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6022,10 +6022,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522706</v>
+        <v>129522129</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,17 +6053,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494454</v>
+        <v>494397</v>
       </c>
       <c r="R55" t="n">
-        <v>6834225</v>
+        <v>6834116</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6107,57 +6107,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129522129</v>
+        <v>129521887</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>80209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494397</v>
+        <v>494350</v>
       </c>
       <c r="R56" t="n">
-        <v>6834116</v>
+        <v>6834298</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,44 +6204,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129524392</v>
+        <v>129521656</v>
       </c>
       <c r="B57" t="n">
-        <v>92863</v>
+        <v>80181</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6251,13 +6251,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494486</v>
+        <v>494219</v>
       </c>
       <c r="R57" t="n">
-        <v>6834613</v>
+        <v>6834291</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6313,45 +6313,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129521358</v>
+        <v>129524059</v>
       </c>
       <c r="B58" t="n">
-        <v>79102</v>
+        <v>98768</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494221</v>
+        <v>494582</v>
       </c>
       <c r="R58" t="n">
-        <v>6834353</v>
+        <v>6834361</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6410,10 +6419,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129521131</v>
+        <v>129522138</v>
       </c>
       <c r="B59" t="n">
-        <v>79102</v>
+        <v>79665</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6421,21 +6430,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6445,10 +6454,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494230</v>
+        <v>494375</v>
       </c>
       <c r="R59" t="n">
-        <v>6834385</v>
+        <v>6834215</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6507,10 +6516,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129522432</v>
+        <v>129521358</v>
       </c>
       <c r="B60" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6542,13 +6551,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494325</v>
+        <v>494221</v>
       </c>
       <c r="R60" t="n">
-        <v>6834177</v>
+        <v>6834353</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6604,10 +6613,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521656</v>
+        <v>129521131</v>
       </c>
       <c r="B61" t="n">
-        <v>80176</v>
+        <v>79107</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,37 +6624,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494219</v>
+        <v>494230</v>
       </c>
       <c r="R61" t="n">
-        <v>6834291</v>
+        <v>6834385</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6689,22 +6698,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129522151</v>
+        <v>129522432</v>
       </c>
       <c r="B62" t="n">
-        <v>78827</v>
+        <v>79107</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6712,21 +6721,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6736,13 +6745,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494385</v>
+        <v>494325</v>
       </c>
       <c r="R62" t="n">
-        <v>6834229</v>
+        <v>6834177</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6798,48 +6807,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129524189</v>
+        <v>129524392</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494606</v>
+        <v>494486</v>
       </c>
       <c r="R63" t="n">
-        <v>6834497</v>
+        <v>6834613</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6883,12 +6892,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6898,7 +6907,7 @@
         <v>129522857</v>
       </c>
       <c r="B64" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6995,7 +7004,7 @@
         <v>129524775</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7089,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129522138</v>
+        <v>129522151</v>
       </c>
       <c r="B66" t="n">
-        <v>79660</v>
+        <v>78832</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,13 +7133,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494375</v>
+        <v>494385</v>
       </c>
       <c r="R66" t="n">
-        <v>6834215</v>
+        <v>6834229</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7186,57 +7195,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524059</v>
+        <v>129524189</v>
       </c>
       <c r="B67" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494582</v>
+        <v>494606</v>
       </c>
       <c r="R67" t="n">
-        <v>6834361</v>
+        <v>6834497</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>129521986</v>
       </c>
       <c r="B68" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B69" t="n">
-        <v>80175</v>
+        <v>78832</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R69" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,48 +7486,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129521804</v>
+        <v>129522294</v>
       </c>
       <c r="B70" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494297</v>
+        <v>494419</v>
       </c>
       <c r="R70" t="n">
-        <v>6834314</v>
+        <v>6834113</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,22 +7571,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129520975</v>
+        <v>129521804</v>
       </c>
       <c r="B71" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,21 +7594,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7618,10 +7618,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494243</v>
+        <v>494297</v>
       </c>
       <c r="R71" t="n">
-        <v>6834445</v>
+        <v>6834314</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -7680,45 +7680,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129522294</v>
+        <v>129524680</v>
       </c>
       <c r="B72" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494419</v>
+        <v>494357</v>
       </c>
       <c r="R72" t="n">
-        <v>6834113</v>
+        <v>6834592</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7765,22 +7765,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129522011</v>
+        <v>129523011</v>
       </c>
       <c r="B73" t="n">
-        <v>79102</v>
+        <v>79075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494385</v>
+        <v>494480</v>
       </c>
       <c r="R73" t="n">
-        <v>6834293</v>
+        <v>6834232</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,22 +7862,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129521838</v>
+        <v>129522011</v>
       </c>
       <c r="B74" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494355</v>
+        <v>494385</v>
       </c>
       <c r="R74" t="n">
-        <v>6834299</v>
+        <v>6834293</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129524606</v>
+        <v>129521838</v>
       </c>
       <c r="B75" t="n">
-        <v>80175</v>
+        <v>79107</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494333</v>
+        <v>494355</v>
       </c>
       <c r="R75" t="n">
-        <v>6834609</v>
+        <v>6834299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129523011</v>
+        <v>129524606</v>
       </c>
       <c r="B76" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,34 +8079,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494480</v>
+        <v>494333</v>
       </c>
       <c r="R76" t="n">
-        <v>6834232</v>
+        <v>6834609</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8153,12 +8153,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8168,7 +8168,7 @@
         <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>129521271</v>
       </c>
       <c r="B78" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524246</v>
+        <v>129524119</v>
       </c>
       <c r="B79" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,34 +8370,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494560</v>
+        <v>494556</v>
       </c>
       <c r="R79" t="n">
-        <v>6834565</v>
+        <v>6834467</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8444,57 +8444,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522454</v>
+        <v>129520989</v>
       </c>
       <c r="B80" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494456</v>
+        <v>494262</v>
       </c>
       <c r="R80" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8553,48 +8562,57 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522450</v>
+        <v>129522644</v>
       </c>
       <c r="B81" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494325</v>
+        <v>494450</v>
       </c>
       <c r="R81" t="n">
-        <v>6834177</v>
+        <v>6834178</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8638,22 +8656,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129524119</v>
+        <v>129522454</v>
       </c>
       <c r="B82" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8661,21 +8679,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8685,10 +8703,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494556</v>
+        <v>494456</v>
       </c>
       <c r="R82" t="n">
-        <v>6834467</v>
+        <v>6834177</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8747,57 +8765,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522644</v>
+        <v>129522450</v>
       </c>
       <c r="B83" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494450</v>
+        <v>494325</v>
       </c>
       <c r="R83" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8841,66 +8850,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129520989</v>
+        <v>129524246</v>
       </c>
       <c r="B84" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494262</v>
+        <v>494560</v>
       </c>
       <c r="R84" t="n">
-        <v>6834427</v>
+        <v>6834565</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8947,12 +8947,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8962,7 +8962,7 @@
         <v>129520902</v>
       </c>
       <c r="B85" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>129524525</v>
       </c>
       <c r="B86" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>129523899</v>
       </c>
       <c r="B87" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>129521936</v>
       </c>
       <c r="B88" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>129521041</v>
       </c>
       <c r="B89" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>129522147</v>
       </c>
       <c r="B90" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129521897</v>
+        <v>129522027</v>
       </c>
       <c r="B91" t="n">
-        <v>98756</v>
+        <v>80181</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494323</v>
+        <v>494337</v>
       </c>
       <c r="R91" t="n">
-        <v>6834131</v>
+        <v>6834149</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9638,45 +9638,59 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129522027</v>
+        <v>129524797</v>
       </c>
       <c r="B92" t="n">
-        <v>80176</v>
+        <v>92869</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494337</v>
+        <v>494387</v>
       </c>
       <c r="R92" t="n">
-        <v>6834149</v>
+        <v>6834437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,71 +9737,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524797</v>
+        <v>129522173</v>
       </c>
       <c r="B93" t="n">
-        <v>92863</v>
+        <v>80180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494387</v>
+        <v>494418</v>
       </c>
       <c r="R93" t="n">
-        <v>6834437</v>
+        <v>6834113</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9834,12 +9834,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -9849,7 +9849,7 @@
         <v>129524791</v>
       </c>
       <c r="B94" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9943,32 +9943,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129522173</v>
+        <v>129521897</v>
       </c>
       <c r="B95" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9978,10 +9978,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494418</v>
+        <v>494323</v>
       </c>
       <c r="R95" t="n">
-        <v>6834113</v>
+        <v>6834131</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10043,7 +10043,7 @@
         <v>129521475</v>
       </c>
       <c r="B96" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10137,57 +10137,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129522632</v>
+        <v>129524273</v>
       </c>
       <c r="B97" t="n">
-        <v>98756</v>
+        <v>79107</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494455</v>
+        <v>494549</v>
       </c>
       <c r="R97" t="n">
-        <v>6834185</v>
+        <v>6834588</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10231,22 +10222,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524273</v>
+        <v>129524530</v>
       </c>
       <c r="B98" t="n">
-        <v>79102</v>
+        <v>79075</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10254,21 +10245,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10278,13 +10269,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494549</v>
+        <v>494349</v>
       </c>
       <c r="R98" t="n">
-        <v>6834588</v>
+        <v>6834653</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10343,7 +10334,7 @@
         <v>129524130</v>
       </c>
       <c r="B99" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10440,7 +10431,7 @@
         <v>129523005</v>
       </c>
       <c r="B100" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10534,45 +10525,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129524530</v>
+        <v>129522632</v>
       </c>
       <c r="B101" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494349</v>
+        <v>494455</v>
       </c>
       <c r="R101" t="n">
-        <v>6834653</v>
+        <v>6834185</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10619,12 +10619,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10634,7 +10634,7 @@
         <v>129524122</v>
       </c>
       <c r="B102" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521967</v>
+        <v>129521144</v>
       </c>
       <c r="B103" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494346</v>
+        <v>494222</v>
       </c>
       <c r="R103" t="n">
-        <v>6834277</v>
+        <v>6834390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521418</v>
+        <v>129521967</v>
       </c>
       <c r="B104" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10856,14 +10856,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494176</v>
+        <v>494346</v>
       </c>
       <c r="R104" t="n">
-        <v>6834368</v>
+        <v>6834277</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521144</v>
+        <v>129521418</v>
       </c>
       <c r="B105" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10953,14 +10953,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494222</v>
+        <v>494176</v>
       </c>
       <c r="R105" t="n">
-        <v>6834390</v>
+        <v>6834368</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,12 +11007,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11022,7 +11022,7 @@
         <v>129522341</v>
       </c>
       <c r="B106" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>129521977</v>
       </c>
       <c r="B107" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11213,32 +11213,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522100</v>
+        <v>129522517</v>
       </c>
       <c r="B108" t="n">
-        <v>58100</v>
+        <v>78833</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494368</v>
+        <v>494455</v>
       </c>
       <c r="R108" t="n">
-        <v>6834126</v>
+        <v>6834176</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11310,32 +11310,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522517</v>
+        <v>129522100</v>
       </c>
       <c r="B109" t="n">
-        <v>78828</v>
+        <v>58105</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494455</v>
+        <v>494368</v>
       </c>
       <c r="R109" t="n">
-        <v>6834176</v>
+        <v>6834126</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11407,54 +11407,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B110" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R110" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11513,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129522819</v>
+        <v>129523028</v>
       </c>
       <c r="B111" t="n">
-        <v>79070</v>
+        <v>78083</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11524,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11548,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494470</v>
+        <v>494500</v>
       </c>
       <c r="R111" t="n">
-        <v>6834231</v>
+        <v>6834263</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11610,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129523028</v>
+        <v>129521874</v>
       </c>
       <c r="B112" t="n">
-        <v>78078</v>
+        <v>80180</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11621,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11645,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494500</v>
+        <v>494355</v>
       </c>
       <c r="R112" t="n">
-        <v>6834263</v>
+        <v>6834295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11707,45 +11698,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129521874</v>
+        <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494355</v>
+        <v>494338</v>
       </c>
       <c r="R113" t="n">
-        <v>6834295</v>
+        <v>6834601</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524762</v>
+        <v>129521147</v>
       </c>
       <c r="B114" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11835,14 +11835,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494406</v>
+        <v>494225</v>
       </c>
       <c r="R114" t="n">
-        <v>6834477</v>
+        <v>6834382</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11889,22 +11889,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129524240</v>
+        <v>129524762</v>
       </c>
       <c r="B115" t="n">
-        <v>79102</v>
+        <v>79075</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11912,21 +11912,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494559</v>
+        <v>494406</v>
       </c>
       <c r="R115" t="n">
-        <v>6834519</v>
+        <v>6834477</v>
       </c>
       <c r="S115" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11998,10 +11998,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521147</v>
+        <v>129521072</v>
       </c>
       <c r="B116" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12029,14 +12029,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494225</v>
+        <v>494234</v>
       </c>
       <c r="R116" t="n">
-        <v>6834382</v>
+        <v>6834416</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12083,22 +12083,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129521072</v>
+        <v>129524240</v>
       </c>
       <c r="B117" t="n">
-        <v>79070</v>
+        <v>79107</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12130,13 +12130,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494234</v>
+        <v>494559</v>
       </c>
       <c r="R117" t="n">
-        <v>6834416</v>
+        <v>6834519</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521664</v>
+        <v>129521663</v>
       </c>
       <c r="B118" t="n">
-        <v>91602</v>
+        <v>78833</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494255</v>
+        <v>494242</v>
       </c>
       <c r="R118" t="n">
-        <v>6834250</v>
+        <v>6834295</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524747</v>
+        <v>129523234</v>
       </c>
       <c r="B119" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494401</v>
+        <v>494472</v>
       </c>
       <c r="R119" t="n">
-        <v>6834640</v>
+        <v>6834268</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129524381</v>
+        <v>129521664</v>
       </c>
       <c r="B120" t="n">
-        <v>79070</v>
+        <v>91608</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494485</v>
+        <v>494255</v>
       </c>
       <c r="R120" t="n">
-        <v>6834612</v>
+        <v>6834250</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129521663</v>
+        <v>129524747</v>
       </c>
       <c r="B121" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494242</v>
+        <v>494401</v>
       </c>
       <c r="R121" t="n">
-        <v>6834295</v>
+        <v>6834640</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129523234</v>
+        <v>129524381</v>
       </c>
       <c r="B122" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494472</v>
+        <v>494485</v>
       </c>
       <c r="R122" t="n">
-        <v>6834268</v>
+        <v>6834612</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,22 +12665,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522012</v>
+        <v>129522783</v>
       </c>
       <c r="B123" t="n">
-        <v>80175</v>
+        <v>79107</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,34 +12688,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494337</v>
+        <v>494456</v>
       </c>
       <c r="R123" t="n">
-        <v>6834146</v>
+        <v>6834228</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12762,22 +12762,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129521002</v>
+        <v>129523308</v>
       </c>
       <c r="B124" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494241</v>
+        <v>494520</v>
       </c>
       <c r="R124" t="n">
-        <v>6834425</v>
+        <v>6834279</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129522903</v>
+        <v>129521635</v>
       </c>
       <c r="B125" t="n">
-        <v>79070</v>
+        <v>78741</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,13 +12906,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494466</v>
+        <v>494214</v>
       </c>
       <c r="R125" t="n">
-        <v>6834211</v>
+        <v>6834306</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521823</v>
+        <v>129522736</v>
       </c>
       <c r="B126" t="n">
-        <v>79070</v>
+        <v>91608</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,37 +12979,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494360</v>
+        <v>494443</v>
       </c>
       <c r="R126" t="n">
-        <v>6834206</v>
+        <v>6834230</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13053,22 +13053,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522736</v>
+        <v>129522903</v>
       </c>
       <c r="B127" t="n">
-        <v>91602</v>
+        <v>79075</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494443</v>
+        <v>494466</v>
       </c>
       <c r="R127" t="n">
-        <v>6834230</v>
+        <v>6834211</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129524581</v>
+        <v>129521002</v>
       </c>
       <c r="B128" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494323</v>
+        <v>494241</v>
       </c>
       <c r="R128" t="n">
-        <v>6834627</v>
+        <v>6834425</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129522783</v>
+        <v>129521823</v>
       </c>
       <c r="B129" t="n">
-        <v>79102</v>
+        <v>79075</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,37 +13270,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494456</v>
+        <v>494360</v>
       </c>
       <c r="R129" t="n">
-        <v>6834228</v>
+        <v>6834206</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13344,22 +13344,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129523308</v>
+        <v>129522012</v>
       </c>
       <c r="B130" t="n">
-        <v>78736</v>
+        <v>80180</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,37 +13367,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494520</v>
+        <v>494337</v>
       </c>
       <c r="R130" t="n">
-        <v>6834279</v>
+        <v>6834146</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13441,22 +13441,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129521635</v>
+        <v>129524581</v>
       </c>
       <c r="B131" t="n">
-        <v>78736</v>
+        <v>80180</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,13 +13488,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494214</v>
+        <v>494323</v>
       </c>
       <c r="R131" t="n">
-        <v>6834306</v>
+        <v>6834627</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>129521302</v>
       </c>
       <c r="B132" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>129520912</v>
       </c>
       <c r="B133" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>129521752</v>
       </c>
       <c r="B134" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129522065</v>
+        <v>129521403</v>
       </c>
       <c r="B135" t="n">
-        <v>78736</v>
+        <v>90619</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494373</v>
+        <v>494199</v>
       </c>
       <c r="R135" t="n">
-        <v>6834247</v>
+        <v>6834366</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13938,10 +13938,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129521403</v>
+        <v>129524667</v>
       </c>
       <c r="B136" t="n">
-        <v>90613</v>
+        <v>80181</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13949,34 +13949,43 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494199</v>
+        <v>494352</v>
       </c>
       <c r="R136" t="n">
-        <v>6834366</v>
+        <v>6834596</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14035,10 +14044,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524667</v>
+        <v>129522065</v>
       </c>
       <c r="B137" t="n">
-        <v>80176</v>
+        <v>78741</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14046,43 +14055,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494352</v>
+        <v>494373</v>
       </c>
       <c r="R137" t="n">
-        <v>6834596</v>
+        <v>6834247</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14144,7 +14144,7 @@
         <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1739,7 +1739,7 @@
         <v>129476557</v>
       </c>
       <c r="B11" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>129512476</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>129512298</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         <v>129513963</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>129513412</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>129512195</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129512125</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>129513122</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>129511985</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>129511911</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>129511957</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>129512105</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>129512361</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129511943</v>
+        <v>129512918</v>
       </c>
       <c r="B26" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,21 +3220,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494635</v>
+        <v>494417</v>
       </c>
       <c r="R26" t="n">
-        <v>6834347</v>
+        <v>6833948</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129512918</v>
+        <v>129511943</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,21 +3317,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494417</v>
+        <v>494635</v>
       </c>
       <c r="R27" t="n">
-        <v>6833948</v>
+        <v>6834347</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,7 +3406,7 @@
         <v>129512658</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>129513370</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R31" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B32" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R32" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
         <v>129513741</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>129513342</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129512771</v>
+        <v>129512470</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494466</v>
+        <v>494652</v>
       </c>
       <c r="R35" t="n">
-        <v>6833989</v>
+        <v>6833984</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129512470</v>
+        <v>129512771</v>
       </c>
       <c r="B36" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494652</v>
+        <v>494466</v>
       </c>
       <c r="R36" t="n">
-        <v>6833984</v>
+        <v>6833989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
         <v>129512788</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129512556</v>
       </c>
       <c r="B38" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>129520952</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>129522021</v>
       </c>
       <c r="B40" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>129522417</v>
       </c>
       <c r="B41" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>129524342</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129521092</v>
       </c>
       <c r="B43" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129524785</v>
+        <v>129524779</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494405</v>
+        <v>494423</v>
       </c>
       <c r="R44" t="n">
-        <v>6834446</v>
+        <v>6834463</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129524779</v>
+        <v>129524785</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494423</v>
+        <v>494405</v>
       </c>
       <c r="R45" t="n">
-        <v>6834463</v>
+        <v>6834446</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129524385</v>
+        <v>129522893</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79108</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494528</v>
+        <v>494477</v>
       </c>
       <c r="R46" t="n">
-        <v>6834660</v>
+        <v>6834229</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524595</v>
+        <v>129524385</v>
       </c>
       <c r="B47" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494349</v>
+        <v>494528</v>
       </c>
       <c r="R47" t="n">
-        <v>6834611</v>
+        <v>6834660</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129522893</v>
+        <v>129522256</v>
       </c>
       <c r="B48" t="n">
-        <v>79107</v>
+        <v>78834</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494477</v>
+        <v>494384</v>
       </c>
       <c r="R48" t="n">
-        <v>6834229</v>
+        <v>6834211</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129522256</v>
+        <v>129521425</v>
       </c>
       <c r="B49" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494384</v>
+        <v>494187</v>
       </c>
       <c r="R49" t="n">
-        <v>6834211</v>
+        <v>6834373</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129521425</v>
+        <v>129524595</v>
       </c>
       <c r="B50" t="n">
-        <v>78833</v>
+        <v>80181</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494187</v>
+        <v>494349</v>
       </c>
       <c r="R50" t="n">
-        <v>6834373</v>
+        <v>6834611</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129521826</v>
+        <v>129520992</v>
       </c>
       <c r="B51" t="n">
-        <v>80181</v>
+        <v>78742</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494361</v>
+        <v>494221</v>
       </c>
       <c r="R51" t="n">
-        <v>6834336</v>
+        <v>6834431</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129520992</v>
+        <v>129521655</v>
       </c>
       <c r="B52" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494221</v>
+        <v>494247</v>
       </c>
       <c r="R52" t="n">
-        <v>6834431</v>
+        <v>6834296</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521655</v>
+        <v>129521887</v>
       </c>
       <c r="B53" t="n">
-        <v>78741</v>
+        <v>80210</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494247</v>
+        <v>494350</v>
       </c>
       <c r="R53" t="n">
-        <v>6834296</v>
+        <v>6834298</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522706</v>
+        <v>129522129</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5956,17 +5956,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494454</v>
+        <v>494397</v>
       </c>
       <c r="R54" t="n">
-        <v>6834225</v>
+        <v>6834116</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,22 +6010,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522129</v>
+        <v>129522706</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6053,17 +6053,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494397</v>
+        <v>494454</v>
       </c>
       <c r="R55" t="n">
-        <v>6834116</v>
+        <v>6834225</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6107,44 +6107,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521887</v>
+        <v>129521826</v>
       </c>
       <c r="B56" t="n">
-        <v>80209</v>
+        <v>80182</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494350</v>
+        <v>494361</v>
       </c>
       <c r="R56" t="n">
-        <v>6834298</v>
+        <v>6834336</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6216,10 +6216,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521656</v>
+        <v>129521358</v>
       </c>
       <c r="B57" t="n">
-        <v>80181</v>
+        <v>79108</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,37 +6227,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494219</v>
+        <v>494221</v>
       </c>
       <c r="R57" t="n">
-        <v>6834291</v>
+        <v>6834353</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6301,69 +6301,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129524059</v>
+        <v>129521131</v>
       </c>
       <c r="B58" t="n">
-        <v>98768</v>
+        <v>79108</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494582</v>
+        <v>494230</v>
       </c>
       <c r="R58" t="n">
-        <v>6834361</v>
+        <v>6834385</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6419,10 +6410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522138</v>
+        <v>129522432</v>
       </c>
       <c r="B59" t="n">
-        <v>79665</v>
+        <v>79108</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6430,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6454,10 +6445,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494375</v>
+        <v>494325</v>
       </c>
       <c r="R59" t="n">
-        <v>6834215</v>
+        <v>6834177</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6516,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129521358</v>
+        <v>129524189</v>
       </c>
       <c r="B60" t="n">
-        <v>79107</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6527,21 +6518,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6551,13 +6542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494221</v>
+        <v>494606</v>
       </c>
       <c r="R60" t="n">
-        <v>6834353</v>
+        <v>6834497</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6613,10 +6604,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521131</v>
+        <v>129522857</v>
       </c>
       <c r="B61" t="n">
-        <v>79107</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,21 +6615,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6648,13 +6639,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494230</v>
+        <v>494475</v>
       </c>
       <c r="R61" t="n">
-        <v>6834385</v>
+        <v>6834232</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6710,10 +6701,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129522432</v>
+        <v>129524775</v>
       </c>
       <c r="B62" t="n">
-        <v>79107</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6712,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,13 +6736,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494325</v>
+        <v>494416</v>
       </c>
       <c r="R62" t="n">
-        <v>6834177</v>
+        <v>6834464</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6807,32 +6798,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129524392</v>
+        <v>129521656</v>
       </c>
       <c r="B63" t="n">
-        <v>92869</v>
+        <v>80182</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6842,13 +6833,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494486</v>
+        <v>494219</v>
       </c>
       <c r="R63" t="n">
-        <v>6834613</v>
+        <v>6834291</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6904,45 +6895,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129522857</v>
+        <v>129524392</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494475</v>
+        <v>494486</v>
       </c>
       <c r="R64" t="n">
-        <v>6834232</v>
+        <v>6834613</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6989,57 +6980,66 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129524775</v>
+        <v>129524059</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494416</v>
+        <v>494582</v>
       </c>
       <c r="R65" t="n">
-        <v>6834464</v>
+        <v>6834361</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7101,7 +7101,7 @@
         <v>129522151</v>
       </c>
       <c r="B66" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7195,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524189</v>
+        <v>129522138</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,21 +7206,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494606</v>
+        <v>494375</v>
       </c>
       <c r="R67" t="n">
-        <v>6834497</v>
+        <v>6834215</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B68" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R68" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,60 +7377,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129520975</v>
+        <v>129522294</v>
       </c>
       <c r="B69" t="n">
-        <v>78832</v>
+        <v>98769</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494243</v>
+        <v>494419</v>
       </c>
       <c r="R69" t="n">
-        <v>6834445</v>
+        <v>6834113</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7474,44 +7474,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129522294</v>
+        <v>129521986</v>
       </c>
       <c r="B70" t="n">
-        <v>98768</v>
+        <v>80182</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494419</v>
+        <v>494336</v>
       </c>
       <c r="R70" t="n">
-        <v>6834113</v>
+        <v>6834146</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129521804</v>
+        <v>129524680</v>
       </c>
       <c r="B71" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,21 +7594,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494297</v>
+        <v>494357</v>
       </c>
       <c r="R71" t="n">
-        <v>6834314</v>
+        <v>6834592</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B72" t="n">
-        <v>80180</v>
+        <v>78833</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7691,21 +7691,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R72" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129523011</v>
+        <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>79075</v>
+        <v>79108</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494480</v>
+        <v>494385</v>
       </c>
       <c r="R73" t="n">
-        <v>6834232</v>
+        <v>6834293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,22 +7862,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129522011</v>
+        <v>129521838</v>
       </c>
       <c r="B74" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494385</v>
+        <v>494355</v>
       </c>
       <c r="R74" t="n">
-        <v>6834293</v>
+        <v>6834299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129521838</v>
+        <v>129524606</v>
       </c>
       <c r="B75" t="n">
-        <v>79107</v>
+        <v>80181</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494355</v>
+        <v>494333</v>
       </c>
       <c r="R75" t="n">
-        <v>6834299</v>
+        <v>6834609</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129524606</v>
+        <v>129523011</v>
       </c>
       <c r="B76" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,34 +8079,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494333</v>
+        <v>494480</v>
       </c>
       <c r="R76" t="n">
-        <v>6834609</v>
+        <v>6834232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8153,12 +8153,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8168,7 +8168,7 @@
         <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>129521271</v>
       </c>
       <c r="B78" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>129524119</v>
       </c>
       <c r="B79" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8456,54 +8456,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129520989</v>
+        <v>129522454</v>
       </c>
       <c r="B80" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494262</v>
+        <v>494456</v>
       </c>
       <c r="R80" t="n">
-        <v>6834427</v>
+        <v>6834177</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8565,7 +8556,7 @@
         <v>129522644</v>
       </c>
       <c r="B81" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8668,45 +8659,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522454</v>
+        <v>129520989</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494456</v>
+        <v>494262</v>
       </c>
       <c r="R82" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8765,10 +8765,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522450</v>
+        <v>129524246</v>
       </c>
       <c r="B83" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8800,13 +8800,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494325</v>
+        <v>494560</v>
       </c>
       <c r="R83" t="n">
-        <v>6834177</v>
+        <v>6834565</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129524246</v>
+        <v>129522450</v>
       </c>
       <c r="B84" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8897,13 +8897,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494560</v>
+        <v>494325</v>
       </c>
       <c r="R84" t="n">
-        <v>6834565</v>
+        <v>6834177</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>129520902</v>
       </c>
       <c r="B85" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>129524525</v>
       </c>
       <c r="B86" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>129523899</v>
       </c>
       <c r="B87" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>129521936</v>
       </c>
       <c r="B88" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>129521041</v>
       </c>
       <c r="B89" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>129522147</v>
       </c>
       <c r="B90" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9541,10 +9541,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522027</v>
+        <v>129524791</v>
       </c>
       <c r="B91" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9552,34 +9552,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494337</v>
+        <v>494381</v>
       </c>
       <c r="R91" t="n">
-        <v>6834149</v>
+        <v>6834429</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,71 +9626,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524797</v>
+        <v>129522173</v>
       </c>
       <c r="B92" t="n">
-        <v>92869</v>
+        <v>80181</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494387</v>
+        <v>494418</v>
       </c>
       <c r="R92" t="n">
-        <v>6834437</v>
+        <v>6834113</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9737,44 +9723,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129522173</v>
+        <v>129521897</v>
       </c>
       <c r="B93" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9784,10 +9770,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494418</v>
+        <v>494323</v>
       </c>
       <c r="R93" t="n">
-        <v>6834113</v>
+        <v>6834131</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,10 +9832,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129524791</v>
+        <v>129522027</v>
       </c>
       <c r="B94" t="n">
-        <v>79075</v>
+        <v>80182</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9857,34 +9843,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494381</v>
+        <v>494337</v>
       </c>
       <c r="R94" t="n">
-        <v>6834429</v>
+        <v>6834149</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9931,57 +9917,71 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521897</v>
+        <v>129524797</v>
       </c>
       <c r="B95" t="n">
-        <v>98768</v>
+        <v>92870</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494323</v>
+        <v>494387</v>
       </c>
       <c r="R95" t="n">
-        <v>6834131</v>
+        <v>6834437</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,12 +10028,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10043,7 +10043,7 @@
         <v>129521475</v>
       </c>
       <c r="B96" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10137,48 +10137,57 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129524273</v>
+        <v>129522632</v>
       </c>
       <c r="B97" t="n">
-        <v>79107</v>
+        <v>98769</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494549</v>
+        <v>494455</v>
       </c>
       <c r="R97" t="n">
-        <v>6834588</v>
+        <v>6834185</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10222,22 +10231,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524530</v>
+        <v>129524273</v>
       </c>
       <c r="B98" t="n">
-        <v>79075</v>
+        <v>79108</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10245,21 +10254,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10269,13 +10278,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494349</v>
+        <v>494549</v>
       </c>
       <c r="R98" t="n">
-        <v>6834653</v>
+        <v>6834588</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10331,10 +10340,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129524130</v>
+        <v>129523005</v>
       </c>
       <c r="B99" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10362,14 +10371,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494537</v>
+        <v>494491</v>
       </c>
       <c r="R99" t="n">
-        <v>6834492</v>
+        <v>6834229</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10416,22 +10425,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129523005</v>
+        <v>129524530</v>
       </c>
       <c r="B100" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10463,10 +10472,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494491</v>
+        <v>494349</v>
       </c>
       <c r="R100" t="n">
-        <v>6834229</v>
+        <v>6834653</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10525,54 +10534,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129522632</v>
+        <v>129524130</v>
       </c>
       <c r="B101" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494455</v>
+        <v>494537</v>
       </c>
       <c r="R101" t="n">
-        <v>6834185</v>
+        <v>6834492</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10631,32 +10631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129524122</v>
+        <v>129522100</v>
       </c>
       <c r="B102" t="n">
-        <v>80181</v>
+        <v>58106</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>103015</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494556</v>
+        <v>494368</v>
       </c>
       <c r="R102" t="n">
-        <v>6834467</v>
+        <v>6834126</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521144</v>
+        <v>129522517</v>
       </c>
       <c r="B103" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,34 +10739,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494222</v>
+        <v>494455</v>
       </c>
       <c r="R103" t="n">
-        <v>6834390</v>
+        <v>6834176</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,12 +10813,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -10828,7 +10828,7 @@
         <v>129521967</v>
       </c>
       <c r="B104" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521418</v>
+        <v>129521144</v>
       </c>
       <c r="B105" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10953,14 +10953,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494176</v>
+        <v>494222</v>
       </c>
       <c r="R105" t="n">
-        <v>6834368</v>
+        <v>6834390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129522341</v>
+        <v>129524122</v>
       </c>
       <c r="B106" t="n">
-        <v>78832</v>
+        <v>80182</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494345</v>
+        <v>494556</v>
       </c>
       <c r="R106" t="n">
-        <v>6834202</v>
+        <v>6834467</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,12 +11104,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11119,7 +11119,7 @@
         <v>129521977</v>
       </c>
       <c r="B107" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522517</v>
+        <v>129521418</v>
       </c>
       <c r="B108" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,21 +11224,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,10 +11248,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494455</v>
+        <v>494176</v>
       </c>
       <c r="R108" t="n">
-        <v>6834176</v>
+        <v>6834368</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11310,48 +11310,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522100</v>
+        <v>129522341</v>
       </c>
       <c r="B109" t="n">
-        <v>58105</v>
+        <v>78833</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494368</v>
+        <v>494345</v>
       </c>
       <c r="R109" t="n">
-        <v>6834126</v>
+        <v>6834202</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11395,12 +11395,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11410,7 +11410,7 @@
         <v>129522819</v>
       </c>
       <c r="B110" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11504,45 +11504,54 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129523028</v>
+        <v>129524619</v>
       </c>
       <c r="B111" t="n">
-        <v>78083</v>
+        <v>98769</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494500</v>
+        <v>494338</v>
       </c>
       <c r="R111" t="n">
-        <v>6834263</v>
+        <v>6834601</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11610,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129521874</v>
+        <v>129523028</v>
       </c>
       <c r="B112" t="n">
-        <v>80180</v>
+        <v>78084</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11621,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11645,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494355</v>
+        <v>494500</v>
       </c>
       <c r="R112" t="n">
-        <v>6834295</v>
+        <v>6834263</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11698,54 +11707,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129524619</v>
+        <v>129521874</v>
       </c>
       <c r="B113" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494338</v>
+        <v>494355</v>
       </c>
       <c r="R113" t="n">
-        <v>6834601</v>
+        <v>6834295</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129521147</v>
+        <v>129524240</v>
       </c>
       <c r="B114" t="n">
-        <v>79075</v>
+        <v>79108</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,37 +11815,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494225</v>
+        <v>494559</v>
       </c>
       <c r="R114" t="n">
-        <v>6834382</v>
+        <v>6834519</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11889,12 +11889,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -11904,7 +11904,7 @@
         <v>129524762</v>
       </c>
       <c r="B115" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11998,10 +11998,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521072</v>
+        <v>129521147</v>
       </c>
       <c r="B116" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12029,14 +12029,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494234</v>
+        <v>494225</v>
       </c>
       <c r="R116" t="n">
-        <v>6834416</v>
+        <v>6834382</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12083,22 +12083,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129524240</v>
+        <v>129521072</v>
       </c>
       <c r="B117" t="n">
-        <v>79107</v>
+        <v>79076</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12130,13 +12130,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494559</v>
+        <v>494234</v>
       </c>
       <c r="R117" t="n">
-        <v>6834519</v>
+        <v>6834416</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521663</v>
+        <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>78833</v>
+        <v>91609</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494242</v>
+        <v>494255</v>
       </c>
       <c r="R118" t="n">
-        <v>6834295</v>
+        <v>6834250</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129523234</v>
+        <v>129524747</v>
       </c>
       <c r="B119" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494472</v>
+        <v>494401</v>
       </c>
       <c r="R119" t="n">
-        <v>6834268</v>
+        <v>6834640</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129521664</v>
+        <v>129524381</v>
       </c>
       <c r="B120" t="n">
-        <v>91608</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494255</v>
+        <v>494485</v>
       </c>
       <c r="R120" t="n">
-        <v>6834250</v>
+        <v>6834612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129524747</v>
+        <v>129521663</v>
       </c>
       <c r="B121" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494401</v>
+        <v>494242</v>
       </c>
       <c r="R121" t="n">
-        <v>6834640</v>
+        <v>6834295</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129524381</v>
+        <v>129523234</v>
       </c>
       <c r="B122" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494485</v>
+        <v>494472</v>
       </c>
       <c r="R122" t="n">
-        <v>6834612</v>
+        <v>6834268</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,12 +12665,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12680,7 +12680,7 @@
         <v>129522783</v>
       </c>
       <c r="B123" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>129523308</v>
       </c>
       <c r="B124" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>129521635</v>
       </c>
       <c r="B125" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129522736</v>
+        <v>129521002</v>
       </c>
       <c r="B126" t="n">
-        <v>91608</v>
+        <v>79076</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494443</v>
+        <v>494241</v>
       </c>
       <c r="R126" t="n">
-        <v>6834230</v>
+        <v>6834425</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13068,7 +13068,7 @@
         <v>129522903</v>
       </c>
       <c r="B127" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129521002</v>
+        <v>129522736</v>
       </c>
       <c r="B128" t="n">
-        <v>79075</v>
+        <v>91609</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494241</v>
+        <v>494443</v>
       </c>
       <c r="R128" t="n">
-        <v>6834425</v>
+        <v>6834230</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129521823</v>
+        <v>129522012</v>
       </c>
       <c r="B129" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13294,13 +13294,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494360</v>
+        <v>494337</v>
       </c>
       <c r="R129" t="n">
-        <v>6834206</v>
+        <v>6834146</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13356,10 +13356,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129522012</v>
+        <v>129521823</v>
       </c>
       <c r="B130" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13391,13 +13391,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494337</v>
+        <v>494360</v>
       </c>
       <c r="R130" t="n">
-        <v>6834146</v>
+        <v>6834206</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>129524581</v>
       </c>
       <c r="B131" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521302</v>
+        <v>129520912</v>
       </c>
       <c r="B132" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13581,17 +13581,17 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494215</v>
+        <v>494290</v>
       </c>
       <c r="R132" t="n">
-        <v>6834362</v>
+        <v>6834454</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13635,22 +13635,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129520912</v>
+        <v>129521752</v>
       </c>
       <c r="B133" t="n">
-        <v>79075</v>
+        <v>78742</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13658,34 +13658,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494290</v>
+        <v>494258</v>
       </c>
       <c r="R133" t="n">
-        <v>6834454</v>
+        <v>6834310</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13732,22 +13732,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B134" t="n">
-        <v>78741</v>
+        <v>79076</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,21 +13755,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13779,13 +13779,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R134" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>129521403</v>
       </c>
       <c r="B135" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>129524667</v>
       </c>
       <c r="B136" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>129522065</v>
       </c>
       <c r="B137" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -4955,7 +4955,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129524779</v>
+        <v>129524785</v>
       </c>
       <c r="B44" t="n">
         <v>79076</v>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494423</v>
+        <v>494405</v>
       </c>
       <c r="R44" t="n">
-        <v>6834463</v>
+        <v>6834446</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5052,7 +5052,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129524785</v>
+        <v>129524779</v>
       </c>
       <c r="B45" t="n">
         <v>79076</v>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494405</v>
+        <v>494423</v>
       </c>
       <c r="R45" t="n">
-        <v>6834446</v>
+        <v>6834463</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129520992</v>
+        <v>129522706</v>
       </c>
       <c r="B51" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494221</v>
+        <v>494454</v>
       </c>
       <c r="R51" t="n">
-        <v>6834431</v>
+        <v>6834225</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521655</v>
+        <v>129521826</v>
       </c>
       <c r="B52" t="n">
-        <v>78742</v>
+        <v>80182</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494247</v>
+        <v>494361</v>
       </c>
       <c r="R52" t="n">
-        <v>6834296</v>
+        <v>6834336</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521887</v>
+        <v>129520992</v>
       </c>
       <c r="B53" t="n">
-        <v>80210</v>
+        <v>78742</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494350</v>
+        <v>494221</v>
       </c>
       <c r="R53" t="n">
-        <v>6834298</v>
+        <v>6834431</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522129</v>
+        <v>129521655</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,37 +5936,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494397</v>
+        <v>494247</v>
       </c>
       <c r="R54" t="n">
-        <v>6834116</v>
+        <v>6834296</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,44 +6010,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522706</v>
+        <v>129521887</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>80210</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6057,13 +6057,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494454</v>
+        <v>494350</v>
       </c>
       <c r="R55" t="n">
-        <v>6834225</v>
+        <v>6834298</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6119,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521826</v>
+        <v>129522129</v>
       </c>
       <c r="B56" t="n">
-        <v>80182</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,34 +6130,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494361</v>
+        <v>494397</v>
       </c>
       <c r="R56" t="n">
-        <v>6834336</v>
+        <v>6834116</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6992,54 +6992,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129524059</v>
+        <v>129522151</v>
       </c>
       <c r="B65" t="n">
-        <v>98769</v>
+        <v>78833</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494582</v>
+        <v>494385</v>
       </c>
       <c r="R65" t="n">
-        <v>6834361</v>
+        <v>6834229</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7098,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129522151</v>
+        <v>129522138</v>
       </c>
       <c r="B66" t="n">
-        <v>78833</v>
+        <v>79666</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7100,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,13 +7124,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494385</v>
+        <v>494375</v>
       </c>
       <c r="R66" t="n">
-        <v>6834229</v>
+        <v>6834215</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7195,48 +7186,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129522138</v>
+        <v>129524059</v>
       </c>
       <c r="B67" t="n">
-        <v>79666</v>
+        <v>98769</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494375</v>
+        <v>494582</v>
       </c>
       <c r="R67" t="n">
-        <v>6834215</v>
+        <v>6834361</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524119</v>
+        <v>129524246</v>
       </c>
       <c r="B79" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,34 +8370,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494556</v>
+        <v>494560</v>
       </c>
       <c r="R79" t="n">
-        <v>6834467</v>
+        <v>6834565</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8444,19 +8444,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B80" t="n">
         <v>79076</v>
@@ -8487,17 +8487,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R80" t="n">
         <v>6834177</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8541,66 +8541,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129522644</v>
+        <v>129524119</v>
       </c>
       <c r="B81" t="n">
-        <v>98769</v>
+        <v>80181</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494450</v>
+        <v>494556</v>
       </c>
       <c r="R81" t="n">
-        <v>6834178</v>
+        <v>6834467</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8659,54 +8650,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129520989</v>
+        <v>129522454</v>
       </c>
       <c r="B82" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494262</v>
+        <v>494456</v>
       </c>
       <c r="R82" t="n">
-        <v>6834427</v>
+        <v>6834177</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8765,45 +8747,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129524246</v>
+        <v>129522644</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494560</v>
+        <v>494450</v>
       </c>
       <c r="R83" t="n">
-        <v>6834565</v>
+        <v>6834178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,60 +8841,69 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522450</v>
+        <v>129520989</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494325</v>
+        <v>494262</v>
       </c>
       <c r="R84" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8947,12 +8947,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -11504,54 +11504,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129524619</v>
+        <v>129523028</v>
       </c>
       <c r="B111" t="n">
-        <v>98769</v>
+        <v>78084</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494338</v>
+        <v>494500</v>
       </c>
       <c r="R111" t="n">
-        <v>6834601</v>
+        <v>6834263</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11610,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129523028</v>
+        <v>129521874</v>
       </c>
       <c r="B112" t="n">
-        <v>78084</v>
+        <v>80181</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11621,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11645,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494500</v>
+        <v>494355</v>
       </c>
       <c r="R112" t="n">
-        <v>6834263</v>
+        <v>6834295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11707,45 +11698,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129521874</v>
+        <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494355</v>
+        <v>494338</v>
       </c>
       <c r="R113" t="n">
-        <v>6834295</v>
+        <v>6834601</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522783</v>
+        <v>129522736</v>
       </c>
       <c r="B123" t="n">
-        <v>79108</v>
+        <v>91609</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494456</v>
+        <v>494443</v>
       </c>
       <c r="R123" t="n">
-        <v>6834228</v>
+        <v>6834230</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129523308</v>
+        <v>129522012</v>
       </c>
       <c r="B124" t="n">
-        <v>78742</v>
+        <v>80181</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,37 +12785,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494520</v>
+        <v>494337</v>
       </c>
       <c r="R124" t="n">
-        <v>6834279</v>
+        <v>6834146</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12859,22 +12859,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129521635</v>
+        <v>129521823</v>
       </c>
       <c r="B125" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,37 +12882,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494214</v>
+        <v>494360</v>
       </c>
       <c r="R125" t="n">
-        <v>6834306</v>
+        <v>6834206</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12956,22 +12956,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521002</v>
+        <v>129524581</v>
       </c>
       <c r="B126" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494241</v>
+        <v>494323</v>
       </c>
       <c r="R126" t="n">
-        <v>6834425</v>
+        <v>6834627</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13065,10 +13065,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522903</v>
+        <v>129522783</v>
       </c>
       <c r="B127" t="n">
-        <v>79076</v>
+        <v>79108</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494466</v>
+        <v>494456</v>
       </c>
       <c r="R127" t="n">
-        <v>6834211</v>
+        <v>6834228</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129522736</v>
+        <v>129523308</v>
       </c>
       <c r="B128" t="n">
-        <v>91609</v>
+        <v>78742</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,13 +13197,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494443</v>
+        <v>494520</v>
       </c>
       <c r="R128" t="n">
-        <v>6834230</v>
+        <v>6834279</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129522012</v>
+        <v>129521635</v>
       </c>
       <c r="B129" t="n">
-        <v>80181</v>
+        <v>78742</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,37 +13270,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494337</v>
+        <v>494214</v>
       </c>
       <c r="R129" t="n">
-        <v>6834146</v>
+        <v>6834306</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13344,19 +13344,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129521823</v>
+        <v>129521002</v>
       </c>
       <c r="B130" t="n">
         <v>79076</v>
@@ -13387,17 +13387,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494360</v>
+        <v>494241</v>
       </c>
       <c r="R130" t="n">
-        <v>6834206</v>
+        <v>6834425</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13441,22 +13441,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129524581</v>
+        <v>129522903</v>
       </c>
       <c r="B131" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494323</v>
+        <v>494466</v>
       </c>
       <c r="R131" t="n">
-        <v>6834627</v>
+        <v>6834211</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129520912</v>
+        <v>129521752</v>
       </c>
       <c r="B132" t="n">
-        <v>79076</v>
+        <v>78742</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,34 +13561,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494290</v>
+        <v>494258</v>
       </c>
       <c r="R132" t="n">
-        <v>6834454</v>
+        <v>6834310</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13635,22 +13635,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B133" t="n">
-        <v>78742</v>
+        <v>79076</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13658,21 +13658,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13682,13 +13682,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R133" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521302</v>
+        <v>129520912</v>
       </c>
       <c r="B134" t="n">
         <v>79076</v>
@@ -13775,17 +13775,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494215</v>
+        <v>494290</v>
       </c>
       <c r="R134" t="n">
-        <v>6834362</v>
+        <v>6834454</v>
       </c>
       <c r="S134" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13829,12 +13829,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14044,45 +14044,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129522065</v>
+        <v>129521085</v>
       </c>
       <c r="B137" t="n">
-        <v>78742</v>
+        <v>98769</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494373</v>
+        <v>494228</v>
       </c>
       <c r="R137" t="n">
-        <v>6834247</v>
+        <v>6834405</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14129,57 +14129,57 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129521085</v>
+        <v>129522065</v>
       </c>
       <c r="B138" t="n">
-        <v>98769</v>
+        <v>78742</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494228</v>
+        <v>494373</v>
       </c>
       <c r="R138" t="n">
-        <v>6834405</v>
+        <v>6834247</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14226,12 +14226,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1739,7 +1739,7 @@
         <v>129476557</v>
       </c>
       <c r="B11" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>129512476</v>
       </c>
       <c r="B14" t="n">
-        <v>80182</v>
+        <v>80187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129512298</v>
+        <v>129513963</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,14 +2173,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494611</v>
+        <v>494311</v>
       </c>
       <c r="R15" t="n">
-        <v>6834107</v>
+        <v>6834701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513963</v>
+        <v>129513412</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494311</v>
+        <v>494427</v>
       </c>
       <c r="R16" t="n">
-        <v>6834701</v>
+        <v>6834434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129513412</v>
+        <v>129512298</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494427</v>
+        <v>494611</v>
       </c>
       <c r="R17" t="n">
-        <v>6834434</v>
+        <v>6834107</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2436,7 +2436,7 @@
         <v>129512195</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129512125</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>129513122</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>129511985</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>129511911</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129511957</v>
+        <v>129512105</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494635</v>
+        <v>494664</v>
       </c>
       <c r="R23" t="n">
-        <v>6834347</v>
+        <v>6834295</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,10 +3015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129512105</v>
+        <v>129511957</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494664</v>
+        <v>494635</v>
       </c>
       <c r="R24" t="n">
-        <v>6834295</v>
+        <v>6834347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
         <v>129512361</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>129512918</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>129511943</v>
       </c>
       <c r="B27" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>129512658</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>129513370</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B31" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R31" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R32" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
         <v>129513741</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>129513342</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>129512470</v>
       </c>
       <c r="B35" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>129512771</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>129512788</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>129512556</v>
       </c>
       <c r="B38" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>129520952</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>129522417</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>129524342</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>129521092</v>
       </c>
       <c r="B43" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>129524785</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>129524779</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>129522893</v>
       </c>
       <c r="B46" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>129524385</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129522256</v>
+        <v>129524595</v>
       </c>
       <c r="B48" t="n">
-        <v>78834</v>
+        <v>80186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494384</v>
+        <v>494349</v>
       </c>
       <c r="R48" t="n">
-        <v>6834211</v>
+        <v>6834611</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129521425</v>
+        <v>129522256</v>
       </c>
       <c r="B49" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494187</v>
+        <v>494384</v>
       </c>
       <c r="R49" t="n">
-        <v>6834373</v>
+        <v>6834211</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129524595</v>
+        <v>129521425</v>
       </c>
       <c r="B50" t="n">
-        <v>80181</v>
+        <v>78839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494349</v>
+        <v>494187</v>
       </c>
       <c r="R50" t="n">
-        <v>6834611</v>
+        <v>6834373</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129522706</v>
+        <v>129521826</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494454</v>
+        <v>494361</v>
       </c>
       <c r="R51" t="n">
-        <v>6834225</v>
+        <v>6834336</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521826</v>
+        <v>129520992</v>
       </c>
       <c r="B52" t="n">
-        <v>80182</v>
+        <v>78747</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494361</v>
+        <v>494221</v>
       </c>
       <c r="R52" t="n">
-        <v>6834336</v>
+        <v>6834431</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129520992</v>
+        <v>129521655</v>
       </c>
       <c r="B53" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494221</v>
+        <v>494247</v>
       </c>
       <c r="R53" t="n">
-        <v>6834431</v>
+        <v>6834296</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521655</v>
+        <v>129522129</v>
       </c>
       <c r="B54" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,37 +5936,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494247</v>
+        <v>494397</v>
       </c>
       <c r="R54" t="n">
-        <v>6834296</v>
+        <v>6834116</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,44 +6010,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129521887</v>
+        <v>129522706</v>
       </c>
       <c r="B55" t="n">
-        <v>80210</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6057,13 +6057,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494350</v>
+        <v>494454</v>
       </c>
       <c r="R55" t="n">
-        <v>6834298</v>
+        <v>6834225</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6119,45 +6119,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129522129</v>
+        <v>129521887</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>80215</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494397</v>
+        <v>494350</v>
       </c>
       <c r="R56" t="n">
-        <v>6834116</v>
+        <v>6834298</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,22 +6204,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521358</v>
+        <v>129524189</v>
       </c>
       <c r="B57" t="n">
-        <v>79108</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6227,21 +6227,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6251,13 +6251,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494221</v>
+        <v>494606</v>
       </c>
       <c r="R57" t="n">
-        <v>6834353</v>
+        <v>6834497</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129521131</v>
+        <v>129522857</v>
       </c>
       <c r="B58" t="n">
-        <v>79108</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,21 +6324,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6348,13 +6348,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494230</v>
+        <v>494475</v>
       </c>
       <c r="R58" t="n">
-        <v>6834385</v>
+        <v>6834232</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522432</v>
+        <v>129522151</v>
       </c>
       <c r="B59" t="n">
-        <v>79108</v>
+        <v>78838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6421,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494325</v>
+        <v>494385</v>
       </c>
       <c r="R59" t="n">
-        <v>6834177</v>
+        <v>6834229</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524189</v>
+        <v>129524775</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6542,13 +6542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494606</v>
+        <v>494416</v>
       </c>
       <c r="R60" t="n">
-        <v>6834497</v>
+        <v>6834464</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6604,45 +6604,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129522857</v>
+        <v>129524392</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494475</v>
+        <v>494486</v>
       </c>
       <c r="R61" t="n">
-        <v>6834232</v>
+        <v>6834613</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6689,22 +6689,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524775</v>
+        <v>129521358</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79113</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6712,21 +6712,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494416</v>
+        <v>494221</v>
       </c>
       <c r="R62" t="n">
-        <v>6834464</v>
+        <v>6834353</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6798,10 +6798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129521656</v>
+        <v>129521131</v>
       </c>
       <c r="B63" t="n">
-        <v>80182</v>
+        <v>79113</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,37 +6809,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494219</v>
+        <v>494230</v>
       </c>
       <c r="R63" t="n">
-        <v>6834291</v>
+        <v>6834385</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6883,60 +6883,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524392</v>
+        <v>129522432</v>
       </c>
       <c r="B64" t="n">
-        <v>92870</v>
+        <v>79113</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494486</v>
+        <v>494325</v>
       </c>
       <c r="R64" t="n">
-        <v>6834613</v>
+        <v>6834177</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6980,22 +6980,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129522151</v>
+        <v>129521656</v>
       </c>
       <c r="B65" t="n">
-        <v>78833</v>
+        <v>80187</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,37 +7003,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494385</v>
+        <v>494219</v>
       </c>
       <c r="R65" t="n">
-        <v>6834229</v>
+        <v>6834291</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7077,12 +7077,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7092,7 +7092,7 @@
         <v>129522138</v>
       </c>
       <c r="B66" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>129524059</v>
       </c>
       <c r="B67" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521804</v>
+        <v>129521986</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494297</v>
+        <v>494336</v>
       </c>
       <c r="R68" t="n">
-        <v>6834314</v>
+        <v>6834146</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,60 +7377,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129522294</v>
+        <v>129520975</v>
       </c>
       <c r="B69" t="n">
-        <v>98769</v>
+        <v>78838</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494419</v>
+        <v>494243</v>
       </c>
       <c r="R69" t="n">
-        <v>6834113</v>
+        <v>6834445</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7474,22 +7474,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129521986</v>
+        <v>129524680</v>
       </c>
       <c r="B70" t="n">
-        <v>80182</v>
+        <v>80186</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,34 +7497,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494336</v>
+        <v>494357</v>
       </c>
       <c r="R70" t="n">
-        <v>6834146</v>
+        <v>6834592</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,22 +7571,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129524680</v>
+        <v>129521804</v>
       </c>
       <c r="B71" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,21 +7594,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494357</v>
+        <v>494297</v>
       </c>
       <c r="R71" t="n">
-        <v>6834592</v>
+        <v>6834314</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7680,48 +7680,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129520975</v>
+        <v>129522294</v>
       </c>
       <c r="B72" t="n">
-        <v>78833</v>
+        <v>98774</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494243</v>
+        <v>494419</v>
       </c>
       <c r="R72" t="n">
-        <v>6834445</v>
+        <v>6834113</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7765,12 +7765,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7780,7 +7780,7 @@
         <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>129521838</v>
       </c>
       <c r="B74" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>129524606</v>
       </c>
       <c r="B75" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>129523011</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8165,48 +8165,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524147</v>
+        <v>129522644</v>
       </c>
       <c r="B77" t="n">
-        <v>79108</v>
+        <v>98774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494596</v>
+        <v>494450</v>
       </c>
       <c r="R77" t="n">
-        <v>6834467</v>
+        <v>6834178</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,22 +8259,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129521271</v>
+        <v>129524147</v>
       </c>
       <c r="B78" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8297,10 +8306,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494237</v>
+        <v>494596</v>
       </c>
       <c r="R78" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8359,10 +8368,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524246</v>
+        <v>129521271</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>79113</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,21 +8379,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8394,13 +8403,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494560</v>
+        <v>494237</v>
       </c>
       <c r="R79" t="n">
-        <v>6834565</v>
+        <v>6834397</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8456,10 +8465,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522450</v>
+        <v>129524119</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8467,37 +8476,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494325</v>
+        <v>494556</v>
       </c>
       <c r="R80" t="n">
-        <v>6834177</v>
+        <v>6834467</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8541,22 +8550,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129524119</v>
+        <v>129524246</v>
       </c>
       <c r="B81" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8564,34 +8573,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494556</v>
+        <v>494560</v>
       </c>
       <c r="R81" t="n">
-        <v>6834467</v>
+        <v>6834565</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,22 +8647,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8681,17 +8690,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R82" t="n">
         <v>6834177</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8735,66 +8744,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522644</v>
+        <v>129522454</v>
       </c>
       <c r="B83" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494450</v>
+        <v>494456</v>
       </c>
       <c r="R83" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8856,7 +8856,7 @@
         <v>129520989</v>
       </c>
       <c r="B84" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129520902</v>
+        <v>129523899</v>
       </c>
       <c r="B85" t="n">
-        <v>79076</v>
+        <v>57896</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8970,37 +8970,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494278</v>
+        <v>494543</v>
       </c>
       <c r="R85" t="n">
-        <v>6834456</v>
+        <v>6834251</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9044,22 +9044,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129524525</v>
+        <v>129520902</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9087,14 +9087,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494354</v>
+        <v>494278</v>
       </c>
       <c r="R86" t="n">
-        <v>6834662</v>
+        <v>6834456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9141,22 +9141,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129523899</v>
+        <v>129524525</v>
       </c>
       <c r="B87" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9164,37 +9164,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494543</v>
+        <v>494354</v>
       </c>
       <c r="R87" t="n">
-        <v>6834251</v>
+        <v>6834662</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>129521936</v>
       </c>
       <c r="B88" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>129521041</v>
       </c>
       <c r="B89" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>129522147</v>
       </c>
       <c r="B90" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9541,10 +9541,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129524791</v>
+        <v>129522173</v>
       </c>
       <c r="B91" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9552,34 +9552,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494381</v>
+        <v>494418</v>
       </c>
       <c r="R91" t="n">
-        <v>6834429</v>
+        <v>6834113</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,22 +9626,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129522173</v>
+        <v>129524791</v>
       </c>
       <c r="B92" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9649,34 +9649,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494418</v>
+        <v>494381</v>
       </c>
       <c r="R92" t="n">
-        <v>6834113</v>
+        <v>6834429</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,57 +9723,71 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129521897</v>
+        <v>129524797</v>
       </c>
       <c r="B93" t="n">
-        <v>98769</v>
+        <v>92875</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494323</v>
+        <v>494387</v>
       </c>
       <c r="R93" t="n">
-        <v>6834131</v>
+        <v>6834437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9820,22 +9834,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129522027</v>
+        <v>129521475</v>
       </c>
       <c r="B94" t="n">
-        <v>80182</v>
+        <v>78839</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9843,21 +9857,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9867,10 +9881,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494337</v>
+        <v>494181</v>
       </c>
       <c r="R94" t="n">
-        <v>6834149</v>
+        <v>6834367</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9929,59 +9943,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129524797</v>
+        <v>129521897</v>
       </c>
       <c r="B95" t="n">
-        <v>92870</v>
+        <v>98774</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494387</v>
+        <v>494323</v>
       </c>
       <c r="R95" t="n">
-        <v>6834437</v>
+        <v>6834131</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,22 +10028,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521475</v>
+        <v>129522027</v>
       </c>
       <c r="B96" t="n">
-        <v>78834</v>
+        <v>80187</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494181</v>
+        <v>494337</v>
       </c>
       <c r="R96" t="n">
-        <v>6834367</v>
+        <v>6834149</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10137,57 +10137,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129522632</v>
+        <v>129524273</v>
       </c>
       <c r="B97" t="n">
-        <v>98769</v>
+        <v>79113</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494455</v>
+        <v>494549</v>
       </c>
       <c r="R97" t="n">
-        <v>6834185</v>
+        <v>6834588</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10231,22 +10222,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524273</v>
+        <v>129524130</v>
       </c>
       <c r="B98" t="n">
-        <v>79108</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10254,37 +10245,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494549</v>
+        <v>494537</v>
       </c>
       <c r="R98" t="n">
-        <v>6834588</v>
+        <v>6834492</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10328,12 +10319,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10343,7 +10334,7 @@
         <v>129523005</v>
       </c>
       <c r="B99" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10440,7 +10431,7 @@
         <v>129524530</v>
       </c>
       <c r="B100" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10534,45 +10525,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129524130</v>
+        <v>129522632</v>
       </c>
       <c r="B101" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494537</v>
+        <v>494455</v>
       </c>
       <c r="R101" t="n">
-        <v>6834492</v>
+        <v>6834185</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10631,32 +10631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129522100</v>
+        <v>129524122</v>
       </c>
       <c r="B102" t="n">
-        <v>58106</v>
+        <v>80187</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103015</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494368</v>
+        <v>494556</v>
       </c>
       <c r="R102" t="n">
-        <v>6834126</v>
+        <v>6834467</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129522517</v>
+        <v>129521144</v>
       </c>
       <c r="B103" t="n">
-        <v>78834</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,34 +10739,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494455</v>
+        <v>494222</v>
       </c>
       <c r="R103" t="n">
-        <v>6834176</v>
+        <v>6834390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,22 +10813,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521967</v>
+        <v>129521418</v>
       </c>
       <c r="B104" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10856,14 +10856,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494346</v>
+        <v>494176</v>
       </c>
       <c r="R104" t="n">
-        <v>6834277</v>
+        <v>6834368</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521144</v>
+        <v>129522341</v>
       </c>
       <c r="B105" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,21 +10933,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494222</v>
+        <v>494345</v>
       </c>
       <c r="R105" t="n">
-        <v>6834390</v>
+        <v>6834202</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129524122</v>
+        <v>129521967</v>
       </c>
       <c r="B106" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494556</v>
+        <v>494346</v>
       </c>
       <c r="R106" t="n">
-        <v>6834467</v>
+        <v>6834277</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,12 +11104,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11119,7 +11119,7 @@
         <v>129521977</v>
       </c>
       <c r="B107" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11213,32 +11213,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521418</v>
+        <v>129522100</v>
       </c>
       <c r="B108" t="n">
-        <v>79076</v>
+        <v>58106</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494176</v>
+        <v>494368</v>
       </c>
       <c r="R108" t="n">
-        <v>6834368</v>
+        <v>6834126</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11310,10 +11310,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522341</v>
+        <v>129522517</v>
       </c>
       <c r="B109" t="n">
-        <v>78833</v>
+        <v>78839</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11321,34 +11321,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494345</v>
+        <v>494455</v>
       </c>
       <c r="R109" t="n">
-        <v>6834202</v>
+        <v>6834176</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11395,12 +11395,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11410,7 +11410,7 @@
         <v>129522819</v>
       </c>
       <c r="B110" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>129523028</v>
       </c>
       <c r="B111" t="n">
-        <v>78084</v>
+        <v>78089</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>129521874</v>
       </c>
       <c r="B112" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524240</v>
+        <v>129521072</v>
       </c>
       <c r="B114" t="n">
-        <v>79108</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494559</v>
+        <v>494234</v>
       </c>
       <c r="R114" t="n">
-        <v>6834519</v>
+        <v>6834416</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>129524762</v>
       </c>
       <c r="B115" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>129521147</v>
       </c>
       <c r="B116" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129521072</v>
+        <v>129524240</v>
       </c>
       <c r="B117" t="n">
-        <v>79076</v>
+        <v>79113</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12130,13 +12130,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494234</v>
+        <v>494559</v>
       </c>
       <c r="R117" t="n">
-        <v>6834416</v>
+        <v>6834519</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521664</v>
+        <v>129524747</v>
       </c>
       <c r="B118" t="n">
-        <v>91609</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494255</v>
+        <v>494401</v>
       </c>
       <c r="R118" t="n">
-        <v>6834250</v>
+        <v>6834640</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12289,10 +12289,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524747</v>
+        <v>129524381</v>
       </c>
       <c r="B119" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12320,14 +12320,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494401</v>
+        <v>494485</v>
       </c>
       <c r="R119" t="n">
-        <v>6834640</v>
+        <v>6834612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12386,10 +12386,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129524381</v>
+        <v>129521664</v>
       </c>
       <c r="B120" t="n">
-        <v>79076</v>
+        <v>91614</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494485</v>
+        <v>494255</v>
       </c>
       <c r="R120" t="n">
-        <v>6834612</v>
+        <v>6834250</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12486,7 +12486,7 @@
         <v>129521663</v>
       </c>
       <c r="B121" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>129523234</v>
       </c>
       <c r="B122" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>129522736</v>
       </c>
       <c r="B123" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522012</v>
+        <v>129522783</v>
       </c>
       <c r="B124" t="n">
-        <v>80181</v>
+        <v>79113</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,34 +12785,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494337</v>
+        <v>494456</v>
       </c>
       <c r="R124" t="n">
-        <v>6834146</v>
+        <v>6834228</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12859,22 +12859,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129521823</v>
+        <v>129523308</v>
       </c>
       <c r="B125" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,37 +12882,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494360</v>
+        <v>494520</v>
       </c>
       <c r="R125" t="n">
-        <v>6834206</v>
+        <v>6834279</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12956,22 +12956,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129524581</v>
+        <v>129521635</v>
       </c>
       <c r="B126" t="n">
-        <v>80181</v>
+        <v>78747</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494323</v>
+        <v>494214</v>
       </c>
       <c r="R126" t="n">
-        <v>6834627</v>
+        <v>6834306</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13065,10 +13065,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522783</v>
+        <v>129521002</v>
       </c>
       <c r="B127" t="n">
-        <v>79108</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494456</v>
+        <v>494241</v>
       </c>
       <c r="R127" t="n">
-        <v>6834228</v>
+        <v>6834425</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129523308</v>
+        <v>129524581</v>
       </c>
       <c r="B128" t="n">
-        <v>78742</v>
+        <v>80186</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,13 +13197,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494520</v>
+        <v>494323</v>
       </c>
       <c r="R128" t="n">
-        <v>6834279</v>
+        <v>6834627</v>
       </c>
       <c r="S128" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129521635</v>
+        <v>129521823</v>
       </c>
       <c r="B129" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,37 +13270,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494214</v>
+        <v>494360</v>
       </c>
       <c r="R129" t="n">
-        <v>6834306</v>
+        <v>6834206</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13344,22 +13344,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129521002</v>
+        <v>129522903</v>
       </c>
       <c r="B130" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494241</v>
+        <v>494466</v>
       </c>
       <c r="R130" t="n">
-        <v>6834425</v>
+        <v>6834211</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522903</v>
+        <v>129522012</v>
       </c>
       <c r="B131" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,34 +13464,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494466</v>
+        <v>494337</v>
       </c>
       <c r="R131" t="n">
-        <v>6834211</v>
+        <v>6834146</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13538,22 +13538,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521752</v>
+        <v>129521302</v>
       </c>
       <c r="B132" t="n">
-        <v>78742</v>
+        <v>79081</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494258</v>
+        <v>494215</v>
       </c>
       <c r="R132" t="n">
-        <v>6834310</v>
+        <v>6834362</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129521302</v>
+        <v>129520912</v>
       </c>
       <c r="B133" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13678,17 +13678,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494215</v>
+        <v>494290</v>
       </c>
       <c r="R133" t="n">
-        <v>6834362</v>
+        <v>6834454</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13732,22 +13732,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129520912</v>
+        <v>129521752</v>
       </c>
       <c r="B134" t="n">
-        <v>79076</v>
+        <v>78747</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,34 +13755,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494290</v>
+        <v>494258</v>
       </c>
       <c r="R134" t="n">
-        <v>6834454</v>
+        <v>6834310</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13829,57 +13829,57 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521403</v>
+        <v>129521085</v>
       </c>
       <c r="B135" t="n">
-        <v>90620</v>
+        <v>98774</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494199</v>
+        <v>494228</v>
       </c>
       <c r="R135" t="n">
-        <v>6834366</v>
+        <v>6834405</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13926,22 +13926,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524667</v>
+        <v>129521403</v>
       </c>
       <c r="B136" t="n">
-        <v>80182</v>
+        <v>90625</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13949,43 +13949,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494352</v>
+        <v>494199</v>
       </c>
       <c r="R136" t="n">
-        <v>6834596</v>
+        <v>6834366</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14044,45 +14035,54 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129521085</v>
+        <v>129524667</v>
       </c>
       <c r="B137" t="n">
-        <v>98769</v>
+        <v>80187</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494228</v>
+        <v>494352</v>
       </c>
       <c r="R137" t="n">
-        <v>6834405</v>
+        <v>6834596</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14129,12 +14129,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -14144,7 +14144,7 @@
         <v>129522065</v>
       </c>
       <c r="B138" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129522893</v>
+        <v>129524385</v>
       </c>
       <c r="B46" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494477</v>
+        <v>494528</v>
       </c>
       <c r="R46" t="n">
-        <v>6834229</v>
+        <v>6834660</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524385</v>
+        <v>129524595</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494528</v>
+        <v>494349</v>
       </c>
       <c r="R47" t="n">
-        <v>6834660</v>
+        <v>6834611</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129524595</v>
+        <v>129522893</v>
       </c>
       <c r="B48" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494349</v>
+        <v>494477</v>
       </c>
       <c r="R48" t="n">
-        <v>6834611</v>
+        <v>6834229</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129521826</v>
+        <v>129522129</v>
       </c>
       <c r="B51" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,34 +5645,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494361</v>
+        <v>494397</v>
       </c>
       <c r="R51" t="n">
-        <v>6834336</v>
+        <v>6834116</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5719,22 +5719,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129520992</v>
+        <v>129522706</v>
       </c>
       <c r="B52" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,21 +5742,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494221</v>
+        <v>494454</v>
       </c>
       <c r="R52" t="n">
-        <v>6834431</v>
+        <v>6834225</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521655</v>
+        <v>129521887</v>
       </c>
       <c r="B53" t="n">
-        <v>78747</v>
+        <v>80215</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494247</v>
+        <v>494350</v>
       </c>
       <c r="R53" t="n">
-        <v>6834296</v>
+        <v>6834298</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522129</v>
+        <v>129521826</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,34 +5936,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494397</v>
+        <v>494361</v>
       </c>
       <c r="R54" t="n">
-        <v>6834116</v>
+        <v>6834336</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6010,22 +6010,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522706</v>
+        <v>129520992</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6033,21 +6033,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494454</v>
+        <v>494221</v>
       </c>
       <c r="R55" t="n">
-        <v>6834225</v>
+        <v>6834431</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521887</v>
+        <v>129521655</v>
       </c>
       <c r="B56" t="n">
-        <v>80215</v>
+        <v>78747</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494350</v>
+        <v>494247</v>
       </c>
       <c r="R56" t="n">
-        <v>6834298</v>
+        <v>6834296</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6216,48 +6216,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129524189</v>
+        <v>129524059</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494606</v>
+        <v>494582</v>
       </c>
       <c r="R57" t="n">
-        <v>6834497</v>
+        <v>6834361</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6313,10 +6322,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129522857</v>
+        <v>129522138</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,21 +6333,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6348,13 +6357,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494475</v>
+        <v>494375</v>
       </c>
       <c r="R58" t="n">
-        <v>6834232</v>
+        <v>6834215</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6410,10 +6419,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522151</v>
+        <v>129522857</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6421,21 +6430,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6445,10 +6454,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494385</v>
+        <v>494475</v>
       </c>
       <c r="R59" t="n">
-        <v>6834229</v>
+        <v>6834232</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,10 +6516,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524775</v>
+        <v>129521656</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6518,37 +6527,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494416</v>
+        <v>494219</v>
       </c>
       <c r="R60" t="n">
-        <v>6834464</v>
+        <v>6834291</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6592,57 +6601,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129524392</v>
+        <v>129521358</v>
       </c>
       <c r="B61" t="n">
-        <v>92875</v>
+        <v>79113</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494486</v>
+        <v>494221</v>
       </c>
       <c r="R61" t="n">
-        <v>6834613</v>
+        <v>6834353</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6689,19 +6698,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129521358</v>
+        <v>129521131</v>
       </c>
       <c r="B62" t="n">
         <v>79113</v>
@@ -6736,13 +6745,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494221</v>
+        <v>494230</v>
       </c>
       <c r="R62" t="n">
-        <v>6834353</v>
+        <v>6834385</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6798,7 +6807,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129521131</v>
+        <v>129522432</v>
       </c>
       <c r="B63" t="n">
         <v>79113</v>
@@ -6833,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494230</v>
+        <v>494325</v>
       </c>
       <c r="R63" t="n">
-        <v>6834385</v>
+        <v>6834177</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6895,48 +6904,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129522432</v>
+        <v>129524392</v>
       </c>
       <c r="B64" t="n">
-        <v>79113</v>
+        <v>92875</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494325</v>
+        <v>494486</v>
       </c>
       <c r="R64" t="n">
-        <v>6834177</v>
+        <v>6834613</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6980,22 +6989,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129521656</v>
+        <v>129524189</v>
       </c>
       <c r="B65" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,37 +7012,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494219</v>
+        <v>494606</v>
       </c>
       <c r="R65" t="n">
-        <v>6834291</v>
+        <v>6834497</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7077,22 +7086,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129522138</v>
+        <v>129522151</v>
       </c>
       <c r="B66" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,13 +7133,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494375</v>
+        <v>494385</v>
       </c>
       <c r="R66" t="n">
-        <v>6834215</v>
+        <v>6834229</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7186,54 +7195,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524059</v>
+        <v>129524775</v>
       </c>
       <c r="B67" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494582</v>
+        <v>494416</v>
       </c>
       <c r="R67" t="n">
-        <v>6834361</v>
+        <v>6834464</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521986</v>
+        <v>129520975</v>
       </c>
       <c r="B68" t="n">
-        <v>80187</v>
+        <v>78838</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,37 +7303,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494336</v>
+        <v>494243</v>
       </c>
       <c r="R68" t="n">
-        <v>6834146</v>
+        <v>6834445</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129520975</v>
+        <v>129521804</v>
       </c>
       <c r="B69" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494243</v>
+        <v>494297</v>
       </c>
       <c r="R69" t="n">
-        <v>6834445</v>
+        <v>6834314</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129521804</v>
+        <v>129521986</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,37 +7594,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494297</v>
+        <v>494336</v>
       </c>
       <c r="R71" t="n">
-        <v>6834314</v>
+        <v>6834146</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7668,12 +7668,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8165,57 +8165,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129522644</v>
+        <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>98774</v>
+        <v>79113</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494450</v>
+        <v>494596</v>
       </c>
       <c r="R77" t="n">
-        <v>6834178</v>
+        <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8259,19 +8250,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129524147</v>
+        <v>129521271</v>
       </c>
       <c r="B78" t="n">
         <v>79113</v>
@@ -8306,10 +8297,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494596</v>
+        <v>494237</v>
       </c>
       <c r="R78" t="n">
-        <v>6834467</v>
+        <v>6834397</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -8368,10 +8359,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129521271</v>
+        <v>129524119</v>
       </c>
       <c r="B79" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8379,37 +8370,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494237</v>
+        <v>494556</v>
       </c>
       <c r="R79" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8453,57 +8444,66 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129524119</v>
+        <v>129522644</v>
       </c>
       <c r="B80" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494556</v>
+        <v>494450</v>
       </c>
       <c r="R80" t="n">
-        <v>6834467</v>
+        <v>6834178</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8562,45 +8562,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129524246</v>
+        <v>129520989</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494560</v>
+        <v>494262</v>
       </c>
       <c r="R81" t="n">
-        <v>6834565</v>
+        <v>6834427</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8647,19 +8656,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522450</v>
+        <v>129524246</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8694,13 +8703,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494325</v>
+        <v>494560</v>
       </c>
       <c r="R82" t="n">
-        <v>6834177</v>
+        <v>6834565</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8756,7 +8765,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B83" t="n">
         <v>79081</v>
@@ -8787,17 +8796,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R83" t="n">
         <v>6834177</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8841,66 +8850,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129520989</v>
+        <v>129522454</v>
       </c>
       <c r="B84" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494262</v>
+        <v>494456</v>
       </c>
       <c r="R84" t="n">
-        <v>6834427</v>
+        <v>6834177</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9541,10 +9541,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522173</v>
+        <v>129522027</v>
       </c>
       <c r="B91" t="n">
-        <v>80186</v>
+        <v>80187</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9552,21 +9552,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494418</v>
+        <v>494337</v>
       </c>
       <c r="R91" t="n">
-        <v>6834113</v>
+        <v>6834149</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9638,45 +9638,59 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524791</v>
+        <v>129524797</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494381</v>
+        <v>494387</v>
       </c>
       <c r="R92" t="n">
-        <v>6834429</v>
+        <v>6834437</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9735,59 +9749,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524797</v>
+        <v>129522173</v>
       </c>
       <c r="B93" t="n">
-        <v>92875</v>
+        <v>80186</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494387</v>
+        <v>494418</v>
       </c>
       <c r="R93" t="n">
-        <v>6834437</v>
+        <v>6834113</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9834,22 +9834,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129521475</v>
+        <v>129524791</v>
       </c>
       <c r="B94" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9857,34 +9857,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494181</v>
+        <v>494381</v>
       </c>
       <c r="R94" t="n">
-        <v>6834367</v>
+        <v>6834429</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9931,12 +9931,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129522027</v>
+        <v>129521475</v>
       </c>
       <c r="B96" t="n">
-        <v>80187</v>
+        <v>78839</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,21 +10051,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494337</v>
+        <v>494181</v>
       </c>
       <c r="R96" t="n">
-        <v>6834149</v>
+        <v>6834367</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10728,48 +10728,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521144</v>
+        <v>129522100</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>58106</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494222</v>
+        <v>494368</v>
       </c>
       <c r="R103" t="n">
-        <v>6834390</v>
+        <v>6834126</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10813,19 +10813,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521418</v>
+        <v>129521144</v>
       </c>
       <c r="B104" t="n">
         <v>79081</v>
@@ -10856,14 +10856,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494176</v>
+        <v>494222</v>
       </c>
       <c r="R104" t="n">
-        <v>6834368</v>
+        <v>6834390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129522341</v>
+        <v>129521418</v>
       </c>
       <c r="B105" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494345</v>
+        <v>494176</v>
       </c>
       <c r="R105" t="n">
-        <v>6834202</v>
+        <v>6834368</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521967</v>
+        <v>129522341</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,21 +11030,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494346</v>
+        <v>494345</v>
       </c>
       <c r="R106" t="n">
-        <v>6834277</v>
+        <v>6834202</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11116,10 +11116,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521977</v>
+        <v>129521967</v>
       </c>
       <c r="B107" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,34 +11127,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494334</v>
+        <v>494346</v>
       </c>
       <c r="R107" t="n">
-        <v>6834144</v>
+        <v>6834277</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,44 +11201,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522100</v>
+        <v>129521977</v>
       </c>
       <c r="B108" t="n">
-        <v>58106</v>
+        <v>80186</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494368</v>
+        <v>494334</v>
       </c>
       <c r="R108" t="n">
-        <v>6834126</v>
+        <v>6834144</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11407,10 +11407,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129522819</v>
+        <v>129523028</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11418,21 +11418,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494470</v>
+        <v>494500</v>
       </c>
       <c r="R110" t="n">
-        <v>6834231</v>
+        <v>6834263</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129523028</v>
+        <v>129521874</v>
       </c>
       <c r="B111" t="n">
-        <v>78089</v>
+        <v>80186</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494500</v>
+        <v>494355</v>
       </c>
       <c r="R111" t="n">
-        <v>6834263</v>
+        <v>6834295</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129521874</v>
+        <v>129522819</v>
       </c>
       <c r="B112" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494355</v>
+        <v>494470</v>
       </c>
       <c r="R112" t="n">
-        <v>6834295</v>
+        <v>6834231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129524747</v>
+        <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494401</v>
+        <v>494255</v>
       </c>
       <c r="R118" t="n">
-        <v>6834640</v>
+        <v>6834250</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12289,10 +12289,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524381</v>
+        <v>129521663</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494485</v>
+        <v>494242</v>
       </c>
       <c r="R119" t="n">
-        <v>6834612</v>
+        <v>6834295</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129521664</v>
+        <v>129524747</v>
       </c>
       <c r="B120" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,34 +12397,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494255</v>
+        <v>494401</v>
       </c>
       <c r="R120" t="n">
-        <v>6834250</v>
+        <v>6834640</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129521663</v>
+        <v>129524381</v>
       </c>
       <c r="B121" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494242</v>
+        <v>494485</v>
       </c>
       <c r="R121" t="n">
-        <v>6834295</v>
+        <v>6834612</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,12 +12568,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522736</v>
+        <v>129522783</v>
       </c>
       <c r="B123" t="n">
-        <v>91614</v>
+        <v>79113</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494443</v>
+        <v>494456</v>
       </c>
       <c r="R123" t="n">
-        <v>6834230</v>
+        <v>6834228</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522783</v>
+        <v>129522736</v>
       </c>
       <c r="B124" t="n">
-        <v>79113</v>
+        <v>91614</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494456</v>
+        <v>494443</v>
       </c>
       <c r="R124" t="n">
-        <v>6834228</v>
+        <v>6834230</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129521302</v>
+        <v>129521752</v>
       </c>
       <c r="B132" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,13 +13585,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>494215</v>
+        <v>494258</v>
       </c>
       <c r="R132" t="n">
-        <v>6834362</v>
+        <v>6834310</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129520912</v>
+        <v>129521302</v>
       </c>
       <c r="B133" t="n">
         <v>79081</v>
@@ -13678,17 +13678,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>494290</v>
+        <v>494215</v>
       </c>
       <c r="R133" t="n">
-        <v>6834454</v>
+        <v>6834362</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13732,22 +13732,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129521752</v>
+        <v>129520912</v>
       </c>
       <c r="B134" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13755,34 +13755,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>494258</v>
+        <v>494290</v>
       </c>
       <c r="R134" t="n">
-        <v>6834310</v>
+        <v>6834454</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13829,12 +13829,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129513963</v>
+        <v>129512298</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2173,14 +2173,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494311</v>
+        <v>494611</v>
       </c>
       <c r="R15" t="n">
-        <v>6834701</v>
+        <v>6834107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513412</v>
+        <v>129513963</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494427</v>
+        <v>494311</v>
       </c>
       <c r="R16" t="n">
-        <v>6834434</v>
+        <v>6834701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129512298</v>
+        <v>129513412</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494611</v>
+        <v>494427</v>
       </c>
       <c r="R17" t="n">
-        <v>6834107</v>
+        <v>6834434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129512105</v>
+        <v>129511957</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494664</v>
+        <v>494635</v>
       </c>
       <c r="R23" t="n">
-        <v>6834295</v>
+        <v>6834347</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129511957</v>
+        <v>129512105</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494635</v>
+        <v>494664</v>
       </c>
       <c r="R24" t="n">
-        <v>6834347</v>
+        <v>6834295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R31" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R32" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R39" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522021</v>
+        <v>129520952</v>
       </c>
       <c r="B40" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494337</v>
+        <v>494291</v>
       </c>
       <c r="R40" t="n">
-        <v>6834149</v>
+        <v>6834454</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129524342</v>
+        <v>129521092</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494544</v>
+        <v>494222</v>
       </c>
       <c r="R42" t="n">
-        <v>6834616</v>
+        <v>6834398</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4846,22 +4846,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129521092</v>
+        <v>129524342</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494222</v>
+        <v>494544</v>
       </c>
       <c r="R43" t="n">
-        <v>6834398</v>
+        <v>6834616</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524595</v>
+        <v>129522256</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>78839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494349</v>
+        <v>494384</v>
       </c>
       <c r="R47" t="n">
-        <v>6834611</v>
+        <v>6834211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129522893</v>
+        <v>129521425</v>
       </c>
       <c r="B48" t="n">
-        <v>79113</v>
+        <v>78839</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494477</v>
+        <v>494187</v>
       </c>
       <c r="R48" t="n">
-        <v>6834229</v>
+        <v>6834373</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129522256</v>
+        <v>129522893</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>79113</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494384</v>
+        <v>494477</v>
       </c>
       <c r="R49" t="n">
-        <v>6834211</v>
+        <v>6834229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129521425</v>
+        <v>129524595</v>
       </c>
       <c r="B50" t="n">
-        <v>78839</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494187</v>
+        <v>494349</v>
       </c>
       <c r="R50" t="n">
-        <v>6834373</v>
+        <v>6834611</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129522129</v>
+        <v>129521826</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,34 +5645,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494397</v>
+        <v>494361</v>
       </c>
       <c r="R51" t="n">
-        <v>6834116</v>
+        <v>6834336</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5719,44 +5719,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129522706</v>
+        <v>129521887</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494454</v>
+        <v>494350</v>
       </c>
       <c r="R52" t="n">
-        <v>6834225</v>
+        <v>6834298</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521887</v>
+        <v>129522706</v>
       </c>
       <c r="B53" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494350</v>
+        <v>494454</v>
       </c>
       <c r="R53" t="n">
-        <v>6834298</v>
+        <v>6834225</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521826</v>
+        <v>129522129</v>
       </c>
       <c r="B54" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,34 +5936,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494361</v>
+        <v>494397</v>
       </c>
       <c r="R54" t="n">
-        <v>6834336</v>
+        <v>6834116</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6010,12 +6010,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6216,54 +6216,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129524059</v>
+        <v>129522151</v>
       </c>
       <c r="B57" t="n">
-        <v>98774</v>
+        <v>78838</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494582</v>
+        <v>494385</v>
       </c>
       <c r="R57" t="n">
-        <v>6834361</v>
+        <v>6834229</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129522138</v>
+        <v>129524189</v>
       </c>
       <c r="B58" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6333,21 +6324,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6357,10 +6348,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494375</v>
+        <v>494606</v>
       </c>
       <c r="R58" t="n">
-        <v>6834215</v>
+        <v>6834497</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6516,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129521656</v>
+        <v>129524775</v>
       </c>
       <c r="B60" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6527,37 +6518,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494219</v>
+        <v>494416</v>
       </c>
       <c r="R60" t="n">
-        <v>6834291</v>
+        <v>6834464</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6601,22 +6592,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521358</v>
+        <v>129521656</v>
       </c>
       <c r="B61" t="n">
-        <v>79113</v>
+        <v>80187</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,37 +6615,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494221</v>
+        <v>494219</v>
       </c>
       <c r="R61" t="n">
-        <v>6834353</v>
+        <v>6834291</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6698,60 +6689,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129521131</v>
+        <v>129524392</v>
       </c>
       <c r="B62" t="n">
-        <v>79113</v>
+        <v>92875</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494230</v>
+        <v>494486</v>
       </c>
       <c r="R62" t="n">
-        <v>6834385</v>
+        <v>6834613</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6795,19 +6786,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129522432</v>
+        <v>129521358</v>
       </c>
       <c r="B63" t="n">
         <v>79113</v>
@@ -6842,13 +6833,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494325</v>
+        <v>494221</v>
       </c>
       <c r="R63" t="n">
-        <v>6834177</v>
+        <v>6834353</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6904,48 +6895,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524392</v>
+        <v>129521131</v>
       </c>
       <c r="B64" t="n">
-        <v>92875</v>
+        <v>79113</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494486</v>
+        <v>494230</v>
       </c>
       <c r="R64" t="n">
-        <v>6834613</v>
+        <v>6834385</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6989,22 +6980,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129524189</v>
+        <v>129522432</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7012,21 +7003,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7036,10 +7027,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494606</v>
+        <v>494325</v>
       </c>
       <c r="R65" t="n">
-        <v>6834497</v>
+        <v>6834177</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7098,10 +7089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129522151</v>
+        <v>129522138</v>
       </c>
       <c r="B66" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7100,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,13 +7124,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494385</v>
+        <v>494375</v>
       </c>
       <c r="R66" t="n">
-        <v>6834229</v>
+        <v>6834215</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7195,45 +7186,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524775</v>
+        <v>129524059</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494416</v>
+        <v>494582</v>
       </c>
       <c r="R67" t="n">
-        <v>6834464</v>
+        <v>6834361</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129520975</v>
+        <v>129524680</v>
       </c>
       <c r="B68" t="n">
-        <v>78838</v>
+        <v>80186</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,21 +7303,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494243</v>
+        <v>494357</v>
       </c>
       <c r="R68" t="n">
-        <v>6834445</v>
+        <v>6834592</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B70" t="n">
-        <v>80186</v>
+        <v>78838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7497,21 +7497,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7521,13 +7521,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R70" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129522011</v>
+        <v>129524606</v>
       </c>
       <c r="B73" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,21 +7788,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494385</v>
+        <v>494333</v>
       </c>
       <c r="R73" t="n">
-        <v>6834293</v>
+        <v>6834609</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129521838</v>
+        <v>129523011</v>
       </c>
       <c r="B74" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,37 +7885,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494355</v>
+        <v>494480</v>
       </c>
       <c r="R74" t="n">
-        <v>6834299</v>
+        <v>6834232</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7959,22 +7959,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129524606</v>
+        <v>129522011</v>
       </c>
       <c r="B75" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494333</v>
+        <v>494385</v>
       </c>
       <c r="R75" t="n">
-        <v>6834609</v>
+        <v>6834293</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129523011</v>
+        <v>129521838</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,37 +8079,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494480</v>
+        <v>494355</v>
       </c>
       <c r="R76" t="n">
-        <v>6834232</v>
+        <v>6834299</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8153,22 +8153,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524147</v>
+        <v>129524246</v>
       </c>
       <c r="B77" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,21 +8176,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8200,13 +8200,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494596</v>
+        <v>494560</v>
       </c>
       <c r="R77" t="n">
-        <v>6834467</v>
+        <v>6834565</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8262,10 +8262,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129521271</v>
+        <v>129524119</v>
       </c>
       <c r="B78" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8273,37 +8273,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494237</v>
+        <v>494556</v>
       </c>
       <c r="R78" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8347,22 +8347,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524119</v>
+        <v>129522454</v>
       </c>
       <c r="B79" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,21 +8370,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494556</v>
+        <v>494456</v>
       </c>
       <c r="R79" t="n">
-        <v>6834467</v>
+        <v>6834177</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8456,57 +8456,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522644</v>
+        <v>129522450</v>
       </c>
       <c r="B80" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494450</v>
+        <v>494325</v>
       </c>
       <c r="R80" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8550,69 +8541,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129520989</v>
+        <v>129524147</v>
       </c>
       <c r="B81" t="n">
-        <v>98774</v>
+        <v>79113</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494262</v>
+        <v>494596</v>
       </c>
       <c r="R81" t="n">
-        <v>6834427</v>
+        <v>6834467</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8656,22 +8638,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129524246</v>
+        <v>129521271</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8679,21 +8661,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8703,13 +8685,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494560</v>
+        <v>494237</v>
       </c>
       <c r="R82" t="n">
-        <v>6834565</v>
+        <v>6834397</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8765,48 +8747,57 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522450</v>
+        <v>129522644</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494325</v>
+        <v>494450</v>
       </c>
       <c r="R83" t="n">
-        <v>6834177</v>
+        <v>6834178</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8850,57 +8841,66 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522454</v>
+        <v>129520989</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494456</v>
+        <v>494262</v>
       </c>
       <c r="R84" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129523899</v>
+        <v>129520902</v>
       </c>
       <c r="B85" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8970,37 +8970,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494543</v>
+        <v>494278</v>
       </c>
       <c r="R85" t="n">
-        <v>6834251</v>
+        <v>6834456</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9044,19 +9044,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129520902</v>
+        <v>129524525</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9087,14 +9087,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494278</v>
+        <v>494354</v>
       </c>
       <c r="R86" t="n">
-        <v>6834456</v>
+        <v>6834662</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9141,22 +9141,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129524525</v>
+        <v>129523899</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9164,37 +9164,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>494354</v>
+        <v>494543</v>
       </c>
       <c r="R87" t="n">
-        <v>6834662</v>
+        <v>6834251</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9541,45 +9541,59 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522027</v>
+        <v>129524797</v>
       </c>
       <c r="B91" t="n">
-        <v>80187</v>
+        <v>92875</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494337</v>
+        <v>494387</v>
       </c>
       <c r="R91" t="n">
-        <v>6834149</v>
+        <v>6834437</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,71 +9640,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524797</v>
+        <v>129524791</v>
       </c>
       <c r="B92" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494387</v>
+        <v>494381</v>
       </c>
       <c r="R92" t="n">
-        <v>6834437</v>
+        <v>6834429</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9846,10 +9846,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129524791</v>
+        <v>129522027</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9857,34 +9857,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494381</v>
+        <v>494337</v>
       </c>
       <c r="R94" t="n">
-        <v>6834429</v>
+        <v>6834149</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9931,12 +9931,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10137,10 +10137,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129524273</v>
+        <v>129524130</v>
       </c>
       <c r="B97" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10148,37 +10148,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494549</v>
+        <v>494537</v>
       </c>
       <c r="R97" t="n">
-        <v>6834588</v>
+        <v>6834492</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10222,19 +10222,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129524130</v>
+        <v>129523005</v>
       </c>
       <c r="B98" t="n">
         <v>79081</v>
@@ -10265,14 +10265,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494537</v>
+        <v>494491</v>
       </c>
       <c r="R98" t="n">
-        <v>6834492</v>
+        <v>6834229</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10319,19 +10319,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129523005</v>
+        <v>129524530</v>
       </c>
       <c r="B99" t="n">
         <v>79081</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494491</v>
+        <v>494349</v>
       </c>
       <c r="R99" t="n">
-        <v>6834229</v>
+        <v>6834653</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10428,10 +10428,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129524530</v>
+        <v>129524273</v>
       </c>
       <c r="B100" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10439,21 +10439,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10463,13 +10463,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494349</v>
+        <v>494549</v>
       </c>
       <c r="R100" t="n">
-        <v>6834653</v>
+        <v>6834588</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10631,32 +10631,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129524122</v>
+        <v>129522100</v>
       </c>
       <c r="B102" t="n">
-        <v>80187</v>
+        <v>58106</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>103015</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10666,13 +10666,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494556</v>
+        <v>494368</v>
       </c>
       <c r="R102" t="n">
-        <v>6834467</v>
+        <v>6834126</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10728,32 +10728,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129522100</v>
+        <v>129524122</v>
       </c>
       <c r="B103" t="n">
-        <v>58106</v>
+        <v>80187</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494368</v>
+        <v>494556</v>
       </c>
       <c r="R103" t="n">
-        <v>6834126</v>
+        <v>6834467</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521144</v>
+        <v>129521977</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,34 +10836,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494222</v>
+        <v>494334</v>
       </c>
       <c r="R104" t="n">
-        <v>6834390</v>
+        <v>6834144</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,19 +10910,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521418</v>
+        <v>129521967</v>
       </c>
       <c r="B105" t="n">
         <v>79081</v>
@@ -10953,14 +10953,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494176</v>
+        <v>494346</v>
       </c>
       <c r="R105" t="n">
-        <v>6834368</v>
+        <v>6834277</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129522341</v>
+        <v>129521418</v>
       </c>
       <c r="B106" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494345</v>
+        <v>494176</v>
       </c>
       <c r="R106" t="n">
-        <v>6834202</v>
+        <v>6834368</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,19 +11104,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521967</v>
+        <v>129521144</v>
       </c>
       <c r="B107" t="n">
         <v>79081</v>
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494346</v>
+        <v>494222</v>
       </c>
       <c r="R107" t="n">
-        <v>6834277</v>
+        <v>6834390</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521977</v>
+        <v>129522341</v>
       </c>
       <c r="B108" t="n">
-        <v>80186</v>
+        <v>78838</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,34 +11224,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494334</v>
+        <v>494345</v>
       </c>
       <c r="R108" t="n">
-        <v>6834144</v>
+        <v>6834202</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11298,12 +11298,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11407,45 +11407,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129523028</v>
+        <v>129524619</v>
       </c>
       <c r="B110" t="n">
-        <v>78089</v>
+        <v>98774</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494500</v>
+        <v>494338</v>
       </c>
       <c r="R110" t="n">
-        <v>6834263</v>
+        <v>6834601</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11601,10 +11610,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129522819</v>
+        <v>129523028</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>78089</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11621,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11645,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494470</v>
+        <v>494500</v>
       </c>
       <c r="R112" t="n">
-        <v>6834231</v>
+        <v>6834263</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11698,54 +11707,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B113" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R113" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11804,7 +11804,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129521072</v>
+        <v>129524762</v>
       </c>
       <c r="B114" t="n">
         <v>79081</v>
@@ -11839,10 +11839,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494234</v>
+        <v>494406</v>
       </c>
       <c r="R114" t="n">
-        <v>6834416</v>
+        <v>6834477</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129524762</v>
+        <v>129521147</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -11932,14 +11932,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494406</v>
+        <v>494225</v>
       </c>
       <c r="R115" t="n">
-        <v>6834477</v>
+        <v>6834382</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11986,19 +11986,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521147</v>
+        <v>129521072</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -12029,14 +12029,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494225</v>
+        <v>494234</v>
       </c>
       <c r="R116" t="n">
-        <v>6834382</v>
+        <v>6834416</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12083,12 +12083,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12289,10 +12289,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129521663</v>
+        <v>129524747</v>
       </c>
       <c r="B119" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494242</v>
+        <v>494401</v>
       </c>
       <c r="R119" t="n">
-        <v>6834295</v>
+        <v>6834640</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,19 +12374,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129524747</v>
+        <v>129524381</v>
       </c>
       <c r="B120" t="n">
         <v>79081</v>
@@ -12417,14 +12417,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494401</v>
+        <v>494485</v>
       </c>
       <c r="R120" t="n">
-        <v>6834640</v>
+        <v>6834612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129524381</v>
+        <v>129521663</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494485</v>
+        <v>494242</v>
       </c>
       <c r="R121" t="n">
-        <v>6834612</v>
+        <v>6834295</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,12 +12568,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -12677,10 +12677,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522783</v>
+        <v>129522736</v>
       </c>
       <c r="B123" t="n">
-        <v>79113</v>
+        <v>91614</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>5442</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494456</v>
+        <v>494443</v>
       </c>
       <c r="R123" t="n">
-        <v>6834228</v>
+        <v>6834230</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522736</v>
+        <v>129522012</v>
       </c>
       <c r="B124" t="n">
-        <v>91614</v>
+        <v>80186</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,34 +12785,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494443</v>
+        <v>494337</v>
       </c>
       <c r="R124" t="n">
-        <v>6834230</v>
+        <v>6834146</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12859,22 +12859,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129523308</v>
+        <v>129521002</v>
       </c>
       <c r="B125" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,21 +12882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,13 +12906,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494520</v>
+        <v>494241</v>
       </c>
       <c r="R125" t="n">
-        <v>6834279</v>
+        <v>6834425</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521635</v>
+        <v>129522903</v>
       </c>
       <c r="B126" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494214</v>
+        <v>494466</v>
       </c>
       <c r="R126" t="n">
-        <v>6834306</v>
+        <v>6834211</v>
       </c>
       <c r="S126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129521002</v>
+        <v>129521823</v>
       </c>
       <c r="B127" t="n">
         <v>79081</v>
@@ -13096,17 +13096,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494241</v>
+        <v>494360</v>
       </c>
       <c r="R127" t="n">
-        <v>6834425</v>
+        <v>6834206</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13150,12 +13150,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129521823</v>
+        <v>129522783</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,37 +13270,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494360</v>
+        <v>494456</v>
       </c>
       <c r="R129" t="n">
-        <v>6834206</v>
+        <v>6834228</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13344,22 +13344,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129522903</v>
+        <v>129523308</v>
       </c>
       <c r="B130" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,21 +13367,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13391,13 +13391,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494466</v>
+        <v>494520</v>
       </c>
       <c r="R130" t="n">
-        <v>6834211</v>
+        <v>6834279</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522012</v>
+        <v>129521635</v>
       </c>
       <c r="B131" t="n">
-        <v>80186</v>
+        <v>78747</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,37 +13464,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494337</v>
+        <v>494214</v>
       </c>
       <c r="R131" t="n">
-        <v>6834146</v>
+        <v>6834306</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13538,12 +13538,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -13841,45 +13841,54 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521085</v>
+        <v>129524667</v>
       </c>
       <c r="B135" t="n">
-        <v>98774</v>
+        <v>80187</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494228</v>
+        <v>494352</v>
       </c>
       <c r="R135" t="n">
-        <v>6834405</v>
+        <v>6834596</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13926,12 +13935,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14035,10 +14044,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129524667</v>
+        <v>129522065</v>
       </c>
       <c r="B137" t="n">
-        <v>80187</v>
+        <v>78747</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14046,43 +14055,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494352</v>
+        <v>494373</v>
       </c>
       <c r="R137" t="n">
-        <v>6834596</v>
+        <v>6834247</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14141,45 +14141,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129522065</v>
+        <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>78747</v>
+        <v>98774</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>494373</v>
+        <v>494228</v>
       </c>
       <c r="R138" t="n">
-        <v>6834247</v>
+        <v>6834405</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14226,12 +14226,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R31" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R32" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129513342</v>
+        <v>129512470</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494384</v>
+        <v>494652</v>
       </c>
       <c r="R34" t="n">
-        <v>6834354</v>
+        <v>6833984</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129512470</v>
+        <v>129513342</v>
       </c>
       <c r="B35" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494652</v>
+        <v>494384</v>
       </c>
       <c r="R35" t="n">
-        <v>6833984</v>
+        <v>6834354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129522021</v>
+        <v>129520952</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494337</v>
+        <v>494291</v>
       </c>
       <c r="R39" t="n">
-        <v>6834149</v>
+        <v>6834454</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R40" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129521092</v>
+        <v>129524342</v>
       </c>
       <c r="B42" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494222</v>
+        <v>494544</v>
       </c>
       <c r="R42" t="n">
-        <v>6834398</v>
+        <v>6834616</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4846,22 +4846,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129524342</v>
+        <v>129521092</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494544</v>
+        <v>494222</v>
       </c>
       <c r="R43" t="n">
-        <v>6834616</v>
+        <v>6834398</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129524385</v>
+        <v>129522893</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494528</v>
+        <v>494477</v>
       </c>
       <c r="R46" t="n">
-        <v>6834660</v>
+        <v>6834229</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129522256</v>
+        <v>129524595</v>
       </c>
       <c r="B47" t="n">
-        <v>78839</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494384</v>
+        <v>494349</v>
       </c>
       <c r="R47" t="n">
-        <v>6834211</v>
+        <v>6834611</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5343,7 +5343,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129521425</v>
+        <v>129522256</v>
       </c>
       <c r="B48" t="n">
         <v>78839</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494187</v>
+        <v>494384</v>
       </c>
       <c r="R48" t="n">
-        <v>6834373</v>
+        <v>6834211</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129522893</v>
+        <v>129521425</v>
       </c>
       <c r="B49" t="n">
-        <v>79113</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494477</v>
+        <v>494187</v>
       </c>
       <c r="R49" t="n">
-        <v>6834229</v>
+        <v>6834373</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129524595</v>
+        <v>129524385</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494349</v>
+        <v>494528</v>
       </c>
       <c r="R50" t="n">
-        <v>6834611</v>
+        <v>6834660</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5731,32 +5731,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129521887</v>
+        <v>129520992</v>
       </c>
       <c r="B52" t="n">
-        <v>80215</v>
+        <v>78747</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494350</v>
+        <v>494221</v>
       </c>
       <c r="R52" t="n">
-        <v>6834298</v>
+        <v>6834431</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129522706</v>
+        <v>129521655</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5839,21 +5839,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494454</v>
+        <v>494247</v>
       </c>
       <c r="R53" t="n">
-        <v>6834225</v>
+        <v>6834296</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5925,7 +5925,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522129</v>
+        <v>129522706</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -5956,17 +5956,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494397</v>
+        <v>494454</v>
       </c>
       <c r="R54" t="n">
-        <v>6834116</v>
+        <v>6834225</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,22 +6010,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129520992</v>
+        <v>129522129</v>
       </c>
       <c r="B55" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6033,37 +6033,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494221</v>
+        <v>494397</v>
       </c>
       <c r="R55" t="n">
-        <v>6834431</v>
+        <v>6834116</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6107,44 +6107,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521655</v>
+        <v>129521887</v>
       </c>
       <c r="B56" t="n">
-        <v>78747</v>
+        <v>80215</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494247</v>
+        <v>494350</v>
       </c>
       <c r="R56" t="n">
-        <v>6834296</v>
+        <v>6834298</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129524189</v>
+        <v>129521656</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,37 +6324,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494606</v>
+        <v>494219</v>
       </c>
       <c r="R58" t="n">
-        <v>6834497</v>
+        <v>6834291</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6398,22 +6398,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522857</v>
+        <v>129521358</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6421,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494475</v>
+        <v>494221</v>
       </c>
       <c r="R59" t="n">
-        <v>6834232</v>
+        <v>6834353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,10 +6507,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524775</v>
+        <v>129521131</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6518,21 +6518,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6542,13 +6542,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494416</v>
+        <v>494230</v>
       </c>
       <c r="R60" t="n">
-        <v>6834464</v>
+        <v>6834385</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6604,10 +6604,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521656</v>
+        <v>129522432</v>
       </c>
       <c r="B61" t="n">
-        <v>80187</v>
+        <v>79113</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494219</v>
+        <v>494325</v>
       </c>
       <c r="R61" t="n">
-        <v>6834291</v>
+        <v>6834177</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6689,12 +6689,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6798,10 +6798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129521358</v>
+        <v>129524189</v>
       </c>
       <c r="B63" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,21 +6809,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6833,13 +6833,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494221</v>
+        <v>494606</v>
       </c>
       <c r="R63" t="n">
-        <v>6834353</v>
+        <v>6834497</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6895,10 +6895,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129521131</v>
+        <v>129522857</v>
       </c>
       <c r="B64" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6906,21 +6906,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6930,13 +6930,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494230</v>
+        <v>494475</v>
       </c>
       <c r="R64" t="n">
-        <v>6834385</v>
+        <v>6834232</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129522432</v>
+        <v>129524775</v>
       </c>
       <c r="B65" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7003,21 +7003,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7027,13 +7027,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494325</v>
+        <v>494416</v>
       </c>
       <c r="R65" t="n">
-        <v>6834177</v>
+        <v>6834464</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129524680</v>
+        <v>129521804</v>
       </c>
       <c r="B68" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,21 +7303,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494357</v>
+        <v>494297</v>
       </c>
       <c r="R68" t="n">
-        <v>6834592</v>
+        <v>6834314</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129521804</v>
+        <v>129524680</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494297</v>
+        <v>494357</v>
       </c>
       <c r="R69" t="n">
-        <v>6834314</v>
+        <v>6834592</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129523011</v>
+        <v>129522011</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,34 +7885,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494480</v>
+        <v>494385</v>
       </c>
       <c r="R74" t="n">
-        <v>6834232</v>
+        <v>6834293</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7959,19 +7959,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129522011</v>
+        <v>129521838</v>
       </c>
       <c r="B75" t="n">
         <v>79113</v>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494385</v>
+        <v>494355</v>
       </c>
       <c r="R75" t="n">
-        <v>6834293</v>
+        <v>6834299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129521838</v>
+        <v>129523011</v>
       </c>
       <c r="B76" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,37 +8079,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494355</v>
+        <v>494480</v>
       </c>
       <c r="R76" t="n">
-        <v>6834299</v>
+        <v>6834232</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8153,12 +8153,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8262,10 +8262,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129524119</v>
+        <v>129522454</v>
       </c>
       <c r="B78" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8273,21 +8273,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494556</v>
+        <v>494456</v>
       </c>
       <c r="R78" t="n">
-        <v>6834467</v>
+        <v>6834177</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8359,7 +8359,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B79" t="n">
         <v>79081</v>
@@ -8390,17 +8390,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R79" t="n">
         <v>6834177</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8444,22 +8444,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522450</v>
+        <v>129524147</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494325</v>
+        <v>494596</v>
       </c>
       <c r="R80" t="n">
-        <v>6834177</v>
+        <v>6834467</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8553,7 +8553,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129524147</v>
+        <v>129521271</v>
       </c>
       <c r="B81" t="n">
         <v>79113</v>
@@ -8588,10 +8588,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494596</v>
+        <v>494237</v>
       </c>
       <c r="R81" t="n">
-        <v>6834467</v>
+        <v>6834397</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8650,10 +8650,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129521271</v>
+        <v>129524119</v>
       </c>
       <c r="B82" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8661,37 +8661,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494237</v>
+        <v>494556</v>
       </c>
       <c r="R82" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8735,12 +8735,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9541,59 +9541,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129524797</v>
+        <v>129521897</v>
       </c>
       <c r="B91" t="n">
-        <v>92875</v>
+        <v>98774</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494387</v>
+        <v>494323</v>
       </c>
       <c r="R91" t="n">
-        <v>6834437</v>
+        <v>6834131</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9640,22 +9626,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524791</v>
+        <v>129521475</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9663,34 +9649,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494381</v>
+        <v>494181</v>
       </c>
       <c r="R92" t="n">
-        <v>6834429</v>
+        <v>6834367</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9737,22 +9723,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129522173</v>
+        <v>129522027</v>
       </c>
       <c r="B93" t="n">
-        <v>80186</v>
+        <v>80187</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9760,21 +9746,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9784,10 +9770,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494418</v>
+        <v>494337</v>
       </c>
       <c r="R93" t="n">
-        <v>6834113</v>
+        <v>6834149</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,10 +9832,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129522027</v>
+        <v>129522173</v>
       </c>
       <c r="B94" t="n">
-        <v>80187</v>
+        <v>80186</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9857,21 +9843,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9881,10 +9867,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494337</v>
+        <v>494418</v>
       </c>
       <c r="R94" t="n">
-        <v>6834149</v>
+        <v>6834113</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9943,45 +9929,59 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521897</v>
+        <v>129524797</v>
       </c>
       <c r="B95" t="n">
-        <v>98774</v>
+        <v>92875</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494323</v>
+        <v>494387</v>
       </c>
       <c r="R95" t="n">
-        <v>6834131</v>
+        <v>6834437</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,22 +10028,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521475</v>
+        <v>129524791</v>
       </c>
       <c r="B96" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10051,34 +10051,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494181</v>
+        <v>494381</v>
       </c>
       <c r="R96" t="n">
-        <v>6834367</v>
+        <v>6834429</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10125,22 +10125,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129524130</v>
+        <v>129524273</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10148,37 +10148,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>494537</v>
+        <v>494549</v>
       </c>
       <c r="R97" t="n">
-        <v>6834492</v>
+        <v>6834588</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10222,57 +10222,66 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129523005</v>
+        <v>129522632</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494491</v>
+        <v>494455</v>
       </c>
       <c r="R98" t="n">
-        <v>6834229</v>
+        <v>6834185</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10319,19 +10328,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129524530</v>
+        <v>129524130</v>
       </c>
       <c r="B99" t="n">
         <v>79081</v>
@@ -10362,14 +10371,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494349</v>
+        <v>494537</v>
       </c>
       <c r="R99" t="n">
-        <v>6834653</v>
+        <v>6834492</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10416,22 +10425,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129524273</v>
+        <v>129523005</v>
       </c>
       <c r="B100" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10439,21 +10448,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10463,13 +10472,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494549</v>
+        <v>494491</v>
       </c>
       <c r="R100" t="n">
-        <v>6834588</v>
+        <v>6834229</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10525,54 +10534,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129522632</v>
+        <v>129524530</v>
       </c>
       <c r="B101" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494455</v>
+        <v>494349</v>
       </c>
       <c r="R101" t="n">
-        <v>6834185</v>
+        <v>6834653</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10619,60 +10619,60 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129522100</v>
+        <v>129521967</v>
       </c>
       <c r="B102" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494368</v>
+        <v>494346</v>
       </c>
       <c r="R102" t="n">
-        <v>6834126</v>
+        <v>6834277</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10716,22 +10716,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129524122</v>
+        <v>129521418</v>
       </c>
       <c r="B103" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,21 +10739,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494556</v>
+        <v>494176</v>
       </c>
       <c r="R103" t="n">
-        <v>6834467</v>
+        <v>6834368</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521977</v>
+        <v>129521144</v>
       </c>
       <c r="B104" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,34 +10836,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494334</v>
+        <v>494222</v>
       </c>
       <c r="R104" t="n">
-        <v>6834144</v>
+        <v>6834390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521967</v>
+        <v>129524122</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494346</v>
+        <v>494556</v>
       </c>
       <c r="R105" t="n">
-        <v>6834277</v>
+        <v>6834467</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521418</v>
+        <v>129521977</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,21 +11030,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494176</v>
+        <v>494334</v>
       </c>
       <c r="R106" t="n">
-        <v>6834368</v>
+        <v>6834144</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11116,10 +11116,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521144</v>
+        <v>129522341</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494222</v>
+        <v>494345</v>
       </c>
       <c r="R107" t="n">
-        <v>6834390</v>
+        <v>6834202</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11213,48 +11213,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522341</v>
+        <v>129522100</v>
       </c>
       <c r="B108" t="n">
-        <v>78838</v>
+        <v>58106</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494345</v>
+        <v>494368</v>
       </c>
       <c r="R108" t="n">
-        <v>6834202</v>
+        <v>6834126</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11298,12 +11298,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11407,54 +11407,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B110" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R110" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11513,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129521874</v>
+        <v>129523028</v>
       </c>
       <c r="B111" t="n">
-        <v>80186</v>
+        <v>78089</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11524,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11548,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494355</v>
+        <v>494500</v>
       </c>
       <c r="R111" t="n">
-        <v>6834295</v>
+        <v>6834263</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11610,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129523028</v>
+        <v>129521874</v>
       </c>
       <c r="B112" t="n">
-        <v>78089</v>
+        <v>80186</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11621,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11645,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494500</v>
+        <v>494355</v>
       </c>
       <c r="R112" t="n">
-        <v>6834263</v>
+        <v>6834295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11707,45 +11698,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129522819</v>
+        <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494470</v>
+        <v>494338</v>
       </c>
       <c r="R113" t="n">
-        <v>6834231</v>
+        <v>6834601</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521664</v>
+        <v>129521663</v>
       </c>
       <c r="B118" t="n">
-        <v>91614</v>
+        <v>78839</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494255</v>
+        <v>494242</v>
       </c>
       <c r="R118" t="n">
-        <v>6834250</v>
+        <v>6834295</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524747</v>
+        <v>129523234</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494401</v>
+        <v>494472</v>
       </c>
       <c r="R119" t="n">
-        <v>6834640</v>
+        <v>6834268</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129524381</v>
+        <v>129521664</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>91614</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494485</v>
+        <v>494255</v>
       </c>
       <c r="R120" t="n">
-        <v>6834612</v>
+        <v>6834250</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129521663</v>
+        <v>129524747</v>
       </c>
       <c r="B121" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494242</v>
+        <v>494401</v>
       </c>
       <c r="R121" t="n">
-        <v>6834295</v>
+        <v>6834640</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129523234</v>
+        <v>129524381</v>
       </c>
       <c r="B122" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494472</v>
+        <v>494485</v>
       </c>
       <c r="R122" t="n">
-        <v>6834268</v>
+        <v>6834612</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,22 +12665,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522736</v>
+        <v>129521002</v>
       </c>
       <c r="B123" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494443</v>
+        <v>494241</v>
       </c>
       <c r="R123" t="n">
-        <v>6834230</v>
+        <v>6834425</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522012</v>
+        <v>129522903</v>
       </c>
       <c r="B124" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,34 +12785,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494337</v>
+        <v>494466</v>
       </c>
       <c r="R124" t="n">
-        <v>6834146</v>
+        <v>6834211</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12859,19 +12859,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129521002</v>
+        <v>129521823</v>
       </c>
       <c r="B125" t="n">
         <v>79081</v>
@@ -12902,17 +12902,17 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494241</v>
+        <v>494360</v>
       </c>
       <c r="R125" t="n">
-        <v>6834425</v>
+        <v>6834206</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12956,22 +12956,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129522903</v>
+        <v>129522012</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,34 +12979,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494466</v>
+        <v>494337</v>
       </c>
       <c r="R126" t="n">
-        <v>6834211</v>
+        <v>6834146</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13053,22 +13053,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129521823</v>
+        <v>129524581</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,37 +13076,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494360</v>
+        <v>494323</v>
       </c>
       <c r="R127" t="n">
-        <v>6834206</v>
+        <v>6834627</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13150,22 +13150,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129524581</v>
+        <v>129522783</v>
       </c>
       <c r="B128" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494323</v>
+        <v>494456</v>
       </c>
       <c r="R128" t="n">
-        <v>6834627</v>
+        <v>6834228</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129522783</v>
+        <v>129523308</v>
       </c>
       <c r="B129" t="n">
-        <v>79113</v>
+        <v>78747</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13294,13 +13294,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494456</v>
+        <v>494520</v>
       </c>
       <c r="R129" t="n">
-        <v>6834228</v>
+        <v>6834279</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129523308</v>
+        <v>129521635</v>
       </c>
       <c r="B130" t="n">
         <v>78747</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494520</v>
+        <v>494214</v>
       </c>
       <c r="R130" t="n">
-        <v>6834279</v>
+        <v>6834306</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129521635</v>
+        <v>129522736</v>
       </c>
       <c r="B131" t="n">
-        <v>78747</v>
+        <v>91614</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,13 +13488,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494214</v>
+        <v>494443</v>
       </c>
       <c r="R131" t="n">
-        <v>6834306</v>
+        <v>6834230</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129524667</v>
+        <v>129521403</v>
       </c>
       <c r="B135" t="n">
-        <v>80187</v>
+        <v>90625</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,43 +13852,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494352</v>
+        <v>494199</v>
       </c>
       <c r="R135" t="n">
-        <v>6834596</v>
+        <v>6834366</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13947,10 +13938,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129521403</v>
+        <v>129524667</v>
       </c>
       <c r="B136" t="n">
-        <v>90625</v>
+        <v>80187</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13958,34 +13949,43 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1962</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494199</v>
+        <v>494352</v>
       </c>
       <c r="R136" t="n">
-        <v>6834366</v>
+        <v>6834596</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129512298</v>
+        <v>129513963</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2173,14 +2173,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494611</v>
+        <v>494311</v>
       </c>
       <c r="R15" t="n">
-        <v>6834107</v>
+        <v>6834701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513963</v>
+        <v>129513412</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494311</v>
+        <v>494427</v>
       </c>
       <c r="R16" t="n">
-        <v>6834701</v>
+        <v>6834434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129513412</v>
+        <v>129512298</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494427</v>
+        <v>494611</v>
       </c>
       <c r="R17" t="n">
-        <v>6834434</v>
+        <v>6834107</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
         <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129512676</v>
+        <v>129512549</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494500</v>
+        <v>494625</v>
       </c>
       <c r="R31" t="n">
-        <v>6834016</v>
+        <v>6834032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129512549</v>
+        <v>129512676</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494625</v>
+        <v>494500</v>
       </c>
       <c r="R32" t="n">
-        <v>6834032</v>
+        <v>6834016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129512470</v>
+        <v>129513342</v>
       </c>
       <c r="B34" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494652</v>
+        <v>494384</v>
       </c>
       <c r="R34" t="n">
-        <v>6833984</v>
+        <v>6834354</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129513342</v>
+        <v>129512771</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494384</v>
+        <v>494466</v>
       </c>
       <c r="R35" t="n">
-        <v>6834354</v>
+        <v>6833989</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129512771</v>
+        <v>129512470</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494466</v>
+        <v>494652</v>
       </c>
       <c r="R36" t="n">
-        <v>6833989</v>
+        <v>6833984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4481,21 +4481,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R39" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B40" t="n">
-        <v>57896</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R40" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522417</v>
+        <v>129520952</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494442</v>
+        <v>494291</v>
       </c>
       <c r="R41" t="n">
-        <v>6834141</v>
+        <v>6834454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129522893</v>
+        <v>129524385</v>
       </c>
       <c r="B46" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494477</v>
+        <v>494528</v>
       </c>
       <c r="R46" t="n">
-        <v>6834229</v>
+        <v>6834660</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129524595</v>
+        <v>129522256</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>78839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494349</v>
+        <v>494384</v>
       </c>
       <c r="R47" t="n">
-        <v>6834611</v>
+        <v>6834211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5343,7 +5343,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129522256</v>
+        <v>129521425</v>
       </c>
       <c r="B48" t="n">
         <v>78839</v>
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494384</v>
+        <v>494187</v>
       </c>
       <c r="R48" t="n">
-        <v>6834211</v>
+        <v>6834373</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129521425</v>
+        <v>129522893</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>79113</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494187</v>
+        <v>494477</v>
       </c>
       <c r="R49" t="n">
-        <v>6834373</v>
+        <v>6834229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129524385</v>
+        <v>129524595</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,13 +5572,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494528</v>
+        <v>494349</v>
       </c>
       <c r="R50" t="n">
-        <v>6834660</v>
+        <v>6834611</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129521826</v>
+        <v>129520992</v>
       </c>
       <c r="B51" t="n">
-        <v>80187</v>
+        <v>78747</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,21 +5645,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5669,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>494361</v>
+        <v>494221</v>
       </c>
       <c r="R51" t="n">
-        <v>6834336</v>
+        <v>6834431</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129520992</v>
+        <v>129521655</v>
       </c>
       <c r="B52" t="n">
         <v>78747</v>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>494221</v>
+        <v>494247</v>
       </c>
       <c r="R52" t="n">
-        <v>6834431</v>
+        <v>6834296</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521655</v>
+        <v>129521887</v>
       </c>
       <c r="B53" t="n">
-        <v>78747</v>
+        <v>80215</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494247</v>
+        <v>494350</v>
       </c>
       <c r="R53" t="n">
-        <v>6834296</v>
+        <v>6834298</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522706</v>
+        <v>129521826</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,13 +5960,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494454</v>
+        <v>494361</v>
       </c>
       <c r="R54" t="n">
-        <v>6834225</v>
+        <v>6834336</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521887</v>
+        <v>129522706</v>
       </c>
       <c r="B56" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494350</v>
+        <v>494454</v>
       </c>
       <c r="R56" t="n">
-        <v>6834298</v>
+        <v>6834225</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6216,45 +6216,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129522151</v>
+        <v>129524392</v>
       </c>
       <c r="B57" t="n">
-        <v>78838</v>
+        <v>92879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494385</v>
+        <v>494486</v>
       </c>
       <c r="R57" t="n">
-        <v>6834229</v>
+        <v>6834613</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6301,12 +6301,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6410,10 +6410,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129521358</v>
+        <v>129522138</v>
       </c>
       <c r="B59" t="n">
-        <v>79113</v>
+        <v>79671</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6421,21 +6421,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494221</v>
+        <v>494375</v>
       </c>
       <c r="R59" t="n">
-        <v>6834353</v>
+        <v>6834215</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6507,48 +6507,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129521131</v>
+        <v>129524059</v>
       </c>
       <c r="B60" t="n">
-        <v>79113</v>
+        <v>98778</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494230</v>
+        <v>494582</v>
       </c>
       <c r="R60" t="n">
-        <v>6834385</v>
+        <v>6834361</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6604,7 +6613,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129522432</v>
+        <v>129521358</v>
       </c>
       <c r="B61" t="n">
         <v>79113</v>
@@ -6639,13 +6648,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494325</v>
+        <v>494221</v>
       </c>
       <c r="R61" t="n">
-        <v>6834177</v>
+        <v>6834353</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6701,48 +6710,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129524392</v>
+        <v>129521131</v>
       </c>
       <c r="B62" t="n">
-        <v>92875</v>
+        <v>79113</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494486</v>
+        <v>494230</v>
       </c>
       <c r="R62" t="n">
-        <v>6834613</v>
+        <v>6834385</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6786,22 +6795,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129524189</v>
+        <v>129522432</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6809,21 +6818,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6833,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494606</v>
+        <v>494325</v>
       </c>
       <c r="R63" t="n">
-        <v>6834497</v>
+        <v>6834177</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6895,7 +6904,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129522857</v>
+        <v>129524189</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6930,13 +6939,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494475</v>
+        <v>494606</v>
       </c>
       <c r="R64" t="n">
-        <v>6834232</v>
+        <v>6834497</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6992,7 +7001,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129524775</v>
+        <v>129522857</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7027,10 +7036,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494416</v>
+        <v>494475</v>
       </c>
       <c r="R65" t="n">
-        <v>6834464</v>
+        <v>6834232</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7089,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129522138</v>
+        <v>129522151</v>
       </c>
       <c r="B66" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7100,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7124,13 +7133,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494375</v>
+        <v>494385</v>
       </c>
       <c r="R66" t="n">
-        <v>6834215</v>
+        <v>6834229</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7186,54 +7195,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524059</v>
+        <v>129524775</v>
       </c>
       <c r="B67" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494582</v>
+        <v>494416</v>
       </c>
       <c r="R67" t="n">
-        <v>6834361</v>
+        <v>6834464</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7292,10 +7292,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521804</v>
+        <v>129524680</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,21 +7303,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494297</v>
+        <v>494357</v>
       </c>
       <c r="R68" t="n">
-        <v>6834314</v>
+        <v>6834592</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129524680</v>
+        <v>129521986</v>
       </c>
       <c r="B69" t="n">
-        <v>80186</v>
+        <v>80187</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,34 +7400,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494357</v>
+        <v>494336</v>
       </c>
       <c r="R69" t="n">
-        <v>6834592</v>
+        <v>6834146</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7474,12 +7474,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B71" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,37 +7594,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R71" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7668,12 +7668,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7683,7 +7683,7 @@
         <v>129522294</v>
       </c>
       <c r="B72" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129524606</v>
+        <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,21 +7788,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494333</v>
+        <v>494385</v>
       </c>
       <c r="R73" t="n">
-        <v>6834609</v>
+        <v>6834293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129522011</v>
+        <v>129521838</v>
       </c>
       <c r="B74" t="n">
         <v>79113</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494385</v>
+        <v>494355</v>
       </c>
       <c r="R74" t="n">
-        <v>6834293</v>
+        <v>6834299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129521838</v>
+        <v>129524606</v>
       </c>
       <c r="B75" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494355</v>
+        <v>494333</v>
       </c>
       <c r="R75" t="n">
-        <v>6834299</v>
+        <v>6834609</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8165,45 +8165,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524246</v>
+        <v>129522644</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494560</v>
+        <v>494450</v>
       </c>
       <c r="R77" t="n">
-        <v>6834565</v>
+        <v>6834178</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8250,57 +8259,66 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129522454</v>
+        <v>129520989</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494456</v>
+        <v>494262</v>
       </c>
       <c r="R78" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8359,10 +8377,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129522450</v>
+        <v>129524147</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8370,21 +8388,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8394,10 +8412,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494325</v>
+        <v>494596</v>
       </c>
       <c r="R79" t="n">
-        <v>6834177</v>
+        <v>6834467</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8456,7 +8474,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129524147</v>
+        <v>129521271</v>
       </c>
       <c r="B80" t="n">
         <v>79113</v>
@@ -8491,10 +8509,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494596</v>
+        <v>494237</v>
       </c>
       <c r="R80" t="n">
-        <v>6834467</v>
+        <v>6834397</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8553,10 +8571,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129521271</v>
+        <v>129524119</v>
       </c>
       <c r="B81" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8564,37 +8582,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494237</v>
+        <v>494556</v>
       </c>
       <c r="R81" t="n">
-        <v>6834397</v>
+        <v>6834468</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8638,22 +8656,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129524119</v>
+        <v>129524246</v>
       </c>
       <c r="B82" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8661,34 +8679,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494556</v>
+        <v>494560</v>
       </c>
       <c r="R82" t="n">
-        <v>6834467</v>
+        <v>6834565</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,69 +8753,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522644</v>
+        <v>129522450</v>
       </c>
       <c r="B83" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494450</v>
+        <v>494325</v>
       </c>
       <c r="R83" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8841,66 +8850,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129520989</v>
+        <v>129522454</v>
       </c>
       <c r="B84" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494262</v>
+        <v>494456</v>
       </c>
       <c r="R84" t="n">
-        <v>6834427</v>
+        <v>6834177</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9541,32 +9541,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129521897</v>
+        <v>129522173</v>
       </c>
       <c r="B91" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494323</v>
+        <v>494418</v>
       </c>
       <c r="R91" t="n">
-        <v>6834131</v>
+        <v>6834113</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129521475</v>
+        <v>129522027</v>
       </c>
       <c r="B92" t="n">
-        <v>78839</v>
+        <v>80187</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9649,21 +9649,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9673,10 +9673,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494181</v>
+        <v>494337</v>
       </c>
       <c r="R92" t="n">
-        <v>6834367</v>
+        <v>6834149</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9735,10 +9735,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129522027</v>
+        <v>129524791</v>
       </c>
       <c r="B93" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9746,34 +9746,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494337</v>
+        <v>494381</v>
       </c>
       <c r="R93" t="n">
-        <v>6834149</v>
+        <v>6834429</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9820,22 +9820,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129522173</v>
+        <v>129521475</v>
       </c>
       <c r="B94" t="n">
-        <v>80186</v>
+        <v>78839</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9843,21 +9843,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494418</v>
+        <v>494181</v>
       </c>
       <c r="R94" t="n">
-        <v>6834113</v>
+        <v>6834367</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>129524797</v>
       </c>
       <c r="B95" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10040,45 +10040,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129524791</v>
+        <v>129521897</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494381</v>
+        <v>494323</v>
       </c>
       <c r="R96" t="n">
-        <v>6834429</v>
+        <v>6834131</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10125,12 +10125,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10237,7 +10237,7 @@
         <v>129522632</v>
       </c>
       <c r="B98" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129521967</v>
+        <v>129524122</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494346</v>
+        <v>494556</v>
       </c>
       <c r="R102" t="n">
-        <v>6834277</v>
+        <v>6834468</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,19 +10716,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521418</v>
+        <v>129521144</v>
       </c>
       <c r="B103" t="n">
         <v>79081</v>
@@ -10759,14 +10759,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494176</v>
+        <v>494222</v>
       </c>
       <c r="R103" t="n">
-        <v>6834368</v>
+        <v>6834390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,19 +10813,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521144</v>
+        <v>129521418</v>
       </c>
       <c r="B104" t="n">
         <v>79081</v>
@@ -10856,14 +10856,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494222</v>
+        <v>494176</v>
       </c>
       <c r="R104" t="n">
-        <v>6834390</v>
+        <v>6834368</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129524122</v>
+        <v>129522341</v>
       </c>
       <c r="B105" t="n">
-        <v>80187</v>
+        <v>78838</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494556</v>
+        <v>494345</v>
       </c>
       <c r="R105" t="n">
-        <v>6834467</v>
+        <v>6834202</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,22 +11007,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521977</v>
+        <v>129521967</v>
       </c>
       <c r="B106" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494334</v>
+        <v>494346</v>
       </c>
       <c r="R106" t="n">
-        <v>6834144</v>
+        <v>6834277</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129522341</v>
+        <v>129521977</v>
       </c>
       <c r="B107" t="n">
-        <v>78838</v>
+        <v>80186</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,34 +11127,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494345</v>
+        <v>494334</v>
       </c>
       <c r="R107" t="n">
-        <v>6834202</v>
+        <v>6834144</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,12 +11201,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11701,7 +11701,7 @@
         <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524762</v>
+        <v>129524240</v>
       </c>
       <c r="B114" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494406</v>
+        <v>494559</v>
       </c>
       <c r="R114" t="n">
-        <v>6834477</v>
+        <v>6834519</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521147</v>
+        <v>129521072</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -11932,14 +11932,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494225</v>
+        <v>494234</v>
       </c>
       <c r="R115" t="n">
-        <v>6834382</v>
+        <v>6834416</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11986,19 +11986,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521072</v>
+        <v>129524762</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -12033,10 +12033,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494234</v>
+        <v>494406</v>
       </c>
       <c r="R116" t="n">
-        <v>6834416</v>
+        <v>6834477</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129524240</v>
+        <v>129521147</v>
       </c>
       <c r="B117" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,37 +12106,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494559</v>
+        <v>494225</v>
       </c>
       <c r="R117" t="n">
-        <v>6834519</v>
+        <v>6834382</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12180,22 +12180,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521663</v>
+        <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>78839</v>
+        <v>91618</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494242</v>
+        <v>494255</v>
       </c>
       <c r="R118" t="n">
-        <v>6834295</v>
+        <v>6834250</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129523234</v>
+        <v>129524747</v>
       </c>
       <c r="B119" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494472</v>
+        <v>494401</v>
       </c>
       <c r="R119" t="n">
-        <v>6834268</v>
+        <v>6834640</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129521664</v>
+        <v>129524381</v>
       </c>
       <c r="B120" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494255</v>
+        <v>494485</v>
       </c>
       <c r="R120" t="n">
-        <v>6834250</v>
+        <v>6834612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129524747</v>
+        <v>129523234</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494401</v>
+        <v>494472</v>
       </c>
       <c r="R121" t="n">
-        <v>6834640</v>
+        <v>6834268</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129524381</v>
+        <v>129521663</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494485</v>
+        <v>494242</v>
       </c>
       <c r="R122" t="n">
-        <v>6834612</v>
+        <v>6834295</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,22 +12665,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129521002</v>
+        <v>129522736</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>91618</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494241</v>
+        <v>494443</v>
       </c>
       <c r="R123" t="n">
-        <v>6834425</v>
+        <v>6834230</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522903</v>
+        <v>129522783</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494466</v>
+        <v>494456</v>
       </c>
       <c r="R124" t="n">
-        <v>6834211</v>
+        <v>6834228</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129521823</v>
+        <v>129523308</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>78747</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,37 +12882,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494360</v>
+        <v>494520</v>
       </c>
       <c r="R125" t="n">
-        <v>6834206</v>
+        <v>6834279</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12956,22 +12956,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129522012</v>
+        <v>129521635</v>
       </c>
       <c r="B126" t="n">
-        <v>80186</v>
+        <v>78747</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,37 +12979,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494337</v>
+        <v>494214</v>
       </c>
       <c r="R126" t="n">
-        <v>6834146</v>
+        <v>6834306</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13053,19 +13053,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129524581</v>
+        <v>129522012</v>
       </c>
       <c r="B127" t="n">
         <v>80186</v>
@@ -13096,14 +13096,14 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494323</v>
+        <v>494337</v>
       </c>
       <c r="R127" t="n">
-        <v>6834627</v>
+        <v>6834146</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13150,22 +13150,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129522783</v>
+        <v>129524581</v>
       </c>
       <c r="B128" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494456</v>
+        <v>494323</v>
       </c>
       <c r="R128" t="n">
-        <v>6834228</v>
+        <v>6834627</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129523308</v>
+        <v>129521002</v>
       </c>
       <c r="B129" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,21 +13270,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13294,13 +13294,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494520</v>
+        <v>494241</v>
       </c>
       <c r="R129" t="n">
-        <v>6834279</v>
+        <v>6834425</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13356,10 +13356,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129521635</v>
+        <v>129521823</v>
       </c>
       <c r="B130" t="n">
-        <v>78747</v>
+        <v>79081</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13367,37 +13367,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>494214</v>
+        <v>494360</v>
       </c>
       <c r="R130" t="n">
-        <v>6834306</v>
+        <v>6834206</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13441,22 +13441,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522736</v>
+        <v>129522903</v>
       </c>
       <c r="B131" t="n">
-        <v>91614</v>
+        <v>79081</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494443</v>
+        <v>494466</v>
       </c>
       <c r="R131" t="n">
-        <v>6834230</v>
+        <v>6834211</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129521403</v>
+        <v>129522065</v>
       </c>
       <c r="B135" t="n">
-        <v>90625</v>
+        <v>78747</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>494199</v>
+        <v>494373</v>
       </c>
       <c r="R135" t="n">
-        <v>6834366</v>
+        <v>6834247</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -13938,10 +13938,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129524667</v>
+        <v>129521403</v>
       </c>
       <c r="B136" t="n">
-        <v>80187</v>
+        <v>90629</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13949,43 +13949,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>1962</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>494352</v>
+        <v>494199</v>
       </c>
       <c r="R136" t="n">
-        <v>6834596</v>
+        <v>6834366</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14044,10 +14035,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129522065</v>
+        <v>129524667</v>
       </c>
       <c r="B137" t="n">
-        <v>78747</v>
+        <v>80187</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14055,34 +14046,43 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>494373</v>
+        <v>494352</v>
       </c>
       <c r="R137" t="n">
-        <v>6834247</v>
+        <v>6834596</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14144,7 +14144,7 @@
         <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
         <v>129456266</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129456325</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129513963</v>
+        <v>129512298</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2173,14 +2173,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494311</v>
+        <v>494611</v>
       </c>
       <c r="R15" t="n">
-        <v>6834701</v>
+        <v>6834107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129513412</v>
+        <v>129513963</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2270,14 +2270,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494427</v>
+        <v>494311</v>
       </c>
       <c r="R16" t="n">
-        <v>6834434</v>
+        <v>6834701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129512298</v>
+        <v>129513412</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494611</v>
+        <v>494427</v>
       </c>
       <c r="R17" t="n">
-        <v>6834107</v>
+        <v>6834434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3503,7 +3503,7 @@
         <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129512771</v>
+        <v>129512470</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494466</v>
+        <v>494652</v>
       </c>
       <c r="R35" t="n">
-        <v>6833989</v>
+        <v>6833984</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129512470</v>
+        <v>129512771</v>
       </c>
       <c r="B36" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4190,21 +4190,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494652</v>
+        <v>494466</v>
       </c>
       <c r="R36" t="n">
-        <v>6833984</v>
+        <v>6833989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R39" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4567,32 +4567,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129522417</v>
+        <v>129520952</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494442</v>
+        <v>494291</v>
       </c>
       <c r="R40" t="n">
-        <v>6834141</v>
+        <v>6834454</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,21 +4675,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R41" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129524385</v>
+        <v>129522893</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5160,21 +5160,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>494528</v>
+        <v>494477</v>
       </c>
       <c r="R46" t="n">
-        <v>6834660</v>
+        <v>6834229</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129522893</v>
+        <v>129524385</v>
       </c>
       <c r="B49" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494477</v>
+        <v>494528</v>
       </c>
       <c r="R49" t="n">
-        <v>6834229</v>
+        <v>6834660</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521887</v>
+        <v>129521826</v>
       </c>
       <c r="B53" t="n">
-        <v>80215</v>
+        <v>80187</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494350</v>
+        <v>494361</v>
       </c>
       <c r="R53" t="n">
-        <v>6834298</v>
+        <v>6834336</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129521826</v>
+        <v>129522706</v>
       </c>
       <c r="B54" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,21 +5936,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5960,13 +5960,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494361</v>
+        <v>494454</v>
       </c>
       <c r="R54" t="n">
-        <v>6834336</v>
+        <v>6834225</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6022,45 +6022,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522129</v>
+        <v>129521887</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494397</v>
+        <v>494350</v>
       </c>
       <c r="R55" t="n">
-        <v>6834116</v>
+        <v>6834298</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6107,19 +6107,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129522706</v>
+        <v>129522129</v>
       </c>
       <c r="B56" t="n">
         <v>79081</v>
@@ -6150,17 +6150,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494454</v>
+        <v>494397</v>
       </c>
       <c r="R56" t="n">
-        <v>6834225</v>
+        <v>6834116</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6204,44 +6204,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129524392</v>
+        <v>129521656</v>
       </c>
       <c r="B57" t="n">
-        <v>92879</v>
+        <v>80187</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6251,13 +6251,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494486</v>
+        <v>494219</v>
       </c>
       <c r="R57" t="n">
-        <v>6834613</v>
+        <v>6834291</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6313,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129521656</v>
+        <v>129522151</v>
       </c>
       <c r="B58" t="n">
-        <v>80187</v>
+        <v>78838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,37 +6324,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494219</v>
+        <v>494385</v>
       </c>
       <c r="R58" t="n">
-        <v>6834291</v>
+        <v>6834229</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6398,60 +6398,69 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129522138</v>
+        <v>129524059</v>
       </c>
       <c r="B59" t="n">
-        <v>79671</v>
+        <v>98780</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494375</v>
+        <v>494582</v>
       </c>
       <c r="R59" t="n">
-        <v>6834215</v>
+        <v>6834361</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6507,57 +6516,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129524059</v>
+        <v>129522138</v>
       </c>
       <c r="B60" t="n">
-        <v>98778</v>
+        <v>79671</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494582</v>
+        <v>494375</v>
       </c>
       <c r="R60" t="n">
-        <v>6834361</v>
+        <v>6834215</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129522151</v>
+        <v>129524775</v>
       </c>
       <c r="B66" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7109,21 +7109,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494385</v>
+        <v>494416</v>
       </c>
       <c r="R66" t="n">
-        <v>6834229</v>
+        <v>6834464</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7195,45 +7195,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524775</v>
+        <v>129524392</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494416</v>
+        <v>494486</v>
       </c>
       <c r="R67" t="n">
-        <v>6834464</v>
+        <v>6834613</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7280,22 +7280,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129524680</v>
+        <v>129521986</v>
       </c>
       <c r="B68" t="n">
-        <v>80186</v>
+        <v>80187</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7303,34 +7303,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494357</v>
+        <v>494336</v>
       </c>
       <c r="R68" t="n">
-        <v>6834592</v>
+        <v>6834146</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7377,22 +7377,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129521986</v>
+        <v>129521804</v>
       </c>
       <c r="B69" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,37 +7400,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494336</v>
+        <v>494297</v>
       </c>
       <c r="R69" t="n">
-        <v>6834146</v>
+        <v>6834314</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7474,60 +7474,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129520975</v>
+        <v>129522294</v>
       </c>
       <c r="B70" t="n">
-        <v>78838</v>
+        <v>98780</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494243</v>
+        <v>494419</v>
       </c>
       <c r="R70" t="n">
-        <v>6834445</v>
+        <v>6834113</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,22 +7571,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129521804</v>
+        <v>129524680</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,21 +7594,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494297</v>
+        <v>494357</v>
       </c>
       <c r="R71" t="n">
-        <v>6834314</v>
+        <v>6834592</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7680,48 +7680,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129522294</v>
+        <v>129520975</v>
       </c>
       <c r="B72" t="n">
-        <v>98778</v>
+        <v>78838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494419</v>
+        <v>494243</v>
       </c>
       <c r="R72" t="n">
-        <v>6834113</v>
+        <v>6834445</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7765,22 +7765,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129522011</v>
+        <v>129524606</v>
       </c>
       <c r="B73" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,21 +7788,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494385</v>
+        <v>494333</v>
       </c>
       <c r="R73" t="n">
-        <v>6834293</v>
+        <v>6834609</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129521838</v>
+        <v>129523011</v>
       </c>
       <c r="B74" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,37 +7885,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494355</v>
+        <v>494480</v>
       </c>
       <c r="R74" t="n">
-        <v>6834299</v>
+        <v>6834232</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7959,22 +7959,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129524606</v>
+        <v>129522011</v>
       </c>
       <c r="B75" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494333</v>
+        <v>494385</v>
       </c>
       <c r="R75" t="n">
-        <v>6834609</v>
+        <v>6834293</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129523011</v>
+        <v>129521838</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,37 +8079,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494480</v>
+        <v>494355</v>
       </c>
       <c r="R76" t="n">
-        <v>6834232</v>
+        <v>6834299</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8153,69 +8153,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129522644</v>
+        <v>129524147</v>
       </c>
       <c r="B77" t="n">
-        <v>98778</v>
+        <v>79113</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494450</v>
+        <v>494596</v>
       </c>
       <c r="R77" t="n">
-        <v>6834178</v>
+        <v>6834467</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8259,69 +8250,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129520989</v>
+        <v>129521271</v>
       </c>
       <c r="B78" t="n">
-        <v>98778</v>
+        <v>79113</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494262</v>
+        <v>494237</v>
       </c>
       <c r="R78" t="n">
-        <v>6834427</v>
+        <v>6834397</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8365,22 +8347,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524147</v>
+        <v>129524246</v>
       </c>
       <c r="B79" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8388,21 +8370,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8412,13 +8394,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494596</v>
+        <v>494560</v>
       </c>
       <c r="R79" t="n">
-        <v>6834467</v>
+        <v>6834565</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8474,10 +8456,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129521271</v>
+        <v>129522450</v>
       </c>
       <c r="B80" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8485,21 +8467,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8509,10 +8491,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494237</v>
+        <v>494325</v>
       </c>
       <c r="R80" t="n">
-        <v>6834397</v>
+        <v>6834177</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8609,7 +8591,7 @@
         <v>494556</v>
       </c>
       <c r="R81" t="n">
-        <v>6834468</v>
+        <v>6834467</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8668,7 +8650,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129524246</v>
+        <v>129522454</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8699,14 +8681,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494560</v>
+        <v>494456</v>
       </c>
       <c r="R82" t="n">
-        <v>6834565</v>
+        <v>6834177</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8753,60 +8735,69 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129522450</v>
+        <v>129520989</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494325</v>
+        <v>494262</v>
       </c>
       <c r="R83" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8850,57 +8841,66 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522454</v>
+        <v>129522644</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494456</v>
+        <v>494450</v>
       </c>
       <c r="R84" t="n">
-        <v>6834177</v>
+        <v>6834178</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129521936</v>
+        <v>129522147</v>
       </c>
       <c r="B88" t="n">
-        <v>79113</v>
+        <v>78839</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494342</v>
+        <v>494385</v>
       </c>
       <c r="R88" t="n">
-        <v>6834284</v>
+        <v>6834229</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521041</v>
+        <v>129521936</v>
       </c>
       <c r="B89" t="n">
         <v>79113</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494251</v>
+        <v>494342</v>
       </c>
       <c r="R89" t="n">
-        <v>6834413</v>
+        <v>6834284</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129522147</v>
+        <v>129521041</v>
       </c>
       <c r="B90" t="n">
-        <v>78839</v>
+        <v>79113</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,21 +9455,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494385</v>
+        <v>494251</v>
       </c>
       <c r="R90" t="n">
-        <v>6834229</v>
+        <v>6834413</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9541,10 +9541,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522173</v>
+        <v>129522027</v>
       </c>
       <c r="B91" t="n">
-        <v>80186</v>
+        <v>80187</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9552,21 +9552,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494418</v>
+        <v>494337</v>
       </c>
       <c r="R91" t="n">
-        <v>6834113</v>
+        <v>6834149</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9638,10 +9638,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129522027</v>
+        <v>129524791</v>
       </c>
       <c r="B92" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9649,34 +9649,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494337</v>
+        <v>494381</v>
       </c>
       <c r="R92" t="n">
-        <v>6834149</v>
+        <v>6834429</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,57 +9723,71 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524791</v>
+        <v>129524797</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494381</v>
+        <v>494387</v>
       </c>
       <c r="R93" t="n">
-        <v>6834429</v>
+        <v>6834437</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9832,10 +9846,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129521475</v>
+        <v>129522173</v>
       </c>
       <c r="B94" t="n">
-        <v>78839</v>
+        <v>80186</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9843,21 +9857,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9867,10 +9881,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494181</v>
+        <v>494418</v>
       </c>
       <c r="R94" t="n">
-        <v>6834367</v>
+        <v>6834113</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9929,59 +9943,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129524797</v>
+        <v>129521897</v>
       </c>
       <c r="B95" t="n">
-        <v>92879</v>
+        <v>98780</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494387</v>
+        <v>494323</v>
       </c>
       <c r="R95" t="n">
-        <v>6834437</v>
+        <v>6834131</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10028,44 +10028,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521897</v>
+        <v>129521475</v>
       </c>
       <c r="B96" t="n">
-        <v>98778</v>
+        <v>78839</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494323</v>
+        <v>494181</v>
       </c>
       <c r="R96" t="n">
-        <v>6834131</v>
+        <v>6834367</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10234,54 +10234,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129522632</v>
+        <v>129523005</v>
       </c>
       <c r="B98" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494455</v>
+        <v>494491</v>
       </c>
       <c r="R98" t="n">
-        <v>6834185</v>
+        <v>6834229</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10328,19 +10319,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129524130</v>
+        <v>129524530</v>
       </c>
       <c r="B99" t="n">
         <v>79081</v>
@@ -10371,14 +10362,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494537</v>
+        <v>494349</v>
       </c>
       <c r="R99" t="n">
-        <v>6834492</v>
+        <v>6834653</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10425,19 +10416,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129523005</v>
+        <v>129524130</v>
       </c>
       <c r="B100" t="n">
         <v>79081</v>
@@ -10468,14 +10459,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494491</v>
+        <v>494537</v>
       </c>
       <c r="R100" t="n">
-        <v>6834229</v>
+        <v>6834492</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10522,57 +10513,66 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129524530</v>
+        <v>129522632</v>
       </c>
       <c r="B101" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494349</v>
+        <v>494455</v>
       </c>
       <c r="R101" t="n">
-        <v>6834653</v>
+        <v>6834185</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10619,22 +10619,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129524122</v>
+        <v>129522517</v>
       </c>
       <c r="B102" t="n">
-        <v>80187</v>
+        <v>78839</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,21 +10642,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494556</v>
+        <v>494455</v>
       </c>
       <c r="R102" t="n">
-        <v>6834468</v>
+        <v>6834176</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521144</v>
+        <v>129524122</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10739,34 +10739,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494222</v>
+        <v>494556</v>
       </c>
       <c r="R103" t="n">
-        <v>6834390</v>
+        <v>6834467</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10813,19 +10813,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521418</v>
+        <v>129521967</v>
       </c>
       <c r="B104" t="n">
         <v>79081</v>
@@ -10856,14 +10856,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494176</v>
+        <v>494346</v>
       </c>
       <c r="R104" t="n">
-        <v>6834368</v>
+        <v>6834277</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,22 +10910,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129522341</v>
+        <v>129521144</v>
       </c>
       <c r="B105" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,21 +10933,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494345</v>
+        <v>494222</v>
       </c>
       <c r="R105" t="n">
-        <v>6834202</v>
+        <v>6834390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521967</v>
+        <v>129521977</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494346</v>
+        <v>494334</v>
       </c>
       <c r="R106" t="n">
-        <v>6834277</v>
+        <v>6834144</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521977</v>
+        <v>129521418</v>
       </c>
       <c r="B107" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494334</v>
+        <v>494176</v>
       </c>
       <c r="R107" t="n">
-        <v>6834144</v>
+        <v>6834368</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11213,48 +11213,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522100</v>
+        <v>129522341</v>
       </c>
       <c r="B108" t="n">
-        <v>58106</v>
+        <v>78838</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494368</v>
+        <v>494345</v>
       </c>
       <c r="R108" t="n">
-        <v>6834126</v>
+        <v>6834202</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11298,44 +11298,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522517</v>
+        <v>129522100</v>
       </c>
       <c r="B109" t="n">
-        <v>78839</v>
+        <v>58106</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494455</v>
+        <v>494368</v>
       </c>
       <c r="R109" t="n">
-        <v>6834176</v>
+        <v>6834126</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521072</v>
+        <v>129524762</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494234</v>
+        <v>494406</v>
       </c>
       <c r="R115" t="n">
-        <v>6834416</v>
+        <v>6834477</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11998,7 +11998,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129524762</v>
+        <v>129521072</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -12033,10 +12033,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494406</v>
+        <v>494234</v>
       </c>
       <c r="R116" t="n">
-        <v>6834477</v>
+        <v>6834416</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521664</v>
+        <v>129521663</v>
       </c>
       <c r="B118" t="n">
-        <v>91618</v>
+        <v>78839</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494255</v>
+        <v>494242</v>
       </c>
       <c r="R118" t="n">
-        <v>6834250</v>
+        <v>6834295</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129524747</v>
+        <v>129523234</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494401</v>
+        <v>494472</v>
       </c>
       <c r="R119" t="n">
-        <v>6834640</v>
+        <v>6834268</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129524381</v>
+        <v>129521664</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494485</v>
+        <v>494255</v>
       </c>
       <c r="R120" t="n">
-        <v>6834612</v>
+        <v>6834250</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129523234</v>
+        <v>129524747</v>
       </c>
       <c r="B121" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494472</v>
+        <v>494401</v>
       </c>
       <c r="R121" t="n">
-        <v>6834268</v>
+        <v>6834640</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129521663</v>
+        <v>129524381</v>
       </c>
       <c r="B122" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494242</v>
+        <v>494485</v>
       </c>
       <c r="R122" t="n">
-        <v>6834295</v>
+        <v>6834612</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,22 +12665,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129522736</v>
+        <v>129522783</v>
       </c>
       <c r="B123" t="n">
-        <v>91618</v>
+        <v>79113</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12688,21 +12688,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5442</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12712,10 +12712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>494443</v>
+        <v>494456</v>
       </c>
       <c r="R123" t="n">
-        <v>6834230</v>
+        <v>6834228</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,10 +12774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129522783</v>
+        <v>129523308</v>
       </c>
       <c r="B124" t="n">
-        <v>79113</v>
+        <v>78747</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12785,21 +12785,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>494456</v>
+        <v>494520</v>
       </c>
       <c r="R124" t="n">
-        <v>6834228</v>
+        <v>6834279</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129523308</v>
+        <v>129521635</v>
       </c>
       <c r="B125" t="n">
         <v>78747</v>
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494520</v>
+        <v>494214</v>
       </c>
       <c r="R125" t="n">
-        <v>6834279</v>
+        <v>6834306</v>
       </c>
       <c r="S125" t="n">
         <v>20</v>
@@ -12968,10 +12968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129521635</v>
+        <v>129522736</v>
       </c>
       <c r="B126" t="n">
-        <v>78747</v>
+        <v>91620</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494214</v>
+        <v>494443</v>
       </c>
       <c r="R126" t="n">
-        <v>6834306</v>
+        <v>6834230</v>
       </c>
       <c r="S126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13065,10 +13065,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129522012</v>
+        <v>129521002</v>
       </c>
       <c r="B127" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,34 +13076,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494337</v>
+        <v>494241</v>
       </c>
       <c r="R127" t="n">
-        <v>6834146</v>
+        <v>6834425</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13150,22 +13150,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129524581</v>
+        <v>129522903</v>
       </c>
       <c r="B128" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494323</v>
+        <v>494466</v>
       </c>
       <c r="R128" t="n">
-        <v>6834627</v>
+        <v>6834211</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129521002</v>
+        <v>129522012</v>
       </c>
       <c r="B129" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,34 +13270,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494241</v>
+        <v>494337</v>
       </c>
       <c r="R129" t="n">
-        <v>6834425</v>
+        <v>6834146</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13344,12 +13344,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129522903</v>
+        <v>129524581</v>
       </c>
       <c r="B131" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494466</v>
+        <v>494323</v>
       </c>
       <c r="R131" t="n">
-        <v>6834211</v>
+        <v>6834627</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13941,7 +13941,7 @@
         <v>129521403</v>
       </c>
       <c r="B136" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -5925,7 +5925,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522706</v>
+        <v>129522129</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -5956,17 +5956,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494454</v>
+        <v>494397</v>
       </c>
       <c r="R54" t="n">
-        <v>6834225</v>
+        <v>6834116</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,44 +6010,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129521887</v>
+        <v>129522706</v>
       </c>
       <c r="B55" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6057,13 +6057,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494350</v>
+        <v>494454</v>
       </c>
       <c r="R55" t="n">
-        <v>6834298</v>
+        <v>6834225</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6119,45 +6119,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129522129</v>
+        <v>129521887</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494397</v>
+        <v>494350</v>
       </c>
       <c r="R56" t="n">
-        <v>6834116</v>
+        <v>6834298</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7486,45 +7486,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129522294</v>
+        <v>129524680</v>
       </c>
       <c r="B70" t="n">
-        <v>98780</v>
+        <v>80186</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494419</v>
+        <v>494357</v>
       </c>
       <c r="R70" t="n">
-        <v>6834113</v>
+        <v>6834592</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,22 +7571,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129524680</v>
+        <v>129520975</v>
       </c>
       <c r="B71" t="n">
-        <v>80186</v>
+        <v>78838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,21 +7594,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494357</v>
+        <v>494243</v>
       </c>
       <c r="R71" t="n">
-        <v>6834592</v>
+        <v>6834445</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7680,48 +7680,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129520975</v>
+        <v>129522294</v>
       </c>
       <c r="B72" t="n">
-        <v>78838</v>
+        <v>98780</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494243</v>
+        <v>494419</v>
       </c>
       <c r="R72" t="n">
-        <v>6834445</v>
+        <v>6834113</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7765,22 +7765,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129524606</v>
+        <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,21 +7788,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494333</v>
+        <v>494385</v>
       </c>
       <c r="R73" t="n">
-        <v>6834609</v>
+        <v>6834293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129523011</v>
+        <v>129521838</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7885,37 +7885,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494480</v>
+        <v>494355</v>
       </c>
       <c r="R74" t="n">
-        <v>6834232</v>
+        <v>6834299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7959,22 +7959,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129522011</v>
+        <v>129524606</v>
       </c>
       <c r="B75" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494385</v>
+        <v>494333</v>
       </c>
       <c r="R75" t="n">
-        <v>6834293</v>
+        <v>6834609</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129521838</v>
+        <v>129523011</v>
       </c>
       <c r="B76" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,37 +8079,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494355</v>
+        <v>494480</v>
       </c>
       <c r="R76" t="n">
-        <v>6834299</v>
+        <v>6834232</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8153,12 +8153,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9735,59 +9735,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129524797</v>
+        <v>129522173</v>
       </c>
       <c r="B93" t="n">
-        <v>92881</v>
+        <v>80186</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494387</v>
+        <v>494418</v>
       </c>
       <c r="R93" t="n">
-        <v>6834437</v>
+        <v>6834113</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9834,44 +9820,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129522173</v>
+        <v>129521897</v>
       </c>
       <c r="B94" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9881,10 +9867,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494418</v>
+        <v>494323</v>
       </c>
       <c r="R94" t="n">
-        <v>6834113</v>
+        <v>6834131</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9943,32 +9929,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521897</v>
+        <v>129521475</v>
       </c>
       <c r="B95" t="n">
-        <v>98780</v>
+        <v>78839</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9978,10 +9964,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494323</v>
+        <v>494181</v>
       </c>
       <c r="R95" t="n">
-        <v>6834131</v>
+        <v>6834367</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10040,45 +10026,59 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521475</v>
+        <v>129524797</v>
       </c>
       <c r="B96" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494181</v>
+        <v>494387</v>
       </c>
       <c r="R96" t="n">
-        <v>6834367</v>
+        <v>6834437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10125,12 +10125,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10728,32 +10728,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129524122</v>
+        <v>129522100</v>
       </c>
       <c r="B103" t="n">
-        <v>80187</v>
+        <v>58106</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2081</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494556</v>
+        <v>494368</v>
       </c>
       <c r="R103" t="n">
-        <v>6834467</v>
+        <v>6834126</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129521967</v>
+        <v>129524122</v>
       </c>
       <c r="B104" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,34 +10836,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494346</v>
+        <v>494556</v>
       </c>
       <c r="R104" t="n">
-        <v>6834277</v>
+        <v>6834467</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10910,19 +10910,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521144</v>
+        <v>129521967</v>
       </c>
       <c r="B105" t="n">
         <v>79081</v>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494222</v>
+        <v>494346</v>
       </c>
       <c r="R105" t="n">
-        <v>6834390</v>
+        <v>6834277</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521977</v>
+        <v>129521144</v>
       </c>
       <c r="B106" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494334</v>
+        <v>494222</v>
       </c>
       <c r="R106" t="n">
-        <v>6834144</v>
+        <v>6834390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521418</v>
+        <v>129521977</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494176</v>
+        <v>494334</v>
       </c>
       <c r="R107" t="n">
-        <v>6834368</v>
+        <v>6834144</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129522341</v>
+        <v>129521418</v>
       </c>
       <c r="B108" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,34 +11224,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494345</v>
+        <v>494176</v>
       </c>
       <c r="R108" t="n">
-        <v>6834202</v>
+        <v>6834368</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11298,60 +11298,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522100</v>
+        <v>129522341</v>
       </c>
       <c r="B109" t="n">
-        <v>58106</v>
+        <v>78838</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494368</v>
+        <v>494345</v>
       </c>
       <c r="R109" t="n">
-        <v>6834126</v>
+        <v>6834202</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11395,22 +11395,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129522819</v>
+        <v>129521874</v>
       </c>
       <c r="B110" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11418,21 +11418,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494470</v>
+        <v>494355</v>
       </c>
       <c r="R110" t="n">
-        <v>6834231</v>
+        <v>6834295</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129523028</v>
+        <v>129522819</v>
       </c>
       <c r="B111" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494500</v>
+        <v>494470</v>
       </c>
       <c r="R111" t="n">
-        <v>6834263</v>
+        <v>6834231</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129521874</v>
+        <v>129523028</v>
       </c>
       <c r="B112" t="n">
-        <v>80186</v>
+        <v>78089</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494355</v>
+        <v>494500</v>
       </c>
       <c r="R112" t="n">
-        <v>6834295</v>
+        <v>6834263</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524240</v>
+        <v>129524762</v>
       </c>
       <c r="B114" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494559</v>
+        <v>494406</v>
       </c>
       <c r="R114" t="n">
-        <v>6834519</v>
+        <v>6834477</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129524762</v>
+        <v>129521072</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494406</v>
+        <v>494234</v>
       </c>
       <c r="R115" t="n">
-        <v>6834477</v>
+        <v>6834416</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11998,7 +11998,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129521072</v>
+        <v>129521147</v>
       </c>
       <c r="B116" t="n">
         <v>79081</v>
@@ -12029,14 +12029,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>494234</v>
+        <v>494225</v>
       </c>
       <c r="R116" t="n">
-        <v>6834416</v>
+        <v>6834382</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12083,22 +12083,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129521147</v>
+        <v>129524240</v>
       </c>
       <c r="B117" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,37 +12106,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494225</v>
+        <v>494559</v>
       </c>
       <c r="R117" t="n">
-        <v>6834382</v>
+        <v>6834519</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12180,12 +12180,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -4470,32 +4470,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129522417</v>
+        <v>129520952</v>
       </c>
       <c r="B39" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494442</v>
+        <v>494291</v>
       </c>
       <c r="R39" t="n">
-        <v>6834141</v>
+        <v>6834454</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129520952</v>
+        <v>129522021</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494291</v>
+        <v>494337</v>
       </c>
       <c r="R40" t="n">
-        <v>6834454</v>
+        <v>6834149</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522021</v>
+        <v>129522417</v>
       </c>
       <c r="B41" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,13 +4699,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494337</v>
+        <v>494442</v>
       </c>
       <c r="R41" t="n">
-        <v>6834149</v>
+        <v>6834141</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -7486,45 +7486,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129524680</v>
+        <v>129522294</v>
       </c>
       <c r="B70" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494357</v>
+        <v>494419</v>
       </c>
       <c r="R70" t="n">
-        <v>6834592</v>
+        <v>6834113</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7571,22 +7571,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129520975</v>
+        <v>129524680</v>
       </c>
       <c r="B71" t="n">
-        <v>78838</v>
+        <v>80186</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,21 +7594,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494243</v>
+        <v>494357</v>
       </c>
       <c r="R71" t="n">
-        <v>6834445</v>
+        <v>6834592</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7680,48 +7680,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129522294</v>
+        <v>129520975</v>
       </c>
       <c r="B72" t="n">
-        <v>98780</v>
+        <v>78838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494419</v>
+        <v>494243</v>
       </c>
       <c r="R72" t="n">
-        <v>6834113</v>
+        <v>6834445</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7765,12 +7765,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129522147</v>
+        <v>129521936</v>
       </c>
       <c r="B88" t="n">
-        <v>78839</v>
+        <v>79113</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494385</v>
+        <v>494342</v>
       </c>
       <c r="R88" t="n">
-        <v>6834229</v>
+        <v>6834284</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521936</v>
+        <v>129521041</v>
       </c>
       <c r="B89" t="n">
         <v>79113</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494342</v>
+        <v>494251</v>
       </c>
       <c r="R89" t="n">
-        <v>6834284</v>
+        <v>6834413</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129521041</v>
+        <v>129522147</v>
       </c>
       <c r="B90" t="n">
-        <v>79113</v>
+        <v>78839</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,21 +9455,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494251</v>
+        <v>494385</v>
       </c>
       <c r="R90" t="n">
-        <v>6834413</v>
+        <v>6834229</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -2918,7 +2918,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129511957</v>
+        <v>129512105</v>
       </c>
       <c r="B23" t="n">
         <v>79081</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494635</v>
+        <v>494664</v>
       </c>
       <c r="R23" t="n">
-        <v>6834347</v>
+        <v>6834295</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129512105</v>
+        <v>129511957</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494664</v>
+        <v>494635</v>
       </c>
       <c r="R24" t="n">
-        <v>6834295</v>
+        <v>6834347</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3403,45 +3403,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129512658</v>
+        <v>129514113</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494506</v>
+        <v>494256</v>
       </c>
       <c r="R28" t="n">
-        <v>6834042</v>
+        <v>6834732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,45 +3500,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129514113</v>
+        <v>129512658</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494256</v>
+        <v>494506</v>
       </c>
       <c r="R29" t="n">
-        <v>6834732</v>
+        <v>6834042</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3985,10 +3985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129513342</v>
+        <v>129512470</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3996,21 +3996,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494384</v>
+        <v>494652</v>
       </c>
       <c r="R34" t="n">
-        <v>6834354</v>
+        <v>6833984</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129512470</v>
+        <v>129513342</v>
       </c>
       <c r="B35" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494652</v>
+        <v>494384</v>
       </c>
       <c r="R35" t="n">
-        <v>6833984</v>
+        <v>6834354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4470,32 +4470,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129520952</v>
+        <v>129522417</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494291</v>
+        <v>494442</v>
       </c>
       <c r="R39" t="n">
-        <v>6834454</v>
+        <v>6834141</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129522417</v>
+        <v>129520952</v>
       </c>
       <c r="B41" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494442</v>
+        <v>494291</v>
       </c>
       <c r="R41" t="n">
-        <v>6834141</v>
+        <v>6834454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129524342</v>
+        <v>129521092</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494544</v>
+        <v>494222</v>
       </c>
       <c r="R42" t="n">
-        <v>6834616</v>
+        <v>6834398</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4846,22 +4846,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129521092</v>
+        <v>129524342</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494222</v>
+        <v>494544</v>
       </c>
       <c r="R43" t="n">
-        <v>6834398</v>
+        <v>6834616</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4943,12 +4943,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5246,10 +5246,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129522256</v>
+        <v>129524595</v>
       </c>
       <c r="B47" t="n">
-        <v>78839</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5257,21 +5257,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494384</v>
+        <v>494349</v>
       </c>
       <c r="R47" t="n">
-        <v>6834211</v>
+        <v>6834611</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129521425</v>
+        <v>129524385</v>
       </c>
       <c r="B48" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494187</v>
+        <v>494528</v>
       </c>
       <c r="R48" t="n">
-        <v>6834373</v>
+        <v>6834660</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129524385</v>
+        <v>129522256</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5475,13 +5475,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494528</v>
+        <v>494384</v>
       </c>
       <c r="R49" t="n">
-        <v>6834660</v>
+        <v>6834211</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5537,10 +5537,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129524595</v>
+        <v>129521425</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>78839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5548,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494349</v>
+        <v>494187</v>
       </c>
       <c r="R50" t="n">
-        <v>6834611</v>
+        <v>6834373</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5828,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129521826</v>
+        <v>129521887</v>
       </c>
       <c r="B53" t="n">
-        <v>80187</v>
+        <v>80215</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494361</v>
+        <v>494350</v>
       </c>
       <c r="R53" t="n">
-        <v>6834336</v>
+        <v>6834298</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5925,7 +5925,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129522129</v>
+        <v>129522706</v>
       </c>
       <c r="B54" t="n">
         <v>79081</v>
@@ -5956,17 +5956,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494397</v>
+        <v>494454</v>
       </c>
       <c r="R54" t="n">
-        <v>6834116</v>
+        <v>6834225</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6010,19 +6010,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129522706</v>
+        <v>129522129</v>
       </c>
       <c r="B55" t="n">
         <v>79081</v>
@@ -6053,17 +6053,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494454</v>
+        <v>494397</v>
       </c>
       <c r="R55" t="n">
-        <v>6834225</v>
+        <v>6834116</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6107,44 +6107,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129521887</v>
+        <v>129521826</v>
       </c>
       <c r="B56" t="n">
-        <v>80215</v>
+        <v>80187</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>494350</v>
+        <v>494361</v>
       </c>
       <c r="R56" t="n">
-        <v>6834298</v>
+        <v>6834336</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6216,48 +6216,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129521656</v>
+        <v>129524059</v>
       </c>
       <c r="B57" t="n">
-        <v>80187</v>
+        <v>98790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494219</v>
+        <v>494582</v>
       </c>
       <c r="R57" t="n">
-        <v>6834291</v>
+        <v>6834361</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6301,22 +6310,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129522151</v>
+        <v>129522138</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6324,21 +6333,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6348,13 +6357,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494385</v>
+        <v>494375</v>
       </c>
       <c r="R58" t="n">
-        <v>6834229</v>
+        <v>6834215</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6410,54 +6419,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129524059</v>
+        <v>129521358</v>
       </c>
       <c r="B59" t="n">
-        <v>98780</v>
+        <v>79113</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494582</v>
+        <v>494221</v>
       </c>
       <c r="R59" t="n">
-        <v>6834361</v>
+        <v>6834353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129522138</v>
+        <v>129521131</v>
       </c>
       <c r="B60" t="n">
-        <v>79671</v>
+        <v>79113</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6527,21 +6527,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494375</v>
+        <v>494230</v>
       </c>
       <c r="R60" t="n">
-        <v>6834215</v>
+        <v>6834385</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129521358</v>
+        <v>129522432</v>
       </c>
       <c r="B61" t="n">
         <v>79113</v>
@@ -6648,13 +6648,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494221</v>
+        <v>494325</v>
       </c>
       <c r="R61" t="n">
-        <v>6834353</v>
+        <v>6834177</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129521131</v>
+        <v>129522151</v>
       </c>
       <c r="B62" t="n">
-        <v>79113</v>
+        <v>78838</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>494230</v>
+        <v>494385</v>
       </c>
       <c r="R62" t="n">
-        <v>6834385</v>
+        <v>6834229</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6807,48 +6807,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129522432</v>
+        <v>129524392</v>
       </c>
       <c r="B63" t="n">
-        <v>79113</v>
+        <v>92881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494325</v>
+        <v>494486</v>
       </c>
       <c r="R63" t="n">
-        <v>6834177</v>
+        <v>6834613</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6892,12 +6892,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7195,32 +7195,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129524392</v>
+        <v>129521656</v>
       </c>
       <c r="B67" t="n">
-        <v>92881</v>
+        <v>80187</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7230,13 +7230,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494486</v>
+        <v>494219</v>
       </c>
       <c r="R67" t="n">
-        <v>6834613</v>
+        <v>6834291</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7292,32 +7292,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129521986</v>
+        <v>129522294</v>
       </c>
       <c r="B68" t="n">
-        <v>80187</v>
+        <v>98790</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494336</v>
+        <v>494419</v>
       </c>
       <c r="R68" t="n">
-        <v>6834146</v>
+        <v>6834113</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129521804</v>
+        <v>129524680</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>494297</v>
+        <v>494357</v>
       </c>
       <c r="R69" t="n">
-        <v>6834314</v>
+        <v>6834592</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7486,48 +7486,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129522294</v>
+        <v>129520975</v>
       </c>
       <c r="B70" t="n">
-        <v>98780</v>
+        <v>78838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>494419</v>
+        <v>494243</v>
       </c>
       <c r="R70" t="n">
-        <v>6834113</v>
+        <v>6834445</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7571,22 +7571,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129524680</v>
+        <v>129521804</v>
       </c>
       <c r="B71" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7594,21 +7594,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7618,13 +7618,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494357</v>
+        <v>494297</v>
       </c>
       <c r="R71" t="n">
-        <v>6834592</v>
+        <v>6834314</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129520975</v>
+        <v>129521986</v>
       </c>
       <c r="B72" t="n">
-        <v>78838</v>
+        <v>80187</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7691,37 +7691,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494243</v>
+        <v>494336</v>
       </c>
       <c r="R72" t="n">
-        <v>6834445</v>
+        <v>6834146</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7765,22 +7765,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129522011</v>
+        <v>129523011</v>
       </c>
       <c r="B73" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494385</v>
+        <v>494480</v>
       </c>
       <c r="R73" t="n">
-        <v>6834293</v>
+        <v>6834232</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,19 +7862,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129521838</v>
+        <v>129522011</v>
       </c>
       <c r="B74" t="n">
         <v>79113</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494355</v>
+        <v>494385</v>
       </c>
       <c r="R74" t="n">
-        <v>6834299</v>
+        <v>6834293</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129524606</v>
+        <v>129521838</v>
       </c>
       <c r="B75" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494333</v>
+        <v>494355</v>
       </c>
       <c r="R75" t="n">
-        <v>6834609</v>
+        <v>6834299</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129523011</v>
+        <v>129524606</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8079,34 +8079,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494480</v>
+        <v>494333</v>
       </c>
       <c r="R76" t="n">
-        <v>6834232</v>
+        <v>6834609</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8153,22 +8153,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129524147</v>
+        <v>129524119</v>
       </c>
       <c r="B77" t="n">
-        <v>79113</v>
+        <v>80186</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8176,37 +8176,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494596</v>
+        <v>494556</v>
       </c>
       <c r="R77" t="n">
-        <v>6834467</v>
+        <v>6834468</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8250,60 +8250,69 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129521271</v>
+        <v>129522644</v>
       </c>
       <c r="B78" t="n">
-        <v>79113</v>
+        <v>98790</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494237</v>
+        <v>494450</v>
       </c>
       <c r="R78" t="n">
-        <v>6834397</v>
+        <v>6834178</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8347,57 +8356,66 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129524246</v>
+        <v>129520989</v>
       </c>
       <c r="B79" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494560</v>
+        <v>494262</v>
       </c>
       <c r="R79" t="n">
-        <v>6834565</v>
+        <v>6834427</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8444,22 +8462,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129522450</v>
+        <v>129524147</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8467,21 +8485,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8491,10 +8509,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494325</v>
+        <v>494596</v>
       </c>
       <c r="R80" t="n">
-        <v>6834177</v>
+        <v>6834467</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -8553,10 +8571,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129524119</v>
+        <v>129521271</v>
       </c>
       <c r="B81" t="n">
-        <v>80186</v>
+        <v>79113</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8564,37 +8582,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494556</v>
+        <v>494237</v>
       </c>
       <c r="R81" t="n">
-        <v>6834467</v>
+        <v>6834397</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8638,19 +8656,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522454</v>
+        <v>129522450</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8681,17 +8699,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494456</v>
+        <v>494325</v>
       </c>
       <c r="R82" t="n">
         <v>6834177</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8735,66 +8753,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129520989</v>
+        <v>129524246</v>
       </c>
       <c r="B83" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494262</v>
+        <v>494560</v>
       </c>
       <c r="R83" t="n">
-        <v>6834427</v>
+        <v>6834565</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8841,66 +8850,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522644</v>
+        <v>129522454</v>
       </c>
       <c r="B84" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494450</v>
+        <v>494456</v>
       </c>
       <c r="R84" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8959,7 +8959,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129520902</v>
+        <v>129524525</v>
       </c>
       <c r="B85" t="n">
         <v>79081</v>
@@ -8990,14 +8990,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>494278</v>
+        <v>494354</v>
       </c>
       <c r="R85" t="n">
-        <v>6834456</v>
+        <v>6834662</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9044,19 +9044,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129524525</v>
+        <v>129520902</v>
       </c>
       <c r="B86" t="n">
         <v>79081</v>
@@ -9087,14 +9087,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494354</v>
+        <v>494278</v>
       </c>
       <c r="R86" t="n">
-        <v>6834662</v>
+        <v>6834456</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9141,12 +9141,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9541,45 +9541,59 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129522027</v>
+        <v>129524797</v>
       </c>
       <c r="B91" t="n">
-        <v>80187</v>
+        <v>92881</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494337</v>
+        <v>494387</v>
       </c>
       <c r="R91" t="n">
-        <v>6834149</v>
+        <v>6834437</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9626,22 +9640,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129524791</v>
+        <v>129522027</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9649,34 +9663,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494381</v>
+        <v>494337</v>
       </c>
       <c r="R92" t="n">
-        <v>6834429</v>
+        <v>6834149</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,22 +9737,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129522173</v>
+        <v>129521475</v>
       </c>
       <c r="B93" t="n">
-        <v>80186</v>
+        <v>78839</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9746,21 +9760,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9770,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494418</v>
+        <v>494181</v>
       </c>
       <c r="R93" t="n">
-        <v>6834113</v>
+        <v>6834367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9832,32 +9846,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129521897</v>
+        <v>129522173</v>
       </c>
       <c r="B94" t="n">
-        <v>98780</v>
+        <v>80186</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9867,10 +9881,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>494323</v>
+        <v>494418</v>
       </c>
       <c r="R94" t="n">
-        <v>6834131</v>
+        <v>6834113</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9929,10 +9943,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129521475</v>
+        <v>129524791</v>
       </c>
       <c r="B95" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9940,34 +9954,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494181</v>
+        <v>494381</v>
       </c>
       <c r="R95" t="n">
-        <v>6834367</v>
+        <v>6834429</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10014,71 +10028,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129524797</v>
+        <v>129521897</v>
       </c>
       <c r="B96" t="n">
-        <v>92881</v>
+        <v>98790</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494387</v>
+        <v>494323</v>
       </c>
       <c r="R96" t="n">
-        <v>6834437</v>
+        <v>6834131</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10125,12 +10125,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10234,7 +10234,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129523005</v>
+        <v>129524130</v>
       </c>
       <c r="B98" t="n">
         <v>79081</v>
@@ -10265,14 +10265,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>494491</v>
+        <v>494537</v>
       </c>
       <c r="R98" t="n">
-        <v>6834229</v>
+        <v>6834492</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10319,19 +10319,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129524530</v>
+        <v>129523005</v>
       </c>
       <c r="B99" t="n">
         <v>79081</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494349</v>
+        <v>494491</v>
       </c>
       <c r="R99" t="n">
-        <v>6834653</v>
+        <v>6834229</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10428,7 +10428,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129524130</v>
+        <v>129524530</v>
       </c>
       <c r="B100" t="n">
         <v>79081</v>
@@ -10459,14 +10459,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>494537</v>
+        <v>494349</v>
       </c>
       <c r="R100" t="n">
-        <v>6834492</v>
+        <v>6834653</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10513,12 +10513,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10528,7 +10528,7 @@
         <v>129522632</v>
       </c>
       <c r="B101" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129522517</v>
+        <v>129521967</v>
       </c>
       <c r="B102" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494455</v>
+        <v>494346</v>
       </c>
       <c r="R102" t="n">
-        <v>6834176</v>
+        <v>6834277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,60 +10716,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129522100</v>
+        <v>129521144</v>
       </c>
       <c r="B103" t="n">
-        <v>58106</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494368</v>
+        <v>494222</v>
       </c>
       <c r="R103" t="n">
-        <v>6834126</v>
+        <v>6834390</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10813,22 +10813,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129524122</v>
+        <v>129522517</v>
       </c>
       <c r="B104" t="n">
-        <v>80187</v>
+        <v>78839</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,21 +10836,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10860,10 +10860,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494556</v>
+        <v>494455</v>
       </c>
       <c r="R104" t="n">
-        <v>6834467</v>
+        <v>6834176</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521967</v>
+        <v>129521977</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,34 +10933,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494346</v>
+        <v>494334</v>
       </c>
       <c r="R105" t="n">
-        <v>6834277</v>
+        <v>6834144</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11007,19 +11007,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521144</v>
+        <v>129521418</v>
       </c>
       <c r="B106" t="n">
         <v>79081</v>
@@ -11050,14 +11050,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494222</v>
+        <v>494176</v>
       </c>
       <c r="R106" t="n">
-        <v>6834390</v>
+        <v>6834368</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129521977</v>
+        <v>129522341</v>
       </c>
       <c r="B107" t="n">
-        <v>80186</v>
+        <v>78838</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,34 +11127,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494334</v>
+        <v>494345</v>
       </c>
       <c r="R107" t="n">
-        <v>6834144</v>
+        <v>6834202</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11201,22 +11201,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129521418</v>
+        <v>129524122</v>
       </c>
       <c r="B108" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,21 +11224,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11248,10 +11248,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494176</v>
+        <v>494556</v>
       </c>
       <c r="R108" t="n">
-        <v>6834368</v>
+        <v>6834468</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11310,48 +11310,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522341</v>
+        <v>129522100</v>
       </c>
       <c r="B109" t="n">
-        <v>78838</v>
+        <v>58106</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494345</v>
+        <v>494368</v>
       </c>
       <c r="R109" t="n">
-        <v>6834202</v>
+        <v>6834126</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11395,22 +11395,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129521874</v>
+        <v>129523028</v>
       </c>
       <c r="B110" t="n">
-        <v>80186</v>
+        <v>78089</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11418,21 +11418,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11442,10 +11442,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494355</v>
+        <v>494500</v>
       </c>
       <c r="R110" t="n">
-        <v>6834295</v>
+        <v>6834263</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,10 +11504,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129522819</v>
+        <v>129521874</v>
       </c>
       <c r="B111" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11515,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494470</v>
+        <v>494355</v>
       </c>
       <c r="R111" t="n">
-        <v>6834231</v>
+        <v>6834295</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11601,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129523028</v>
+        <v>129522819</v>
       </c>
       <c r="B112" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11612,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494500</v>
+        <v>494470</v>
       </c>
       <c r="R112" t="n">
-        <v>6834263</v>
+        <v>6834231</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11701,7 +11701,7 @@
         <v>129524619</v>
       </c>
       <c r="B113" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11804,10 +11804,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129524762</v>
+        <v>129524240</v>
       </c>
       <c r="B114" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11815,21 +11815,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11839,13 +11839,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>494406</v>
+        <v>494559</v>
       </c>
       <c r="R114" t="n">
-        <v>6834477</v>
+        <v>6834519</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129521072</v>
+        <v>129524762</v>
       </c>
       <c r="B115" t="n">
         <v>79081</v>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>494234</v>
+        <v>494406</v>
       </c>
       <c r="R115" t="n">
-        <v>6834416</v>
+        <v>6834477</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129524240</v>
+        <v>129521072</v>
       </c>
       <c r="B117" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12130,13 +12130,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>494559</v>
+        <v>494234</v>
       </c>
       <c r="R117" t="n">
-        <v>6834519</v>
+        <v>6834416</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129521663</v>
+        <v>129521664</v>
       </c>
       <c r="B118" t="n">
-        <v>78839</v>
+        <v>91620</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,34 +12203,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>494242</v>
+        <v>494255</v>
       </c>
       <c r="R118" t="n">
-        <v>6834295</v>
+        <v>6834250</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12277,22 +12277,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129523234</v>
+        <v>129524747</v>
       </c>
       <c r="B119" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12300,34 +12300,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>494472</v>
+        <v>494401</v>
       </c>
       <c r="R119" t="n">
-        <v>6834268</v>
+        <v>6834640</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12374,22 +12374,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129521664</v>
+        <v>129524381</v>
       </c>
       <c r="B120" t="n">
-        <v>91620</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12397,21 +12397,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>494255</v>
+        <v>494485</v>
       </c>
       <c r="R120" t="n">
-        <v>6834250</v>
+        <v>6834612</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129524747</v>
+        <v>129521663</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12494,34 +12494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>494401</v>
+        <v>494242</v>
       </c>
       <c r="R121" t="n">
-        <v>6834640</v>
+        <v>6834295</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12568,22 +12568,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129524381</v>
+        <v>129523234</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12591,34 +12591,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>494485</v>
+        <v>494472</v>
       </c>
       <c r="R122" t="n">
-        <v>6834612</v>
+        <v>6834268</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12665,12 +12665,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12871,10 +12871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129521635</v>
+        <v>129522012</v>
       </c>
       <c r="B125" t="n">
-        <v>78747</v>
+        <v>80186</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12882,37 +12882,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>494214</v>
+        <v>494337</v>
       </c>
       <c r="R125" t="n">
-        <v>6834306</v>
+        <v>6834146</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12956,22 +12956,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129522736</v>
+        <v>129524581</v>
       </c>
       <c r="B126" t="n">
-        <v>91620</v>
+        <v>80186</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12979,21 +12979,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>494443</v>
+        <v>494323</v>
       </c>
       <c r="R126" t="n">
-        <v>6834230</v>
+        <v>6834627</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13065,10 +13065,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129521002</v>
+        <v>129522736</v>
       </c>
       <c r="B127" t="n">
-        <v>79081</v>
+        <v>91620</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13076,21 +13076,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13100,10 +13100,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>494241</v>
+        <v>494443</v>
       </c>
       <c r="R127" t="n">
-        <v>6834425</v>
+        <v>6834230</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129522903</v>
+        <v>129521002</v>
       </c>
       <c r="B128" t="n">
         <v>79081</v>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>494466</v>
+        <v>494241</v>
       </c>
       <c r="R128" t="n">
-        <v>6834211</v>
+        <v>6834425</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129522012</v>
+        <v>129522903</v>
       </c>
       <c r="B129" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13270,34 +13270,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>494337</v>
+        <v>494466</v>
       </c>
       <c r="R129" t="n">
-        <v>6834146</v>
+        <v>6834211</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13344,12 +13344,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129524581</v>
+        <v>129521635</v>
       </c>
       <c r="B131" t="n">
-        <v>80186</v>
+        <v>78747</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13488,13 +13488,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>494323</v>
+        <v>494214</v>
       </c>
       <c r="R131" t="n">
-        <v>6834627</v>
+        <v>6834306</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>129521085</v>
       </c>
       <c r="B138" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -3403,45 +3403,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129514113</v>
+        <v>129512658</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Korplamm, Korplamm, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494256</v>
+        <v>494506</v>
       </c>
       <c r="R28" t="n">
-        <v>6834732</v>
+        <v>6834042</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,45 +3500,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129512658</v>
+        <v>129514113</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Korplamm, Korplamm, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494506</v>
+        <v>494256</v>
       </c>
       <c r="R29" t="n">
-        <v>6834042</v>
+        <v>6834732</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -6216,54 +6216,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129524059</v>
+        <v>129521358</v>
       </c>
       <c r="B57" t="n">
-        <v>98790</v>
+        <v>79113</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>494582</v>
+        <v>494221</v>
       </c>
       <c r="R57" t="n">
-        <v>6834361</v>
+        <v>6834353</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,10 +6313,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129522138</v>
+        <v>129521131</v>
       </c>
       <c r="B58" t="n">
-        <v>79671</v>
+        <v>79113</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6333,21 +6324,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6357,10 +6348,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494375</v>
+        <v>494230</v>
       </c>
       <c r="R58" t="n">
-        <v>6834215</v>
+        <v>6834385</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6419,7 +6410,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129521358</v>
+        <v>129522432</v>
       </c>
       <c r="B59" t="n">
         <v>79113</v>
@@ -6454,13 +6445,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494221</v>
+        <v>494325</v>
       </c>
       <c r="R59" t="n">
-        <v>6834353</v>
+        <v>6834177</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6516,48 +6507,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129521131</v>
+        <v>129524392</v>
       </c>
       <c r="B60" t="n">
-        <v>79113</v>
+        <v>92881</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>494230</v>
+        <v>494486</v>
       </c>
       <c r="R60" t="n">
-        <v>6834385</v>
+        <v>6834613</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6601,22 +6592,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129522432</v>
+        <v>129521656</v>
       </c>
       <c r="B61" t="n">
-        <v>79113</v>
+        <v>80187</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6624,37 +6615,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494325</v>
+        <v>494219</v>
       </c>
       <c r="R61" t="n">
-        <v>6834177</v>
+        <v>6834291</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6698,12 +6689,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6807,48 +6798,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129524392</v>
+        <v>129524189</v>
       </c>
       <c r="B63" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>494486</v>
+        <v>494606</v>
       </c>
       <c r="R63" t="n">
-        <v>6834613</v>
+        <v>6834497</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6892,19 +6883,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129524189</v>
+        <v>129522857</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6939,13 +6930,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494606</v>
+        <v>494475</v>
       </c>
       <c r="R64" t="n">
-        <v>6834497</v>
+        <v>6834232</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7001,7 +6992,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129522857</v>
+        <v>129524775</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7036,10 +7027,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494475</v>
+        <v>494416</v>
       </c>
       <c r="R65" t="n">
-        <v>6834232</v>
+        <v>6834464</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7098,45 +7089,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129524775</v>
+        <v>129524059</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494416</v>
+        <v>494582</v>
       </c>
       <c r="R66" t="n">
-        <v>6834464</v>
+        <v>6834361</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7195,10 +7195,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129521656</v>
+        <v>129522138</v>
       </c>
       <c r="B67" t="n">
-        <v>80187</v>
+        <v>79671</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7206,37 +7206,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494219</v>
+        <v>494375</v>
       </c>
       <c r="R67" t="n">
-        <v>6834291</v>
+        <v>6834215</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7280,12 +7280,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7777,10 +7777,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129523011</v>
+        <v>129522011</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7788,34 +7788,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494480</v>
+        <v>494385</v>
       </c>
       <c r="R73" t="n">
-        <v>6834232</v>
+        <v>6834293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7862,19 +7862,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129522011</v>
+        <v>129521838</v>
       </c>
       <c r="B74" t="n">
         <v>79113</v>
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>494385</v>
+        <v>494355</v>
       </c>
       <c r="R74" t="n">
-        <v>6834293</v>
+        <v>6834299</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129521838</v>
+        <v>129523011</v>
       </c>
       <c r="B75" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7982,37 +7982,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>494355</v>
+        <v>494480</v>
       </c>
       <c r="R75" t="n">
-        <v>6834299</v>
+        <v>6834232</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8056,12 +8056,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8262,57 +8262,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129522644</v>
+        <v>129522450</v>
       </c>
       <c r="B78" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>494450</v>
+        <v>494325</v>
       </c>
       <c r="R78" t="n">
-        <v>6834178</v>
+        <v>6834177</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8356,66 +8347,57 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129520989</v>
+        <v>129524246</v>
       </c>
       <c r="B79" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>494262</v>
+        <v>494560</v>
       </c>
       <c r="R79" t="n">
-        <v>6834427</v>
+        <v>6834565</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8462,22 +8444,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129524147</v>
+        <v>129522454</v>
       </c>
       <c r="B80" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8485,37 +8467,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>494596</v>
+        <v>494456</v>
       </c>
       <c r="R80" t="n">
-        <v>6834467</v>
+        <v>6834177</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8559,19 +8541,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129521271</v>
+        <v>129524147</v>
       </c>
       <c r="B81" t="n">
         <v>79113</v>
@@ -8606,10 +8588,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>494237</v>
+        <v>494596</v>
       </c>
       <c r="R81" t="n">
-        <v>6834397</v>
+        <v>6834467</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -8668,10 +8650,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129522450</v>
+        <v>129521271</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8679,21 +8661,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8703,10 +8685,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>494325</v>
+        <v>494237</v>
       </c>
       <c r="R82" t="n">
-        <v>6834177</v>
+        <v>6834397</v>
       </c>
       <c r="S82" t="n">
         <v>20</v>
@@ -8765,45 +8747,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129524246</v>
+        <v>129522644</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>494560</v>
+        <v>494450</v>
       </c>
       <c r="R83" t="n">
-        <v>6834565</v>
+        <v>6834178</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8850,57 +8841,66 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129522454</v>
+        <v>129520989</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494456</v>
+        <v>494262</v>
       </c>
       <c r="R84" t="n">
-        <v>6834177</v>
+        <v>6834427</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9541,59 +9541,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129524797</v>
+        <v>129524791</v>
       </c>
       <c r="B91" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>494387</v>
+        <v>494381</v>
       </c>
       <c r="R91" t="n">
-        <v>6834437</v>
+        <v>6834429</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9652,32 +9638,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129522027</v>
+        <v>129521897</v>
       </c>
       <c r="B92" t="n">
-        <v>80187</v>
+        <v>98790</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9687,10 +9673,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>494337</v>
+        <v>494323</v>
       </c>
       <c r="R92" t="n">
-        <v>6834149</v>
+        <v>6834131</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9943,45 +9929,59 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129524791</v>
+        <v>129524797</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>494381</v>
+        <v>494387</v>
       </c>
       <c r="R95" t="n">
-        <v>6834429</v>
+        <v>6834437</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10040,32 +10040,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129521897</v>
+        <v>129522027</v>
       </c>
       <c r="B96" t="n">
-        <v>98790</v>
+        <v>80187</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>494323</v>
+        <v>494337</v>
       </c>
       <c r="R96" t="n">
-        <v>6834131</v>
+        <v>6834149</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10631,10 +10631,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129521967</v>
+        <v>129524122</v>
       </c>
       <c r="B102" t="n">
-        <v>79081</v>
+        <v>80187</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,34 +10642,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>494346</v>
+        <v>494556</v>
       </c>
       <c r="R102" t="n">
-        <v>6834277</v>
+        <v>6834468</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10716,60 +10716,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129521144</v>
+        <v>129522100</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>58106</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Rankasåsen, Rankasåsen, Dlr</t>
+          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>494222</v>
+        <v>494368</v>
       </c>
       <c r="R103" t="n">
-        <v>6834390</v>
+        <v>6834126</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10813,22 +10813,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129522517</v>
+        <v>129521977</v>
       </c>
       <c r="B104" t="n">
-        <v>78839</v>
+        <v>80186</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10836,21 +10836,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10860,10 +10860,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>494455</v>
+        <v>494334</v>
       </c>
       <c r="R104" t="n">
-        <v>6834176</v>
+        <v>6834144</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129521977</v>
+        <v>129521418</v>
       </c>
       <c r="B105" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10933,21 +10933,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>494334</v>
+        <v>494176</v>
       </c>
       <c r="R105" t="n">
-        <v>6834144</v>
+        <v>6834368</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129521418</v>
+        <v>129522341</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11030,34 +11030,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>494176</v>
+        <v>494345</v>
       </c>
       <c r="R106" t="n">
-        <v>6834368</v>
+        <v>6834202</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11104,22 +11104,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129522341</v>
+        <v>129521967</v>
       </c>
       <c r="B107" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11151,10 +11151,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>494345</v>
+        <v>494346</v>
       </c>
       <c r="R107" t="n">
-        <v>6834202</v>
+        <v>6834277</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11213,10 +11213,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129524122</v>
+        <v>129521144</v>
       </c>
       <c r="B108" t="n">
-        <v>80187</v>
+        <v>79081</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11224,34 +11224,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kangastorpsbäcken, Kangastorpsbäcken, Dlr</t>
+          <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>494556</v>
+        <v>494222</v>
       </c>
       <c r="R108" t="n">
-        <v>6834468</v>
+        <v>6834390</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11298,44 +11298,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129522100</v>
+        <v>129522517</v>
       </c>
       <c r="B109" t="n">
-        <v>58106</v>
+        <v>78839</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>494368</v>
+        <v>494455</v>
       </c>
       <c r="R109" t="n">
-        <v>6834126</v>
+        <v>6834176</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11407,45 +11407,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129523028</v>
+        <v>129524619</v>
       </c>
       <c r="B110" t="n">
-        <v>78089</v>
+        <v>98790</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>494500</v>
+        <v>494338</v>
       </c>
       <c r="R110" t="n">
-        <v>6834263</v>
+        <v>6834601</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11504,10 +11513,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129521874</v>
+        <v>129523028</v>
       </c>
       <c r="B111" t="n">
-        <v>80186</v>
+        <v>78089</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11515,21 +11524,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11539,10 +11548,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>494355</v>
+        <v>494500</v>
       </c>
       <c r="R111" t="n">
-        <v>6834295</v>
+        <v>6834263</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11601,10 +11610,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129522819</v>
+        <v>129521874</v>
       </c>
       <c r="B112" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11612,21 +11621,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11636,10 +11645,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>494470</v>
+        <v>494355</v>
       </c>
       <c r="R112" t="n">
-        <v>6834231</v>
+        <v>6834295</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11698,54 +11707,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129524619</v>
+        <v>129522819</v>
       </c>
       <c r="B113" t="n">
-        <v>98790</v>
+        <v>79081</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rankasåsen, Rankasåsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>494338</v>
+        <v>494470</v>
       </c>
       <c r="R113" t="n">
-        <v>6834601</v>
+        <v>6834231</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -9250,10 +9250,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129521936</v>
+        <v>129522147</v>
       </c>
       <c r="B88" t="n">
-        <v>79113</v>
+        <v>78839</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9261,21 +9261,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9285,10 +9285,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>494342</v>
+        <v>494385</v>
       </c>
       <c r="R88" t="n">
-        <v>6834284</v>
+        <v>6834229</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,7 +9347,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129521041</v>
+        <v>129521936</v>
       </c>
       <c r="B89" t="n">
         <v>79113</v>
@@ -9382,10 +9382,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>494251</v>
+        <v>494342</v>
       </c>
       <c r="R89" t="n">
-        <v>6834413</v>
+        <v>6834284</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9444,10 +9444,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129522147</v>
+        <v>129521041</v>
       </c>
       <c r="B90" t="n">
-        <v>78839</v>
+        <v>79113</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9455,21 +9455,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9479,10 +9479,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>494385</v>
+        <v>494251</v>
       </c>
       <c r="R90" t="n">
-        <v>6834229</v>
+        <v>6834413</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 52457-2025 artfynd.xlsx
+++ b/artfynd/A 52457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY172"/>
+  <dimension ref="A1:AZ172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121484307</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121484267</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476541</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129455888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129476557</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121484131</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129455942</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456013</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456184</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456266</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456312</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456325</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456373</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,6 +2213,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456404</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2324,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129456470</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2346,6 +2426,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521041</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2443,6 +2528,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521131</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2540,6 +2630,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521271</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2637,6 +2732,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2734,6 +2834,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521838</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2831,6 +2936,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521936</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2928,6 +3038,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522011</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3025,6 +3140,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522432</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3122,6 +3242,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522783</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3219,6 +3344,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522893</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3316,6 +3446,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524147</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3413,6 +3548,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524240</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3510,6 +3650,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524273</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3607,6 +3752,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520992</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3704,6 +3854,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521635</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3801,6 +3956,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521655</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3898,6 +4058,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521752</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3995,6 +4160,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522065</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4092,6 +4262,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523308</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4189,6 +4364,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521403</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4286,6 +4466,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512476</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4383,6 +4568,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521656</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4480,6 +4670,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521826</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4577,6 +4772,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521986</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4674,6 +4874,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522027</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4771,6 +4976,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524122</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4877,6 +5087,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524667</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4974,6 +5189,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524392</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5085,6 +5305,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524797</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5182,6 +5407,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521664</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5279,6 +5509,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522736</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5386,6 +5621,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463373</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5483,6 +5723,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121313238</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5595,6 +5840,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121462834</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5707,6 +5957,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463067</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5819,6 +6074,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463429</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5931,6 +6191,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121463770</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6028,6 +6293,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511911</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6125,6 +6395,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511957</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6222,6 +6497,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511985</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6319,6 +6599,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512105</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6416,6 +6701,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512125</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6513,6 +6803,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512195</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6610,6 +6905,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512298</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6707,6 +7007,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512361</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6804,6 +7109,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512658</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6901,6 +7211,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512676</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6998,6 +7313,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512771</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7095,6 +7415,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512788</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7192,6 +7517,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129512918</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7289,6 +7619,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513122</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7386,6 +7721,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513342</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7483,6 +7823,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513370</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7580,6 +7925,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513412</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7677,6 +8027,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513741</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7774,6 +8129,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513963</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7871,6 +8231,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520902</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7968,6 +8333,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520912</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8065,6 +8435,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520952</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8162,6 +8537,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521002</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8259,6 +8639,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521072</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8356,6 +8741,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521144</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8453,6 +8843,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521147</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8550,6 +8945,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521302</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8647,6 +9047,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521418</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8744,6 +9149,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521804</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8841,6 +9251,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521823</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8938,6 +9353,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129521967</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9035,6 +9455,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522129</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9132,6 +9557,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522450</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9229,6 +9659,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522454</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9326,6 +9761,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522706</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9423,6 +9863,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522819</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9520,6 +9965,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522857</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9617,6 +10067,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129522903</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9714,6 +10169,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523005</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9811,6 +10271,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523011</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9908,6 +10373,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524130</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10005,6 +10475,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524189</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10102,6 +10577,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524246</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10199,6 +10679,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524342</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10296,6 +10781,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524381</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10393,6 +10883,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524385</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10490,6 +10985,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524525</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10587,6 +11087,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524530</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10684,6 +11189,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524747</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10781,6 +11291,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524762</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10878,6 +11393,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524775</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10975,6 +11495,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524779</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11072,6 +11597,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524785</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t=